--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="136">
   <si>
     <t xml:space="preserve">Proiezione pensionistica — Parametri di input</t>
   </si>
@@ -383,22 +383,7 @@
     <t xml:space="preserve">Crescita RAL annua reale</t>
   </si>
   <si>
-    <t xml:space="preserve">0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rivalutazione PIL annua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022</t>
   </si>
   <si>
     <t xml:space="preserve">Pensione INPS lorda annua</t>
@@ -845,34 +830,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1018,7 +1003,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -1396,7 +1381,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -1682,7 +1667,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -3328,7 +3313,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
@@ -5201,7 +5186,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
@@ -5241,60 +5226,60 @@
       <c r="A5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>119</v>
+      <c r="B5" s="31" t="n">
+        <v>0.005</v>
       </c>
       <c r="C5" s="32" t="n">
         <f aca="false">Input!$B$12</f>
         <v>0.015</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>120</v>
+      <c r="D5" s="31" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>0.01</v>
       </c>
       <c r="C6" s="32" t="n">
         <f aca="false">Input!$B$16</f>
         <v>0.018</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>120</v>
+      <c r="D6" s="31" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>120</v>
+      <c r="B7" s="31" t="n">
+        <v>0.025</v>
       </c>
       <c r="C7" s="32" t="n">
         <f aca="false">Input!$B$17</f>
         <v>0.02</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>123</v>
+      <c r="D7" s="31" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>124</v>
+      <c r="B8" s="31" t="n">
+        <v>0.022</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">Input!$B$18</f>
         <v>0.018</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>123</v>
+      <c r="D8" s="31" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5316,7 +5301,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">Pubblica!B61*(1-B8)^(Input!$B$36/2)/(1-Input!$B$18)^(Input!$B$36/2)</f>
@@ -5333,7 +5318,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">Pubblica!B66*B11/Pubblica!B61</f>
@@ -5350,7 +5335,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">Complementare!B58*0.85</f>
@@ -5367,7 +5352,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">Complementare!B61*0.85</f>
@@ -5384,7 +5369,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">Complementare!B62*0.85</f>
@@ -5401,7 +5386,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
@@ -5418,7 +5403,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Input!$B$39*(1+B7)^Input!$B$36</f>
@@ -5435,7 +5420,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
@@ -5452,7 +5437,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
@@ -5469,12 +5454,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -5482,7 +5467,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -5490,7 +5475,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -5498,7 +5483,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -5506,7 +5491,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -5514,7 +5499,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -287,7 +287,7 @@
     <t xml:space="preserve">IRPEF lorda su pensione (scaglioni 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Detrazione pensionati (stima)</t>
+    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR)</t>
   </si>
   <si>
     <t xml:space="preserve">Addizionali regionali + comunali (~2%)</t>
@@ -3239,8 +3239,8 @@
         <v>87</v>
       </c>
       <c r="B64" s="15" t="n">
-        <f aca="false">IF(B61&lt;=8500, 1955, IF(B61&lt;=28000, 1955 - (1955-1880)*(B61-8500)/(28000-8500), 1880))</f>
-        <v>1880</v>
+        <f aca="false">IF(B61&lt;=8500, 1955, IF(B61&lt;=28000, 700 + 1255*(28000-B61)/19500, IF(B61&lt;=50000, 700*(50000-B61)/22000, 0)))</f>
+        <v>310.71244050605</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B66" s="29" t="n">
         <f aca="false">B61-MAX(0,B63-B64)-B65</f>
-        <v>30832.5887153764</v>
+        <v>29263.3011558825</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B67" s="29" t="n">
         <f aca="false">B66/13</f>
-        <v>2371.73759349049</v>
+        <v>2251.02316583711</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5322,15 +5322,15 @@
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">Pubblica!B66*B11/Pubblica!B61</f>
-        <v>29478.883228834</v>
+        <v>27978.4952741984</v>
       </c>
       <c r="C12" s="26" t="n">
         <f aca="false">Pubblica!B66*C11/Pubblica!B61</f>
-        <v>30832.5887153764</v>
+        <v>29263.3011558825</v>
       </c>
       <c r="D12" s="26" t="n">
         <f aca="false">Pubblica!B66*D11/Pubblica!B61</f>
-        <v>31884.687114467</v>
+        <v>30261.8508586798</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5390,15 +5390,15 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
-        <v>39135.6996731654</v>
+        <v>37635.3117185298</v>
       </c>
       <c r="C17" s="25" t="n">
         <f aca="false">C12+C15</f>
-        <v>42193.5492381192</v>
+        <v>40624.2616786253</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">D12+D15</f>
-        <v>45290.6205313035</v>
+        <v>43667.7842755163</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5424,15 +5424,15 @@
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
-        <v>1149.07103020886</v>
+        <v>2649.45898484445</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C18-C17</f>
-        <v>-6017.62494196362</v>
+        <v>-4448.33738246965</v>
       </c>
       <c r="D19" s="33" t="n">
         <f aca="false">D18-D17</f>
-        <v>-12821.6299718247</v>
+        <v>-11198.7937160374</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5441,15 +5441,15 @@
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
-        <v>0.0285237078465639</v>
+        <v>0.0657682528306543</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IFERROR(C19/C18, 0)</f>
-        <v>-0.166343363964942</v>
+        <v>-0.122964028397814</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(D19/D18, 0)</f>
-        <v>-0.394888468994352</v>
+        <v>-0.344907356929459</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="141">
   <si>
     <t xml:space="preserve">Proiezione pensionistica — Parametri di input</t>
   </si>
   <si>
-    <t xml:space="preserve">Modifica le celle in BLU per personalizzare. Le formule (nero) si aggiornano automaticamente.</t>
+    <t xml:space="preserve">Modifica le celle in BLU per personalizzare. Le formule (nero) si aggiornano automaticamente. Tutti gli importi sono in euro di oggi (valori reali).</t>
   </si>
   <si>
     <t xml:space="preserve">ANAGRAFICA E PROFILO</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">MACROECONOMIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Rivalutazione PIL annua (montante INPS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media storica ~1,8%</t>
+    <t xml:space="preserve">Rivalutazione PIL reale annua (montante INPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIL nominale per legge, meno l'inflazione: ~0,5% (come proiezione-inps.py)</t>
   </si>
   <si>
     <t xml:space="preserve">Inflazione attesa</t>
   </si>
   <si>
-    <t xml:space="preserve">target BCE 2%</t>
+    <t xml:space="preserve">target BCE 2%; serve solo alla vista nominale degli Scenari</t>
   </si>
   <si>
     <t xml:space="preserve">Decadimento coefficiente / biennio</t>
@@ -203,6 +203,15 @@
     <t xml:space="preserve">coeff. attuale ridotto per i bienni mancanti</t>
   </si>
   <si>
+    <t xml:space="preserve">PARAMETRI NORMATIVI 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimale contributivo annuo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circ. INPS 6/2026; oltre non si versano contributi (iscritti dal 1996)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coefficienti di trasformazione — biennio 2025-2026</t>
   </si>
   <si>
@@ -245,7 +254,7 @@
     <t xml:space="preserve">Proiezione previdenza obbligatoria INPS</t>
   </si>
   <si>
-    <t xml:space="preserve">Proiezione anno per anno del montante contributivo INPS. La pensione usa il coefficiente PROIETTATO all'anno di pensionamento (vedi foglio Input), non quello attuale.</t>
+    <t xml:space="preserve">Proiezione anno per anno del montante contributivo INPS, in euro di oggi (RAL reale, PIL reale). Il contributo dell'anno si rivaluta dall'anno successivo (L. 335/1995) e la retribuzione oltre il massimale non versa contributi. La pensione usa il coefficiente PROIETTATO all'anno di pensionamento (vedi foglio Input), non quello attuale.</t>
   </si>
   <si>
     <t xml:space="preserve">Anno offset</t>
@@ -254,7 +263,7 @@
     <t xml:space="preserve">RAL lorda</t>
   </si>
   <si>
-    <t xml:space="preserve">Contributo (33%)</t>
+    <t xml:space="preserve">Contributo (33%, fino al massimale)</t>
   </si>
   <si>
     <t xml:space="preserve">Montante inizio</t>
@@ -290,7 +299,7 @@
     <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Addizionali regionali + comunali (~2%)</t>
+    <t xml:space="preserve">Addizionali regionali + comunali (~2%, se c'è IRPEF)</t>
   </si>
   <si>
     <t xml:space="preserve">Pensione NETTA annua</t>
@@ -365,7 +374,7 @@
     <t xml:space="preserve">Confronto scenari: conservativo / base / ottimistico</t>
   </si>
   <si>
-    <t xml:space="preserve">Base è il calcolo degli altri fogli (coefficiente già proiettato). Conservativo/Ottimistico applicano correttivi indicativi per ulteriore incertezza.</t>
+    <t xml:space="preserve">Tutto in euro di oggi. Base coincide con i fogli Pubblica e Complementare; Conservativo e Ottimistico ricalcolano pensione INPS e fondo con i parametri della propria colonna.</t>
   </si>
   <si>
     <t xml:space="preserve">Voce</t>
@@ -383,13 +392,16 @@
     <t xml:space="preserve">Crescita RAL annua reale</t>
   </si>
   <si>
-    <t xml:space="preserve">Rivalutazione PIL annua</t>
+    <t xml:space="preserve">Rivalutazione PIL reale annua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflazione attesa (solo vista nominale, riga 21)</t>
   </si>
   <si>
     <t xml:space="preserve">Pensione INPS lorda annua</t>
   </si>
   <si>
-    <t xml:space="preserve">Pensione INPS netta annua</t>
+    <t xml:space="preserve">Pensione INPS netta annua (IRPEF del foglio Pubblica)</t>
   </si>
   <si>
     <t xml:space="preserve">Montante fondo finale</t>
@@ -404,7 +416,7 @@
     <t xml:space="preserve">Reddito pensione totale netto annuo</t>
   </si>
   <si>
-    <t xml:space="preserve">Spesa target annua (nominale @ pensione)</t>
+    <t xml:space="preserve">Spesa target annua (€ di oggi)</t>
   </si>
   <si>
     <t xml:space="preserve">GAP (spesa target - reddito pensione)</t>
@@ -413,6 +425,9 @@
     <t xml:space="preserve">Gap % della spesa target</t>
   </si>
   <si>
+    <t xml:space="preserve">GAP in € del pensionamento (inflazione dello scenario)</t>
+  </si>
+  <si>
     <t xml:space="preserve">INTERPRETAZIONE:</t>
   </si>
   <si>
@@ -422,16 +437,16 @@
     <t xml:space="preserve">• GAP &lt; 0: over-saving → margine per consumi extra o lascito</t>
   </si>
   <si>
-    <t xml:space="preserve">• Il coefficiente di trasformazione è già proiettato in calo nello scenario Base; conservativo e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ottimistico variano anche il ritmo di decadimento (2,2% vs 1,5% per biennio).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Correttivi fondo: -15%/+18% per incertezza su rendimenti di lungo periodo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Spesa target in valori nominali al pensionamento (inflazione applicata).</t>
+    <t xml:space="preserve">• Tutto in euro di oggi: RAL e PIL reali, spesa target senza inflazione. Conservativo e ottimistico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ricalcolano INPS e fondo con la propria crescita RAL, PIL reale, decadimento e rendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Fondo: stesso montante del foglio Complementare con il rendimento della colonna (B9:D9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• L'inflazione (riga 7) serve solo alla riga 21, che riporta il gap in € del pensionamento.</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -1138,7 +1153,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>22</v>
@@ -1353,8 +1368,26 @@
         <v>58</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>122295</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -1364,6 +1397,7 @@
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1390,27 +1424,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1580,12 +1614,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -1593,7 +1627,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -1601,7 +1635,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -1609,7 +1643,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -1617,7 +1651,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -1625,7 +1659,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -1633,7 +1667,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -1676,7 +1710,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1687,7 +1721,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1698,25 +1732,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1732,20 +1766,20 @@
         <v>45000</v>
       </c>
       <c r="D5" s="25" t="n">
-        <f aca="false">C5*Input!$B$13</f>
+        <f aca="false">MIN(C5,Input!$B$43)*Input!$B$13</f>
         <v>14850</v>
       </c>
       <c r="E5" s="26" t="n">
-        <f aca="false">IF(Input!$B$14&gt;0,Input!$B$14,Input!$B$10*Input!$B$13*(IF(ABS(((1+Input!$B$16)/(1+Input!$B$12))-1)&lt;0.0000001,Input!$B$11,((1+Input!$B$16)/(1+Input!$B$12))*(((1+Input!$B$16)/(1+Input!$B$12))^Input!$B$11-1)/(((1+Input!$B$16)/(1+Input!$B$12))-1))))</f>
-        <v>274932.674790466</v>
+        <f aca="false">IF(Input!$B$14&gt;0,Input!$B$14,MIN(Input!$B$10,Input!$B$43)*Input!$B$13*(IF(ABS(((1+Input!$B$16)/(1+Input!$B$12))-1)&lt;0.0000001,Input!$B$11,((1+Input!$B$16)/(1+Input!$B$12))*(((1+Input!$B$16)/(1+Input!$B$12))^Input!$B$11-1)/(((1+Input!$B$16)/(1+Input!$B$12))-1))))</f>
+        <v>243625.067612767</v>
       </c>
       <c r="F5" s="25" t="n">
-        <f aca="false">(E5+D5)*Input!$B$16</f>
-        <v>5216.08814622839</v>
+        <f aca="false">E5*Input!$B$16</f>
+        <v>1218.12533806384</v>
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">IF(B5&lt;Input!$B$6, E5+D5+F5, E5)</f>
-        <v>294998.762936695</v>
+        <v>259693.192950831</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1761,20 +1795,20 @@
         <v>45675</v>
       </c>
       <c r="D6" s="25" t="n">
-        <f aca="false">C6*Input!$B$13</f>
+        <f aca="false">MIN(C6,Input!$B$43)*Input!$B$13</f>
         <v>15072.75</v>
       </c>
       <c r="E6" s="25" t="n">
         <f aca="false">G5</f>
-        <v>294998.762936695</v>
+        <v>259693.192950831</v>
       </c>
       <c r="F6" s="25" t="n">
-        <f aca="false">(E6+D6)*Input!$B$16</f>
-        <v>5581.2872328605</v>
+        <f aca="false">E6*Input!$B$16</f>
+        <v>1298.46596475416</v>
       </c>
       <c r="G6" s="25" t="n">
         <f aca="false">IF(B6&lt;Input!$B$6, E6+D6+F6, E6)</f>
-        <v>315652.800169555</v>
+        <v>276064.408915585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1790,20 +1824,20 @@
         <v>46360.125</v>
       </c>
       <c r="D7" s="25" t="n">
-        <f aca="false">C7*Input!$B$13</f>
+        <f aca="false">MIN(C7,Input!$B$43)*Input!$B$13</f>
         <v>15298.84125</v>
       </c>
       <c r="E7" s="25" t="n">
         <f aca="false">G6</f>
-        <v>315652.800169555</v>
+        <v>276064.408915585</v>
       </c>
       <c r="F7" s="25" t="n">
-        <f aca="false">(E7+D7)*Input!$B$16</f>
-        <v>5957.12954555199</v>
+        <f aca="false">E7*Input!$B$16</f>
+        <v>1380.32204457793</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">IF(B7&lt;Input!$B$6, E7+D7+F7, E7)</f>
-        <v>336908.770965107</v>
+        <v>292743.572210163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1819,20 +1853,20 @@
         <v>47055.526875</v>
       </c>
       <c r="D8" s="25" t="n">
-        <f aca="false">C8*Input!$B$13</f>
+        <f aca="false">MIN(C8,Input!$B$43)*Input!$B$13</f>
         <v>15528.32386875</v>
       </c>
       <c r="E8" s="25" t="n">
         <f aca="false">G7</f>
-        <v>336908.770965107</v>
+        <v>292743.572210163</v>
       </c>
       <c r="F8" s="25" t="n">
-        <f aca="false">(E8+D8)*Input!$B$16</f>
-        <v>6343.86770700943</v>
+        <f aca="false">E8*Input!$B$16</f>
+        <v>1463.71786105082</v>
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">IF(B8&lt;Input!$B$6, E8+D8+F8, E8)</f>
-        <v>358780.962540867</v>
+        <v>309735.613939964</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1848,20 +1882,20 @@
         <v>47761.359778125</v>
       </c>
       <c r="D9" s="25" t="n">
-        <f aca="false">C9*Input!$B$13</f>
+        <f aca="false">MIN(C9,Input!$B$43)*Input!$B$13</f>
         <v>15761.2487267812</v>
       </c>
       <c r="E9" s="25" t="n">
         <f aca="false">G8</f>
-        <v>358780.962540867</v>
+        <v>309735.613939964</v>
       </c>
       <c r="F9" s="25" t="n">
-        <f aca="false">(E9+D9)*Input!$B$16</f>
-        <v>6741.75980281766</v>
+        <f aca="false">E9*Input!$B$16</f>
+        <v>1548.67806969982</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF(B9&lt;Input!$B$6, E9+D9+F9, E9)</f>
-        <v>381283.971070465</v>
+        <v>327045.540736445</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1877,20 +1911,20 @@
         <v>48477.7801747969</v>
       </c>
       <c r="D10" s="25" t="n">
-        <f aca="false">C10*Input!$B$13</f>
+        <f aca="false">MIN(C10,Input!$B$43)*Input!$B$13</f>
         <v>15997.667457683</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">G9</f>
-        <v>381283.971070465</v>
+        <v>327045.540736445</v>
       </c>
       <c r="F10" s="25" t="n">
-        <f aca="false">(E10+D10)*Input!$B$16</f>
-        <v>7151.06949350667</v>
+        <f aca="false">E10*Input!$B$16</f>
+        <v>1635.22770368223</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF(B10&lt;Input!$B$6, E10+D10+F10, E10)</f>
-        <v>404432.708021655</v>
+        <v>344678.43589781</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1906,20 +1940,20 @@
         <v>49204.9468774188</v>
       </c>
       <c r="D11" s="25" t="n">
-        <f aca="false">C11*Input!$B$13</f>
+        <f aca="false">MIN(C11,Input!$B$43)*Input!$B$13</f>
         <v>16237.6324695482</v>
       </c>
       <c r="E11" s="25" t="n">
         <f aca="false">G10</f>
-        <v>404432.708021655</v>
+        <v>344678.43589781</v>
       </c>
       <c r="F11" s="25" t="n">
-        <f aca="false">(E11+D11)*Input!$B$16</f>
-        <v>7572.06612884166</v>
+        <f aca="false">E11*Input!$B$16</f>
+        <v>1723.39217948905</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF(B11&lt;Input!$B$6, E11+D11+F11, E11)</f>
-        <v>428242.406620045</v>
+        <v>362639.460546847</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1935,20 +1969,20 @@
         <v>49943.0210805801</v>
       </c>
       <c r="D12" s="25" t="n">
-        <f aca="false">C12*Input!$B$13</f>
+        <f aca="false">MIN(C12,Input!$B$43)*Input!$B$13</f>
         <v>16481.1969565914</v>
       </c>
       <c r="E12" s="25" t="n">
         <f aca="false">G11</f>
-        <v>428242.406620045</v>
+        <v>362639.460546847</v>
       </c>
       <c r="F12" s="25" t="n">
-        <f aca="false">(E12+D12)*Input!$B$16</f>
-        <v>8005.02486437945</v>
+        <f aca="false">E12*Input!$B$16</f>
+        <v>1813.19730273424</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF(B12&lt;Input!$B$6, E12+D12+F12, E12)</f>
-        <v>452728.628441016</v>
+        <v>380933.854806173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1964,20 +1998,20 @@
         <v>50692.1663967888</v>
       </c>
       <c r="D13" s="25" t="n">
-        <f aca="false">C13*Input!$B$13</f>
+        <f aca="false">MIN(C13,Input!$B$43)*Input!$B$13</f>
         <v>16728.4149109403</v>
       </c>
       <c r="E13" s="25" t="n">
         <f aca="false">G12</f>
-        <v>452728.628441016</v>
+        <v>380933.854806173</v>
       </c>
       <c r="F13" s="25" t="n">
-        <f aca="false">(E13+D13)*Input!$B$16</f>
-        <v>8450.22678033521</v>
+        <f aca="false">E13*Input!$B$16</f>
+        <v>1904.66927403087</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF(B13&lt;Input!$B$6, E13+D13+F13, E13)</f>
-        <v>477907.270132291</v>
+        <v>399566.938991144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1993,20 +2027,20 @@
         <v>51452.5488927406</v>
       </c>
       <c r="D14" s="25" t="n">
-        <f aca="false">C14*Input!$B$13</f>
+        <f aca="false">MIN(C14,Input!$B$43)*Input!$B$13</f>
         <v>16979.3411346044</v>
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">G13</f>
-        <v>477907.270132291</v>
+        <v>399566.938991144</v>
       </c>
       <c r="F14" s="25" t="n">
-        <f aca="false">(E14+D14)*Input!$B$16</f>
-        <v>8907.95900280412</v>
+        <f aca="false">E14*Input!$B$16</f>
+        <v>1997.83469495572</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF(B14&lt;Input!$B$6, E14+D14+F14, E14)</f>
-        <v>503794.5702697</v>
+        <v>418544.114820704</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2022,20 +2056,20 @@
         <v>52224.3371261317</v>
       </c>
       <c r="D15" s="25" t="n">
-        <f aca="false">C15*Input!$B$13</f>
+        <f aca="false">MIN(C15,Input!$B$43)*Input!$B$13</f>
         <v>17234.0312516235</v>
       </c>
       <c r="E15" s="25" t="n">
         <f aca="false">G14</f>
-        <v>503794.5702697</v>
+        <v>418544.114820704</v>
       </c>
       <c r="F15" s="25" t="n">
-        <f aca="false">(E15+D15)*Input!$B$16</f>
-        <v>9378.51482738382</v>
+        <f aca="false">E15*Input!$B$16</f>
+        <v>2092.72057410352</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF(B15&lt;Input!$B$6, E15+D15+F15, E15)</f>
-        <v>530407.116348707</v>
+        <v>437870.866646431</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2051,20 +2085,20 @@
         <v>53007.7021830237</v>
       </c>
       <c r="D16" s="25" t="n">
-        <f aca="false">C16*Input!$B$13</f>
+        <f aca="false">MIN(C16,Input!$B$43)*Input!$B$13</f>
         <v>17492.5417203978</v>
       </c>
       <c r="E16" s="25" t="n">
         <f aca="false">G15</f>
-        <v>530407.116348707</v>
+        <v>437870.866646431</v>
       </c>
       <c r="F16" s="25" t="n">
-        <f aca="false">(E16+D16)*Input!$B$16</f>
-        <v>9862.19384524389</v>
+        <f aca="false">E16*Input!$B$16</f>
+        <v>2189.35433323216</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF(B16&lt;Input!$B$6, E16+D16+F16, E16)</f>
-        <v>557761.851914349</v>
+        <v>457552.762700061</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2080,20 +2114,20 @@
         <v>53802.817715769</v>
       </c>
       <c r="D17" s="25" t="n">
-        <f aca="false">C17*Input!$B$13</f>
+        <f aca="false">MIN(C17,Input!$B$43)*Input!$B$13</f>
         <v>17754.9298462038</v>
       </c>
       <c r="E17" s="25" t="n">
         <f aca="false">G16</f>
-        <v>557761.851914349</v>
+        <v>457552.762700061</v>
       </c>
       <c r="F17" s="25" t="n">
-        <f aca="false">(E17+D17)*Input!$B$16</f>
-        <v>10359.3020716899</v>
+        <f aca="false">E17*Input!$B$16</f>
+        <v>2287.76381350031</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF(B17&lt;Input!$B$6, E17+D17+F17, E17)</f>
-        <v>585876.083832243</v>
+        <v>477595.456359766</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2109,20 +2143,20 @@
         <v>54609.8599815056</v>
       </c>
       <c r="D18" s="25" t="n">
-        <f aca="false">C18*Input!$B$13</f>
+        <f aca="false">MIN(C18,Input!$B$43)*Input!$B$13</f>
         <v>18021.2537938968</v>
       </c>
       <c r="E18" s="25" t="n">
         <f aca="false">G17</f>
-        <v>585876.083832243</v>
+        <v>477595.456359766</v>
       </c>
       <c r="F18" s="25" t="n">
-        <f aca="false">(E18+D18)*Input!$B$16</f>
-        <v>10870.1520772705</v>
+        <f aca="false">E18*Input!$B$16</f>
+        <v>2387.97728179883</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF(B18&lt;Input!$B$6, E18+D18+F18, E18)</f>
-        <v>614767.48970341</v>
+        <v>498004.687435461</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2138,20 +2172,20 @@
         <v>55429.0078812281</v>
       </c>
       <c r="D19" s="25" t="n">
-        <f aca="false">C19*Input!$B$13</f>
+        <f aca="false">MIN(C19,Input!$B$43)*Input!$B$13</f>
         <v>18291.5726008053</v>
       </c>
       <c r="E19" s="25" t="n">
         <f aca="false">G18</f>
-        <v>614767.48970341</v>
+        <v>498004.687435461</v>
       </c>
       <c r="F19" s="25" t="n">
-        <f aca="false">(E19+D19)*Input!$B$16</f>
-        <v>11395.0631214759</v>
+        <f aca="false">E19*Input!$B$16</f>
+        <v>2490.02343717731</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF(B19&lt;Input!$B$6, E19+D19+F19, E19)</f>
-        <v>644454.125425691</v>
+        <v>518786.283473444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2167,20 +2201,20 @@
         <v>56260.4429994466</v>
       </c>
       <c r="D20" s="25" t="n">
-        <f aca="false">C20*Input!$B$13</f>
+        <f aca="false">MIN(C20,Input!$B$43)*Input!$B$13</f>
         <v>18565.9461898174</v>
       </c>
       <c r="E20" s="25" t="n">
         <f aca="false">G19</f>
-        <v>644454.125425691</v>
+        <v>518786.283473444</v>
       </c>
       <c r="F20" s="25" t="n">
-        <f aca="false">(E20+D20)*Input!$B$16</f>
-        <v>11934.3612890792</v>
+        <f aca="false">E20*Input!$B$16</f>
+        <v>2593.93141736722</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF(B20&lt;Input!$B$6, E20+D20+F20, E20)</f>
-        <v>674954.432904588</v>
+        <v>539946.161080628</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2196,20 +2230,20 @@
         <v>57104.3496444382</v>
       </c>
       <c r="D21" s="25" t="n">
-        <f aca="false">C21*Input!$B$13</f>
+        <f aca="false">MIN(C21,Input!$B$43)*Input!$B$13</f>
         <v>18844.4353826646</v>
       </c>
       <c r="E21" s="25" t="n">
         <f aca="false">G20</f>
-        <v>674954.432904588</v>
+        <v>539946.161080628</v>
       </c>
       <c r="F21" s="25" t="n">
-        <f aca="false">(E21+D21)*Input!$B$16</f>
-        <v>12488.3796291705</v>
+        <f aca="false">E21*Input!$B$16</f>
+        <v>2699.73080540314</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF(B21&lt;Input!$B$6, E21+D21+F21, E21)</f>
-        <v>706287.247916423</v>
+        <v>561490.327268696</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2225,20 +2259,20 @@
         <v>57960.9148891048</v>
       </c>
       <c r="D22" s="25" t="n">
-        <f aca="false">C22*Input!$B$13</f>
+        <f aca="false">MIN(C22,Input!$B$43)*Input!$B$13</f>
         <v>19127.1019134046</v>
       </c>
       <c r="E22" s="25" t="n">
         <f aca="false">G21</f>
-        <v>706287.247916423</v>
+        <v>561490.327268696</v>
       </c>
       <c r="F22" s="25" t="n">
-        <f aca="false">(E22+D22)*Input!$B$16</f>
-        <v>13057.4582969369</v>
+        <f aca="false">E22*Input!$B$16</f>
+        <v>2807.45163634348</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF(B22&lt;Input!$B$6, E22+D22+F22, E22)</f>
-        <v>738471.808126764</v>
+        <v>583424.880818444</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2254,20 +2288,20 @@
         <v>58830.3286124414</v>
       </c>
       <c r="D23" s="25" t="n">
-        <f aca="false">C23*Input!$B$13</f>
+        <f aca="false">MIN(C23,Input!$B$43)*Input!$B$13</f>
         <v>19414.0084421057</v>
       </c>
       <c r="E23" s="25" t="n">
         <f aca="false">G22</f>
-        <v>738471.808126764</v>
+        <v>583424.880818444</v>
       </c>
       <c r="F23" s="25" t="n">
-        <f aca="false">(E23+D23)*Input!$B$16</f>
-        <v>13641.9446982397</v>
+        <f aca="false">E23*Input!$B$16</f>
+        <v>2917.12440409222</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF(B23&lt;Input!$B$6, E23+D23+F23, E23)</f>
-        <v>771527.76126711</v>
+        <v>605756.013664642</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2283,20 +2317,20 @@
         <v>59712.783541628</v>
       </c>
       <c r="D24" s="25" t="n">
-        <f aca="false">C24*Input!$B$13</f>
+        <f aca="false">MIN(C24,Input!$B$43)*Input!$B$13</f>
         <v>19705.2185687372</v>
       </c>
       <c r="E24" s="25" t="n">
         <f aca="false">G23</f>
-        <v>771527.76126711</v>
+        <v>605756.013664642</v>
       </c>
       <c r="F24" s="25" t="n">
-        <f aca="false">(E24+D24)*Input!$B$16</f>
-        <v>14242.1936370452</v>
+        <f aca="false">E24*Input!$B$16</f>
+        <v>3028.78006832321</v>
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">IF(B24&lt;Input!$B$6, E24+D24+F24, E24)</f>
-        <v>805475.173472892</v>
+        <v>628490.012301702</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2312,20 +2346,20 @@
         <v>60608.4752947524</v>
       </c>
       <c r="D25" s="25" t="n">
-        <f aca="false">C25*Input!$B$13</f>
+        <f aca="false">MIN(C25,Input!$B$43)*Input!$B$13</f>
         <v>20000.7968472683</v>
       </c>
       <c r="E25" s="25" t="n">
         <f aca="false">G24</f>
-        <v>805475.173472892</v>
+        <v>628490.012301702</v>
       </c>
       <c r="F25" s="25" t="n">
-        <f aca="false">(E25+D25)*Input!$B$16</f>
-        <v>14858.5674657629</v>
+        <f aca="false">E25*Input!$B$16</f>
+        <v>3142.45006150851</v>
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">IF(B25&lt;Input!$B$6, E25+D25+F25, E25)</f>
-        <v>840334.537785923</v>
+        <v>651633.259210479</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2341,20 +2375,20 @@
         <v>61517.6024241737</v>
       </c>
       <c r="D26" s="25" t="n">
-        <f aca="false">C26*Input!$B$13</f>
+        <f aca="false">MIN(C26,Input!$B$43)*Input!$B$13</f>
         <v>20300.8087999773</v>
       </c>
       <c r="E26" s="25" t="n">
         <f aca="false">G25</f>
-        <v>840334.537785923</v>
+        <v>651633.259210479</v>
       </c>
       <c r="F26" s="25" t="n">
-        <f aca="false">(E26+D26)*Input!$B$16</f>
-        <v>15491.4362385462</v>
+        <f aca="false">E26*Input!$B$16</f>
+        <v>3258.1662960524</v>
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">IF(B26&lt;Input!$B$6, E26+D26+F26, E26)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2370,20 +2404,20 @@
         <v>0</v>
       </c>
       <c r="D27" s="25" t="n">
-        <f aca="false">C27*Input!$B$13</f>
+        <f aca="false">MIN(C27,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">G26</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F27" s="25" t="n">
-        <f aca="false">(E27+D27)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E27*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G27" s="25" t="n">
         <f aca="false">IF(B27&lt;Input!$B$6, E27+D27+F27, E27)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2399,20 +2433,20 @@
         <v>0</v>
       </c>
       <c r="D28" s="25" t="n">
-        <f aca="false">C28*Input!$B$13</f>
+        <f aca="false">MIN(C28,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">G27</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F28" s="25" t="n">
-        <f aca="false">(E28+D28)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E28*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G28" s="25" t="n">
         <f aca="false">IF(B28&lt;Input!$B$6, E28+D28+F28, E28)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,20 +2462,20 @@
         <v>0</v>
       </c>
       <c r="D29" s="25" t="n">
-        <f aca="false">C29*Input!$B$13</f>
+        <f aca="false">MIN(C29,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">G28</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F29" s="25" t="n">
-        <f aca="false">(E29+D29)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E29*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G29" s="25" t="n">
         <f aca="false">IF(B29&lt;Input!$B$6, E29+D29+F29, E29)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,20 +2491,20 @@
         <v>0</v>
       </c>
       <c r="D30" s="25" t="n">
-        <f aca="false">C30*Input!$B$13</f>
+        <f aca="false">MIN(C30,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E30" s="25" t="n">
         <f aca="false">G29</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F30" s="25" t="n">
-        <f aca="false">(E30+D30)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E30*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G30" s="25" t="n">
         <f aca="false">IF(B30&lt;Input!$B$6, E30+D30+F30, E30)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2486,20 +2520,20 @@
         <v>0</v>
       </c>
       <c r="D31" s="25" t="n">
-        <f aca="false">C31*Input!$B$13</f>
+        <f aca="false">MIN(C31,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E31" s="25" t="n">
         <f aca="false">G30</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F31" s="25" t="n">
-        <f aca="false">(E31+D31)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E31*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G31" s="25" t="n">
         <f aca="false">IF(B31&lt;Input!$B$6, E31+D31+F31, E31)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2515,20 +2549,20 @@
         <v>0</v>
       </c>
       <c r="D32" s="25" t="n">
-        <f aca="false">C32*Input!$B$13</f>
+        <f aca="false">MIN(C32,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E32" s="25" t="n">
         <f aca="false">G31</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F32" s="25" t="n">
-        <f aca="false">(E32+D32)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E32*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G32" s="25" t="n">
         <f aca="false">IF(B32&lt;Input!$B$6, E32+D32+F32, E32)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2544,20 +2578,20 @@
         <v>0</v>
       </c>
       <c r="D33" s="25" t="n">
-        <f aca="false">C33*Input!$B$13</f>
+        <f aca="false">MIN(C33,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E33" s="25" t="n">
         <f aca="false">G32</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F33" s="25" t="n">
-        <f aca="false">(E33+D33)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E33*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G33" s="25" t="n">
         <f aca="false">IF(B33&lt;Input!$B$6, E33+D33+F33, E33)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2573,20 +2607,20 @@
         <v>0</v>
       </c>
       <c r="D34" s="25" t="n">
-        <f aca="false">C34*Input!$B$13</f>
+        <f aca="false">MIN(C34,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E34" s="25" t="n">
         <f aca="false">G33</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F34" s="25" t="n">
-        <f aca="false">(E34+D34)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E34*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G34" s="25" t="n">
         <f aca="false">IF(B34&lt;Input!$B$6, E34+D34+F34, E34)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2602,20 +2636,20 @@
         <v>0</v>
       </c>
       <c r="D35" s="25" t="n">
-        <f aca="false">C35*Input!$B$13</f>
+        <f aca="false">MIN(C35,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E35" s="25" t="n">
         <f aca="false">G34</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F35" s="25" t="n">
-        <f aca="false">(E35+D35)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E35*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G35" s="25" t="n">
         <f aca="false">IF(B35&lt;Input!$B$6, E35+D35+F35, E35)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2631,20 +2665,20 @@
         <v>0</v>
       </c>
       <c r="D36" s="25" t="n">
-        <f aca="false">C36*Input!$B$13</f>
+        <f aca="false">MIN(C36,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E36" s="25" t="n">
         <f aca="false">G35</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F36" s="25" t="n">
-        <f aca="false">(E36+D36)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E36*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G36" s="25" t="n">
         <f aca="false">IF(B36&lt;Input!$B$6, E36+D36+F36, E36)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2660,20 +2694,20 @@
         <v>0</v>
       </c>
       <c r="D37" s="25" t="n">
-        <f aca="false">C37*Input!$B$13</f>
+        <f aca="false">MIN(C37,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E37" s="25" t="n">
         <f aca="false">G36</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F37" s="25" t="n">
-        <f aca="false">(E37+D37)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E37*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G37" s="25" t="n">
         <f aca="false">IF(B37&lt;Input!$B$6, E37+D37+F37, E37)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2689,20 +2723,20 @@
         <v>0</v>
       </c>
       <c r="D38" s="25" t="n">
-        <f aca="false">C38*Input!$B$13</f>
+        <f aca="false">MIN(C38,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E38" s="25" t="n">
         <f aca="false">G37</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F38" s="25" t="n">
-        <f aca="false">(E38+D38)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E38*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G38" s="25" t="n">
         <f aca="false">IF(B38&lt;Input!$B$6, E38+D38+F38, E38)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2718,20 +2752,20 @@
         <v>0</v>
       </c>
       <c r="D39" s="25" t="n">
-        <f aca="false">C39*Input!$B$13</f>
+        <f aca="false">MIN(C39,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E39" s="25" t="n">
         <f aca="false">G38</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F39" s="25" t="n">
-        <f aca="false">(E39+D39)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E39*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G39" s="25" t="n">
         <f aca="false">IF(B39&lt;Input!$B$6, E39+D39+F39, E39)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2747,20 +2781,20 @@
         <v>0</v>
       </c>
       <c r="D40" s="25" t="n">
-        <f aca="false">C40*Input!$B$13</f>
+        <f aca="false">MIN(C40,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E40" s="25" t="n">
         <f aca="false">G39</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F40" s="25" t="n">
-        <f aca="false">(E40+D40)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E40*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G40" s="25" t="n">
         <f aca="false">IF(B40&lt;Input!$B$6, E40+D40+F40, E40)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2776,20 +2810,20 @@
         <v>0</v>
       </c>
       <c r="D41" s="25" t="n">
-        <f aca="false">C41*Input!$B$13</f>
+        <f aca="false">MIN(C41,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E41" s="25" t="n">
         <f aca="false">G40</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F41" s="25" t="n">
-        <f aca="false">(E41+D41)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E41*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G41" s="25" t="n">
         <f aca="false">IF(B41&lt;Input!$B$6, E41+D41+F41, E41)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2805,20 +2839,20 @@
         <v>0</v>
       </c>
       <c r="D42" s="25" t="n">
-        <f aca="false">C42*Input!$B$13</f>
+        <f aca="false">MIN(C42,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E42" s="25" t="n">
         <f aca="false">G41</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F42" s="25" t="n">
-        <f aca="false">(E42+D42)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E42*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G42" s="25" t="n">
         <f aca="false">IF(B42&lt;Input!$B$6, E42+D42+F42, E42)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2834,20 +2868,20 @@
         <v>0</v>
       </c>
       <c r="D43" s="25" t="n">
-        <f aca="false">C43*Input!$B$13</f>
+        <f aca="false">MIN(C43,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E43" s="25" t="n">
         <f aca="false">G42</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F43" s="25" t="n">
-        <f aca="false">(E43+D43)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E43*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G43" s="25" t="n">
         <f aca="false">IF(B43&lt;Input!$B$6, E43+D43+F43, E43)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2863,20 +2897,20 @@
         <v>0</v>
       </c>
       <c r="D44" s="25" t="n">
-        <f aca="false">C44*Input!$B$13</f>
+        <f aca="false">MIN(C44,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E44" s="25" t="n">
         <f aca="false">G43</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F44" s="25" t="n">
-        <f aca="false">(E44+D44)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E44*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G44" s="25" t="n">
         <f aca="false">IF(B44&lt;Input!$B$6, E44+D44+F44, E44)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2892,20 +2926,20 @@
         <v>0</v>
       </c>
       <c r="D45" s="25" t="n">
-        <f aca="false">C45*Input!$B$13</f>
+        <f aca="false">MIN(C45,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E45" s="25" t="n">
         <f aca="false">G44</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F45" s="25" t="n">
-        <f aca="false">(E45+D45)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E45*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G45" s="25" t="n">
         <f aca="false">IF(B45&lt;Input!$B$6, E45+D45+F45, E45)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2921,20 +2955,20 @@
         <v>0</v>
       </c>
       <c r="D46" s="25" t="n">
-        <f aca="false">C46*Input!$B$13</f>
+        <f aca="false">MIN(C46,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E46" s="25" t="n">
         <f aca="false">G45</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F46" s="25" t="n">
-        <f aca="false">(E46+D46)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E46*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G46" s="25" t="n">
         <f aca="false">IF(B46&lt;Input!$B$6, E46+D46+F46, E46)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2950,20 +2984,20 @@
         <v>0</v>
       </c>
       <c r="D47" s="25" t="n">
-        <f aca="false">C47*Input!$B$13</f>
+        <f aca="false">MIN(C47,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E47" s="25" t="n">
         <f aca="false">G46</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F47" s="25" t="n">
-        <f aca="false">(E47+D47)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E47*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G47" s="25" t="n">
         <f aca="false">IF(B47&lt;Input!$B$6, E47+D47+F47, E47)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2979,20 +3013,20 @@
         <v>0</v>
       </c>
       <c r="D48" s="25" t="n">
-        <f aca="false">C48*Input!$B$13</f>
+        <f aca="false">MIN(C48,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E48" s="25" t="n">
         <f aca="false">G47</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F48" s="25" t="n">
-        <f aca="false">(E48+D48)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E48*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G48" s="25" t="n">
         <f aca="false">IF(B48&lt;Input!$B$6, E48+D48+F48, E48)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3008,20 +3042,20 @@
         <v>0</v>
       </c>
       <c r="D49" s="25" t="n">
-        <f aca="false">C49*Input!$B$13</f>
+        <f aca="false">MIN(C49,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E49" s="25" t="n">
         <f aca="false">G48</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F49" s="25" t="n">
-        <f aca="false">(E49+D49)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E49*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G49" s="25" t="n">
         <f aca="false">IF(B49&lt;Input!$B$6, E49+D49+F49, E49)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3037,20 +3071,20 @@
         <v>0</v>
       </c>
       <c r="D50" s="25" t="n">
-        <f aca="false">C50*Input!$B$13</f>
+        <f aca="false">MIN(C50,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E50" s="25" t="n">
         <f aca="false">G49</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F50" s="25" t="n">
-        <f aca="false">(E50+D50)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E50*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G50" s="25" t="n">
         <f aca="false">IF(B50&lt;Input!$B$6, E50+D50+F50, E50)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3066,20 +3100,20 @@
         <v>0</v>
       </c>
       <c r="D51" s="25" t="n">
-        <f aca="false">C51*Input!$B$13</f>
+        <f aca="false">MIN(C51,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E51" s="25" t="n">
         <f aca="false">G50</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F51" s="25" t="n">
-        <f aca="false">(E51+D51)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E51*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G51" s="25" t="n">
         <f aca="false">IF(B51&lt;Input!$B$6, E51+D51+F51, E51)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3095,20 +3129,20 @@
         <v>0</v>
       </c>
       <c r="D52" s="25" t="n">
-        <f aca="false">C52*Input!$B$13</f>
+        <f aca="false">MIN(C52,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E52" s="25" t="n">
         <f aca="false">G51</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F52" s="25" t="n">
-        <f aca="false">(E52+D52)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E52*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G52" s="25" t="n">
         <f aca="false">IF(B52&lt;Input!$B$6, E52+D52+F52, E52)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3124,20 +3158,20 @@
         <v>0</v>
       </c>
       <c r="D53" s="25" t="n">
-        <f aca="false">C53*Input!$B$13</f>
+        <f aca="false">MIN(C53,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E53" s="25" t="n">
         <f aca="false">G52</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F53" s="25" t="n">
-        <f aca="false">(E53+D53)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E53*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G53" s="25" t="n">
         <f aca="false">IF(B53&lt;Input!$B$6, E53+D53+F53, E53)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3153,25 +3187,25 @@
         <v>0</v>
       </c>
       <c r="D54" s="25" t="n">
-        <f aca="false">C54*Input!$B$13</f>
+        <f aca="false">MIN(C54,Input!$B$43)*Input!$B$13</f>
         <v>0</v>
       </c>
       <c r="E54" s="25" t="n">
         <f aca="false">G53</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
       <c r="F54" s="25" t="n">
-        <f aca="false">(E54+D54)*Input!$B$16</f>
-        <v>15770.28209084</v>
+        <f aca="false">E54*Input!$B$16</f>
+        <v>3375.96117153254</v>
       </c>
       <c r="G54" s="25" t="n">
         <f aca="false">IF(B54&lt;Input!$B$6, E54+D54+F54, E54)</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3182,16 +3216,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(G5:G54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
-        <v>876126.782824447</v>
+        <v>675192.234306509</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B59" s="27" t="n">
         <f aca="false">VLOOKUP(Input!$B$6, Coefficienti!A5:C19, 3, FALSE())</f>
@@ -3200,7 +3234,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B60" s="28" t="n">
         <f aca="false">Input!$B$40</f>
@@ -3209,79 +3243,79 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58*B60</f>
-        <v>40234.7518698099</v>
+        <v>31007.1470754117</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61/13</f>
-        <v>3094.9809130623</v>
+        <v>2385.16515964705</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">IF(B61&lt;=28000, B61*0.23, IF(B61&lt;=50000, 28000*0.23 + (B61-28000)*0.33, 28000*0.23 + 22000*0.33 + (B61-50000)*0.43))</f>
-        <v>10477.4681170373</v>
+        <v>7432.35853488586</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">IF(B61&lt;=8500, 1955, IF(B61&lt;=28000, 700 + 1255*(28000-B61)/19500, IF(B61&lt;=50000, 700*(50000-B61)/22000, 0)))</f>
-        <v>310.71244050605</v>
+        <v>604.318047600537</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B65" s="15" t="n">
-        <f aca="false">B61*0.02</f>
-        <v>804.695037396197</v>
+        <f aca="false">IF(B63-B64&gt;0,B61*0.02,0)</f>
+        <v>620.142941508234</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B66" s="29" t="n">
         <f aca="false">B61-MAX(0,B63-B64)-B65</f>
-        <v>29263.3011558825</v>
+        <v>23558.9636466181</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B67" s="29" t="n">
         <f aca="false">B66/13</f>
-        <v>2251.02316583711</v>
+        <v>1812.22797281678</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B68" s="11" t="n">
         <f aca="false">IFERROR(B61/INDEX(C5:C54, MATCH(Input!$B$6-1, B5:B54, 0)), 0)</f>
-        <v>0.654036410463217</v>
+        <v>0.504036988659156</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3321,7 +3355,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3333,7 +3367,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3345,28 +3379,28 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5021,7 +5055,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5033,7 +5067,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(H5:H54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
@@ -5042,7 +5076,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B59" s="30" t="n">
         <f aca="false">Input!$B$38</f>
@@ -5051,7 +5085,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B60" s="15" t="n">
         <f aca="false">B58*B59</f>
@@ -5060,7 +5094,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58-B60</f>
@@ -5069,7 +5103,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61*0.055</f>
@@ -5078,7 +5112,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">B62/13</f>
@@ -5087,7 +5121,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">SUM(E5:E54)*Input!$B$37</f>
@@ -5096,12 +5130,12 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -5113,7 +5147,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -5125,7 +5159,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -5137,7 +5171,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -5149,7 +5183,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -5194,7 +5228,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5202,7 +5236,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5210,21 +5244,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>0.005</v>
@@ -5239,22 +5273,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B6" s="31" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C6" s="32" t="n">
         <f aca="false">Input!$B$16</f>
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="D6" s="31" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>0.025</v>
@@ -5301,165 +5335,182 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B11" s="26" t="n">
-        <f aca="false">Pubblica!B61*(1-B8)^(Input!$B$36/2)/(1-Input!$B$18)^(Input!$B$36/2)</f>
-        <v>38468.244202918</v>
+        <f aca="false">(Pubblica!$E$5*(1+B6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+B6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-B8)^(Input!$B$36/2)</f>
+        <v>25820.1521293217</v>
       </c>
       <c r="C11" s="26" t="n">
-        <f aca="false">Pubblica!B61</f>
-        <v>40234.7518698099</v>
+        <f aca="false">(Pubblica!$E$5*(1+C6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+C5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+C5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+C6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-C8)^(Input!$B$36/2)</f>
+        <v>31007.1470754117</v>
       </c>
       <c r="D11" s="26" t="n">
-        <f aca="false">Pubblica!B61*(1-D8)^(Input!$B$36/2)/(1-Input!$B$18)^(Input!$B$36/2)</f>
-        <v>41607.6796645145</v>
+        <f aca="false">(Pubblica!$E$5*(1+D6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+D5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+D5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+D6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-D8)^(Input!$B$36/2)</f>
+        <v>36820.8382399688</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B12" s="26" t="n">
-        <f aca="false">Pubblica!B66*B11/Pubblica!B61</f>
-        <v>27978.4952741984</v>
+        <f aca="false">B11-MAX(0,IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0))))-IF(IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0)))&gt;0,B11*0.02,0)</f>
+        <v>20205.4068702067</v>
       </c>
       <c r="C12" s="26" t="n">
-        <f aca="false">Pubblica!B66*C11/Pubblica!B61</f>
-        <v>29263.3011558825</v>
+        <f aca="false">C11-MAX(0,IF(C11&lt;=28000,C11*0.23,IF(C11&lt;=50000,6440+(C11-28000)*0.33,13700+(C11-50000)*0.43))-IF(C11&lt;=8500,1955,IF(C11&lt;=28000,700+1255*(28000-C11)/19500,IF(C11&lt;=50000,700*(50000-C11)/22000,0))))-IF(IF(C11&lt;=28000,C11*0.23,IF(C11&lt;=50000,6440+(C11-28000)*0.33,13700+(C11-50000)*0.43))-IF(C11&lt;=8500,1955,IF(C11&lt;=28000,700+1255*(28000-C11)/19500,IF(C11&lt;=50000,700*(50000-C11)/22000,0)))&gt;0,C11*0.02,0)</f>
+        <v>23558.9636466181</v>
       </c>
       <c r="D12" s="26" t="n">
-        <f aca="false">Pubblica!B66*D11/Pubblica!B61</f>
-        <v>30261.8508586798</v>
+        <f aca="false">D11-MAX(0,IF(D11&lt;=28000,D11*0.23,IF(D11&lt;=50000,6440+(D11-28000)*0.33,13700+(D11-50000)*0.43))-IF(D11&lt;=8500,1955,IF(D11&lt;=28000,700+1255*(28000-D11)/19500,IF(D11&lt;=50000,700*(50000-D11)/22000,0))))-IF(IF(D11&lt;=28000,D11*0.23,IF(D11&lt;=50000,6440+(D11-28000)*0.33,13700+(D11-50000)*0.43))-IF(D11&lt;=8500,1955,IF(D11&lt;=28000,700+1255*(28000-D11)/19500,IF(D11&lt;=50000,700*(50000-D11)/22000,0)))&gt;0,D11*0.02,0)</f>
+        <v>27152.8818210716</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B13" s="26" t="n">
-        <f aca="false">Complementare!B58*0.85</f>
-        <v>198169.842896191</v>
+        <f aca="false">(Input!$B$22+Input!$B$25)*(1+B9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+B9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <v>194700.656586312</v>
       </c>
       <c r="C13" s="26" t="n">
-        <f aca="false">Complementare!B58</f>
+        <f aca="false">(Input!$B$22+Input!$B$25)*(1+C9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+C9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
         <v>233140.991642577</v>
       </c>
       <c r="D13" s="26" t="n">
-        <f aca="false">Complementare!B58*1.18</f>
-        <v>275106.370138241</v>
+        <f aca="false">(Input!$B$22+Input!$B$25)*(1+D9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+D9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <v>279432.685515174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B14" s="26" t="n">
-        <f aca="false">Complementare!B61*0.85</f>
-        <v>175578.480806025</v>
+        <f aca="false">B13*(1-Input!$B$38)</f>
+        <v>172504.781735473</v>
       </c>
       <c r="C14" s="26" t="n">
-        <f aca="false">Complementare!B61</f>
-        <v>206562.918595324</v>
+        <f aca="false">C13*(1-Input!$B$38)</f>
+        <v>206562.918595323</v>
       </c>
       <c r="D14" s="26" t="n">
-        <f aca="false">Complementare!B61*1.18</f>
-        <v>243744.243942482</v>
+        <f aca="false">D13*(1-Input!$B$38)</f>
+        <v>247577.359366444</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B15" s="26" t="n">
-        <f aca="false">Complementare!B62*0.85</f>
-        <v>9656.81644433137</v>
+        <f aca="false">B14*0.055</f>
+        <v>9487.762995451</v>
       </c>
       <c r="C15" s="26" t="n">
-        <f aca="false">Complementare!B62</f>
+        <f aca="false">C14*0.055</f>
         <v>11360.9605227428</v>
       </c>
       <c r="D15" s="26" t="n">
-        <f aca="false">Complementare!B62*1.18</f>
-        <v>13405.9334168365</v>
+        <f aca="false">D14*0.055</f>
+        <v>13616.7547651544</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
-        <v>37635.3117185298</v>
+        <v>29693.1698656577</v>
       </c>
       <c r="C17" s="25" t="n">
         <f aca="false">C12+C15</f>
-        <v>40624.2616786253</v>
+        <v>34919.9241693609</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">D12+D15</f>
-        <v>43667.7842755163</v>
+        <v>40769.636586226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B18" s="25" t="n">
-        <f aca="false">Input!$B$39*(1+B7)^Input!$B$36</f>
-        <v>40284.7707033742</v>
+        <f aca="false">Input!$B$39</f>
+        <v>23400</v>
       </c>
       <c r="C18" s="25" t="n">
-        <f aca="false">Input!$B$39*(1+C7)^Input!$B$36</f>
-        <v>36175.9242961556</v>
+        <f aca="false">Input!$B$39</f>
+        <v>23400</v>
       </c>
       <c r="D18" s="25" t="n">
-        <f aca="false">Input!$B$39*(1+D7)^Input!$B$36</f>
-        <v>32468.9905594789</v>
+        <f aca="false">Input!$B$39</f>
+        <v>23400</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
-        <v>2649.45898484445</v>
+        <v>-6293.1698656577</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C18-C17</f>
-        <v>-4448.33738246965</v>
+        <v>-11519.9241693609</v>
       </c>
       <c r="D19" s="33" t="n">
         <f aca="false">D18-D17</f>
-        <v>-11198.7937160374</v>
+        <v>-17369.636586226</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
-        <v>0.0657682528306543</v>
+        <v>-0.268938883147765</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IFERROR(C19/C18, 0)</f>
-        <v>-0.122964028397814</v>
+        <v>-0.49230445168209</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(D19/D18, 0)</f>
-        <v>-0.344907356929459</v>
+        <v>-0.742292161804531</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="33" t="n">
+        <f aca="false">B19*(1+B7)^Input!$B$36</f>
+        <v>-10834.1412408293</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <f aca="false">C19*(1+C7)^Input!$B$36</f>
+        <v>-17809.5685747117</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <f aca="false">D19*(1+D7)^Input!$B$36</f>
+        <v>-24101.4771940065</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -5467,7 +5518,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -5475,7 +5526,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -5483,7 +5534,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -5491,7 +5542,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -5499,7 +5550,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="179">
   <si>
     <t xml:space="preserve">Proiezione pensionistica — Parametri di input</t>
   </si>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">Inflazione attesa</t>
   </si>
   <si>
-    <t xml:space="preserve">target BCE 2%; serve solo alla vista nominale degli Scenari</t>
+    <t xml:space="preserve">target BCE 2%; serve al TFR in azienda, alla tassa del fondo in uscita e alla riga 21 degli Scenari</t>
   </si>
   <si>
     <t xml:space="preserve">Decadimento coefficiente / biennio</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Contributo volontario annuo</t>
   </si>
   <si>
-    <t xml:space="preserve">€/anno (max €5.300 deducibili)</t>
+    <t xml:space="preserve">€/anno; deduce nello spazio lasciato da datore e contributo dovuto (plafond B44)</t>
   </si>
   <si>
     <t xml:space="preserve">Contributo datore (% RAL)</t>
@@ -212,6 +212,33 @@
     <t xml:space="preserve">Circ. INPS 6/2026; oltre non si versano contributi (iscritti dal 1996)</t>
   </si>
   <si>
+    <t xml:space="preserve">Plafond deducibilità fondo pensione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art. 8 c. 4 D.Lgs. 252/2005: lavoratore + datore, TFR escluso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONDO PENSIONE E TFR — DETTAGLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributo dovuto lavoratore (% RAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimo da CCNL per avere il contributo del datore (es. 1%); 0 se già nel volontario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anni di servizio già maturati (TFR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per la tassazione separata del TFR in azienda (reddito di riferimento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivalutazione netta reale del TFR in azienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,5% + 75% dell'inflazione, meno l'imposta del 17%, in euro di oggi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coefficienti di trasformazione — biennio 2025-2026</t>
   </si>
   <si>
@@ -317,13 +344,13 @@
     <t xml:space="preserve">Proiezione previdenza complementare</t>
   </si>
   <si>
-    <t xml:space="preserve">Proiezione anno per anno del montante del fondo pensione (TFR + volontari + datore + rendimenti).</t>
+    <t xml:space="preserve">Proiezione anno per anno del fondo pensione in euro di oggi (TFR se conferito + contributi del lavoratore e del datore + rendimenti), con la quota deducibile e il confronto del TFR in azienda.</t>
   </si>
   <si>
     <t xml:space="preserve">TFR (6,91%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Contrib. volontario</t>
+    <t xml:space="preserve">Contrib. lavoratore</t>
   </si>
   <si>
     <t xml:space="preserve">Contrib. datore</t>
@@ -332,13 +359,34 @@
     <t xml:space="preserve">Rendimento</t>
   </si>
   <si>
+    <t xml:space="preserve">Quota deducibile volontario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non dedotto (da comunicare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base tassabile in uscita (€ oggi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda: quota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda: saldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR nel fondo: montante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR: base tassabile (€ oggi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montante fondo finale (lordo)</t>
   </si>
   <si>
     <t xml:space="preserve">Aliquota fondo finale (da Input)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tassazione finale (montante × aliquota)</t>
+    <t xml:space="preserve">Tassazione finale (TFR e contributi dedotti × aliquota)</t>
   </si>
   <si>
     <t xml:space="preserve">Prestazione fondo NETTA</t>
@@ -350,25 +398,79 @@
     <t xml:space="preserve">Rendita lorda mensile (13 mensilità)</t>
   </si>
   <si>
-    <t xml:space="preserve">Risparmio IRPEF cumulato dalle deduzioni</t>
+    <t xml:space="preserve">Risparmio IRPEF cumulato sui volontari (quota deducibile)</t>
   </si>
   <si>
     <t xml:space="preserve">NOTE:</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Contributo volontario costante in termini reali (in nominale cresce con inflazione).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Rendimento netto comparto è al netto della tassa annua 20% (12,5% titoli Stato).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Aliquota fondo finale: 15% → 9% (riduzione 0,30% per ogni anno partecipazione oltre il 15°).</t>
+    <t xml:space="preserve">1. Contributo volontario costante in termini reali: tutto il foglio è in euro di oggi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Rendimento netto del comparto (reale) al netto della tassa annua 20% (12,5% titoli di Stato).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Aliquota finale 15% → 9% sui soli TFR e contributi dedotti: rendimenti già tassati e non dedotti comunicati sono esclusi (art. 11 c. 6 D.Lgs. 252/2005). Il montante già accumulato è trattato come dedotto.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Tasso conversione rendita 5,5%: vitalizia a 67 anni senza reversibilità.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Risparmio IRPEF in valore nominale (non scontato). Vale 0 se il contributo volontario è 0.</t>
+    <t xml:space="preserve">5. Risparmio IRPEF nominale non scontato, solo sulla quota deducibile dei volontari (colonna I).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAFOND DI DEDUCIBILITÀ (art. 8 c. 4 D.Lgs. 252/2005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spazio deducibile residuo per i volontari (primo anno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non dedotto da comunicare al fondo (somma degli anni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo spazio residuo è un tetto fiscale, non un importo consigliato: dipende da liquidità e alternative. Non è consulenza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciò che supera il plafond va comunicato al fondo entro il 31/12 dell'anno dopo: senza comunicazione in uscita è tassato di nuovo (9-15% del non dedotto).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFRONTO TFR: IN AZIENDA O NEL FONDO (tutto il TFR, saldo compreso; € di oggi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda al pensionamento (lordo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base della tassazione (quote, senza rivalutazioni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddito di riferimento (base × 12 / anni di servizio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aliquota media della tassazione separata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda NETTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR nel fondo al pensionamento (lordo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposta in uscita sul TFR nel fondo (15→9% sulle quote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR nel fondo NETTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vantaggio netto del fondo sul TFR (fondo − azienda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR), poi riliquidata sui 5 anni precedenti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondo: rendimento del comparto (Input B28) e 15%→9% sulle sole quote di TFR, non sui rendimenti già tassati (art. 11 c. 6 D.Lgs. 252/2005). Il conferimento è irrevocabile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrazione con le ipotesi del foglio: rischio di mercato e costi del fondo restano all'iscritto. Non è consulenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Confronto scenari: conservativo / base / ottimistico</t>
@@ -413,6 +515,9 @@
     <t xml:space="preserve">Rendita fondo annua (stima)</t>
   </si>
   <si>
+    <t xml:space="preserve">TFR in azienda netto (capitale, fuori dalla rendita)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reddito pensione totale netto annuo</t>
   </si>
   <si>
@@ -443,10 +548,19 @@
     <t xml:space="preserve">  ricalcolano INPS e fondo con la propria crescita RAL, PIL reale, decadimento e rendimento.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Fondo: stesso montante del foglio Complementare con il rendimento della colonna (B9:D9).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• L'inflazione (riga 7) serve solo alla riga 21, che riporta il gap in € del pensionamento.</t>
+    <t xml:space="preserve">• Fondo: montante, tassa in uscita (solo TFR e dedotti) e rendita col rendimento della colonna; il TFR in azienda (riga 16) è capitale, fuori dal gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• L'inflazione (riga 7) entra dove la legge ragiona in nominale (TFR in azienda, base del fondo in uscita) e nella riga 21.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCOLI DI SUPPORTO — TFR in azienda per scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda lordo al pensionamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base della tassazione separata</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1131,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -1386,8 +1500,60 @@
         <v>61</v>
       </c>
     </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" s="11" t="n">
+        <f aca="false">(1+(0.015+0.75*Input!$B$17)*(1-0.17))/(1+Input!$B$17)-1</f>
+        <v>0.0048039215686273</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -1398,6 +1564,7 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1424,27 +1591,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1614,12 +1781,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -1627,7 +1794,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -1635,7 +1802,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -1643,7 +1810,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -1651,7 +1818,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -1659,7 +1826,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -1667,7 +1834,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -1710,7 +1877,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1721,7 +1888,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1732,25 +1899,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3205,7 +3372,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3216,7 +3383,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(G5:G54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
@@ -3225,7 +3392,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B59" s="27" t="n">
         <f aca="false">VLOOKUP(Input!$B$6, Coefficienti!A5:C19, 3, FALSE())</f>
@@ -3234,7 +3401,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B60" s="28" t="n">
         <f aca="false">Input!$B$40</f>
@@ -3243,7 +3410,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58*B60</f>
@@ -3252,7 +3419,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61/13</f>
@@ -3261,7 +3428,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">IF(B61&lt;=28000, B61*0.23, IF(B61&lt;=50000, 28000*0.23 + (B61-28000)*0.33, 28000*0.23 + 22000*0.33 + (B61-50000)*0.43))</f>
@@ -3270,7 +3437,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">IF(B61&lt;=8500, 1955, IF(B61&lt;=28000, 700 + 1255*(28000-B61)/19500, IF(B61&lt;=50000, 700*(50000-B61)/22000, 0)))</f>
@@ -3279,7 +3446,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B65" s="15" t="n">
         <f aca="false">IF(B63-B64&gt;0,B61*0.02,0)</f>
@@ -3288,7 +3455,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B66" s="29" t="n">
         <f aca="false">B61-MAX(0,B63-B64)-B65</f>
@@ -3297,7 +3464,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B67" s="29" t="n">
         <f aca="false">B66/13</f>
@@ -3306,7 +3473,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B68" s="11" t="n">
         <f aca="false">IFERROR(B61/INDEX(C5:C54, MATCH(Input!$B$6-1, B5:B54, 0)), 0)</f>
@@ -3315,7 +3482,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3346,16 +3513,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3367,7 +3535,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3379,28 +3547,49 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3420,7 +3609,7 @@
         <v>3109.5</v>
       </c>
       <c r="E5" s="25" t="n">
-        <f aca="false">IF(B5&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$26+C5*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F5" s="25" t="n">
@@ -3428,12 +3617,40 @@
         <v>675</v>
       </c>
       <c r="G5" s="25" t="n">
-        <f aca="false">(Input!$B$22+Input!$B$25)*Input!$B$28</f>
+        <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*Input!$B$28</f>
         <v>455</v>
       </c>
       <c r="H5" s="25" t="n">
-        <f aca="false">Input!$B$22+Input!$B$25+D5+E5+F5+G5</f>
+        <f aca="false">Input!$B$22*Input!$B$21+Input!$B$25+D5+E5+F5+G5</f>
         <v>19239.5</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E5+F5)-MIN(Input!$B$44,F5+C5*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <f aca="false">E5+F5-MIN(Input!$B$44,E5+F5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <f aca="false">(D5+MIN(Input!$B$44,E5+F5))*(1+Input!$B$17)^(A5-Input!$B$36)</f>
+        <v>3741.64040404033</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <f aca="false">C5*0.0691</f>
+        <v>3109.5</v>
+      </c>
+      <c r="M5" s="25" t="n">
+        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*(1+Input!$B$49)+L5,Input!$B$22)</f>
+        <v>11147.931372549</v>
+      </c>
+      <c r="N5" s="25" t="n">
+        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*(1+Input!$B$28)+L5,Input!$B$22)</f>
+        <v>11389.5</v>
+      </c>
+      <c r="O5" s="25" t="n">
+        <f aca="false">L5*(1+Input!$B$17)^(A5-Input!$B$36)</f>
+        <v>2011.34598260237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3453,7 +3670,7 @@
         <v>3156.1425</v>
       </c>
       <c r="E6" s="25" t="n">
-        <f aca="false">IF(B6&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B6&lt;Input!$B$6,Input!$B$26+C6*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F6" s="25" t="n">
@@ -3468,6 +3685,34 @@
         <f aca="false">H5+D6+E6+F6+G6</f>
         <v>25754.15</v>
       </c>
+      <c r="I6" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E6+F6)-MIN(Input!$B$44,F6+C6*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <f aca="false">E6+F6-MIN(Input!$B$44,E6+F6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <f aca="false">(D6+MIN(Input!$B$44,E6+F6))*(1+Input!$B$17)^(A6-Input!$B$36)</f>
+        <v>3853.92703579977</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <f aca="false">C6*0.0691</f>
+        <v>3156.1425</v>
+      </c>
+      <c r="M6" s="25" t="n">
+        <f aca="false">IF(B6&lt;Input!$B$6,M5*(1+Input!$B$49)+L6,M5)</f>
+        <v>14357.6276605152</v>
+      </c>
+      <c r="N6" s="25" t="n">
+        <f aca="false">IF(B6&lt;Input!$B$6,N5*(1+Input!$B$28)+L6,N5)</f>
+        <v>14944.275</v>
+      </c>
+      <c r="O6" s="25" t="n">
+        <f aca="false">L6*(1+Input!$B$17)^(A6-Input!$B$36)</f>
+        <v>2082.34649578823</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
@@ -3486,7 +3731,7 @@
         <v>3203.4846375</v>
       </c>
       <c r="E7" s="25" t="n">
-        <f aca="false">IF(B7&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B7&lt;Input!$B$6,Input!$B$26+C7*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F7" s="25" t="n">
@@ -3501,6 +3746,34 @@
         <f aca="false">H6+D7+E7+F7+G7</f>
         <v>32554.4317625</v>
       </c>
+      <c r="I7" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E7+F7)-MIN(Input!$B$44,F7+C7*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <f aca="false">E7+F7-MIN(Input!$B$44,E7+F7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <f aca="false">(D7+MIN(Input!$B$44,E7+F7))*(1+Input!$B$17)^(A7-Input!$B$36)</f>
+        <v>3969.78152017026</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <f aca="false">C7*0.0691</f>
+        <v>3203.4846375</v>
+      </c>
+      <c r="M7" s="25" t="n">
+        <f aca="false">IF(B7&lt;Input!$B$6,M6*(1+Input!$B$49)+L7,M6)</f>
+        <v>17630.0852152079</v>
+      </c>
+      <c r="N7" s="25" t="n">
+        <f aca="false">IF(B7&lt;Input!$B$6,N6*(1+Input!$B$28)+L7,N6)</f>
+        <v>18670.8092625</v>
+      </c>
+      <c r="O7" s="25" t="n">
+        <f aca="false">L7*(1+Input!$B$17)^(A7-Input!$B$36)</f>
+        <v>2155.85332708956</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
@@ -3519,7 +3792,7 @@
         <v>3251.5369070625</v>
       </c>
       <c r="E8" s="25" t="n">
-        <f aca="false">IF(B8&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B8&lt;Input!$B$6,Input!$B$26+C8*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F8" s="25" t="n">
@@ -3534,6 +3807,34 @@
         <f aca="false">H7+D8+E8+F8+G8</f>
         <v>39651.206684375</v>
       </c>
+      <c r="I8" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E8+F8)-MIN(Input!$B$44,F8+C8*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <f aca="false">E8+F8-MIN(Input!$B$44,E8+F8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <f aca="false">(D8+MIN(Input!$B$44,E8+F8))*(1+Input!$B$17)^(A8-Input!$B$36)</f>
+        <v>4089.32188503917</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <f aca="false">C8*0.0691</f>
+        <v>3251.5369070625</v>
+      </c>
+      <c r="M8" s="25" t="n">
+        <f aca="false">IF(B8&lt;Input!$B$6,M7*(1+Input!$B$49)+L8,M7)</f>
+        <v>20966.3156688924</v>
+      </c>
+      <c r="N8" s="25" t="n">
+        <f aca="false">IF(B8&lt;Input!$B$6,N7*(1+Input!$B$28)+L8,N7)</f>
+        <v>22575.82449375</v>
+      </c>
+      <c r="O8" s="25" t="n">
+        <f aca="false">L8*(1+Input!$B$17)^(A8-Input!$B$36)</f>
+        <v>2231.95494953582</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="n">
@@ -3552,7 +3853,7 @@
         <v>3300.30996066844</v>
       </c>
       <c r="E9" s="25" t="n">
-        <f aca="false">IF(B9&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B9&lt;Input!$B$6,Input!$B$26+C9*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F9" s="25" t="n">
@@ -3567,6 +3868,34 @@
         <f aca="false">H8+D9+E9+F9+G9</f>
         <v>47055.7292756684</v>
       </c>
+      <c r="I9" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E9+F9)-MIN(Input!$B$44,F9+C9*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <f aca="false">E9+F9-MIN(Input!$B$44,E9+F9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <f aca="false">(D9+MIN(Input!$B$44,E9+F9))*(1+Input!$B$17)^(A9-Input!$B$36)</f>
+        <v>4212.67016633208</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <f aca="false">C9*0.0691</f>
+        <v>3300.30996066844</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <f aca="false">IF(B9&lt;Input!$B$6,M8*(1+Input!$B$49)+L9,M8)</f>
+        <v>24367.3461656173</v>
+      </c>
+      <c r="N9" s="25" t="n">
+        <f aca="false">IF(B9&lt;Input!$B$6,N8*(1+Input!$B$28)+L9,N8)</f>
+        <v>26666.2883116997</v>
+      </c>
+      <c r="O9" s="25" t="n">
+        <f aca="false">L9*(1+Input!$B$17)^(A9-Input!$B$36)</f>
+        <v>2310.74295925443</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="n">
@@ -3585,7 +3914,7 @@
         <v>3349.81461007846</v>
       </c>
       <c r="E10" s="25" t="n">
-        <f aca="false">IF(B10&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B10&lt;Input!$B$6,Input!$B$26+C10*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F10" s="25" t="n">
@@ -3600,6 +3929,34 @@
         <f aca="false">H9+D10+E10+F10+G10</f>
         <v>54779.6611130172</v>
       </c>
+      <c r="I10" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E10+F10)-MIN(Input!$B$44,F10+C10*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <f aca="false">E10+F10-MIN(Input!$B$44,E10+F10)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="25" t="n">
+        <f aca="false">(D10+MIN(Input!$B$44,E10+F10))*(1+Input!$B$17)^(A10-Input!$B$36)</f>
+        <v>4339.95254632966</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <f aca="false">C10*0.0691</f>
+        <v>3349.81461007846</v>
+      </c>
+      <c r="M10" s="25" t="n">
+        <f aca="false">IF(B10&lt;Input!$B$6,M9*(1+Input!$B$49)+L10,M9)</f>
+        <v>27834.219595511</v>
+      </c>
+      <c r="N10" s="25" t="n">
+        <f aca="false">IF(B10&lt;Input!$B$6,N9*(1+Input!$B$28)+L10,N9)</f>
+        <v>30949.4230126876</v>
+      </c>
+      <c r="O10" s="25" t="n">
+        <f aca="false">L10*(1+Input!$B$17)^(A10-Input!$B$36)</f>
+        <v>2392.31218571611</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
@@ -3618,7 +3975,7 @@
         <v>3400.06182922964</v>
       </c>
       <c r="E11" s="25" t="n">
-        <f aca="false">IF(B11&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B11&lt;Input!$B$6,Input!$B$26+C11*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F11" s="25" t="n">
@@ -3633,6 +3990,34 @@
         <f aca="false">H10+D11+E11+F11+G11</f>
         <v>62835.0852843638</v>
       </c>
+      <c r="I11" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E11+F11)-MIN(Input!$B$44,F11+C11*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <f aca="false">E11+F11-MIN(Input!$B$44,E11+F11)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="25" t="n">
+        <f aca="false">(D11+MIN(Input!$B$44,E11+F11))*(1+Input!$B$17)^(A11-Input!$B$36)</f>
+        <v>4471.29949680367</v>
+      </c>
+      <c r="L11" s="25" t="n">
+        <f aca="false">C11*0.0691</f>
+        <v>3400.06182922964</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <f aca="false">IF(B11&lt;Input!$B$6,M10*(1+Input!$B$49)+L11,M10)</f>
+        <v>31367.9948326014</v>
+      </c>
+      <c r="N11" s="25" t="n">
+        <f aca="false">IF(B11&lt;Input!$B$6,N10*(1+Input!$B$28)+L11,N10)</f>
+        <v>35432.7146473613</v>
+      </c>
+      <c r="O11" s="25" t="n">
+        <f aca="false">L11*(1+Input!$B$17)^(A11-Input!$B$36)</f>
+        <v>2476.76080587189</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
@@ -3651,7 +4036,7 @@
         <v>3451.06275666808</v>
       </c>
       <c r="E12" s="25" t="n">
-        <f aca="false">IF(B12&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B12&lt;Input!$B$6,Input!$B$26+C12*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F12" s="25" t="n">
@@ -3666,6 +4051,34 @@
         <f aca="false">H11+D12+E12+F12+G12</f>
         <v>71234.5213421933</v>
       </c>
+      <c r="I12" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E12+F12)-MIN(Input!$B$44,F12+C12*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <f aca="false">E12+F12-MIN(Input!$B$44,E12+F12)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="25" t="n">
+        <f aca="false">(D12+MIN(Input!$B$44,E12+F12))*(1+Input!$B$17)^(A12-Input!$B$36)</f>
+        <v>4606.84592714118</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <f aca="false">C12*0.0691</f>
+        <v>3451.06275666808</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <f aca="false">IF(B12&lt;Input!$B$6,M11*(1+Input!$B$49)+L12,M11)</f>
+        <v>34969.7469762104</v>
+      </c>
+      <c r="N12" s="25" t="n">
+        <f aca="false">IF(B12&lt;Input!$B$6,N11*(1+Input!$B$28)+L12,N11)</f>
+        <v>40123.9224166871</v>
+      </c>
+      <c r="O12" s="25" t="n">
+        <f aca="false">L12*(1+Input!$B$17)^(A12-Input!$B$36)</f>
+        <v>2564.19046231917</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
@@ -3684,7 +4097,7 @@
         <v>3502.8286980181</v>
       </c>
       <c r="E13" s="25" t="n">
-        <f aca="false">IF(B13&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B13&lt;Input!$B$6,Input!$B$26+C13*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F13" s="25" t="n">
@@ -3699,6 +4112,34 @@
         <f aca="false">H12+D13+E13+F13+G13</f>
         <v>79990.94078314</v>
       </c>
+      <c r="I13" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E13+F13)-MIN(Input!$B$44,F13+C13*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <f aca="false">E13+F13-MIN(Input!$B$44,E13+F13)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="25" t="n">
+        <f aca="false">(D13+MIN(Input!$B$44,E13+F13))*(1+Input!$B$17)^(A13-Input!$B$36)</f>
+        <v>4746.73133763161</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <f aca="false">C13*0.0691</f>
+        <v>3502.8286980181</v>
+      </c>
+      <c r="M13" s="25" t="n">
+        <f aca="false">IF(B13&lt;Input!$B$6,M12*(1+Input!$B$49)+L13,M12)</f>
+        <v>38640.567595977</v>
+      </c>
+      <c r="N13" s="25" t="n">
+        <f aca="false">IF(B13&lt;Input!$B$6,N12*(1+Input!$B$28)+L13,N12)</f>
+        <v>45031.0883992892</v>
+      </c>
+      <c r="O13" s="25" t="n">
+        <f aca="false">L13*(1+Input!$B$17)^(A13-Input!$B$36)</f>
+        <v>2654.70638563904</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="n">
@@ -3717,7 +4158,7 @@
         <v>3555.37112848838</v>
       </c>
       <c r="E14" s="25" t="n">
-        <f aca="false">IF(B14&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B14&lt;Input!$B$6,Input!$B$26+C14*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F14" s="25" t="n">
@@ -3732,6 +4173,34 @@
         <f aca="false">H13+D14+E14+F14+G14</f>
         <v>89117.7830724294</v>
       </c>
+      <c r="I14" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E14+F14)-MIN(Input!$B$44,F14+C14*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <f aca="false">E14+F14-MIN(Input!$B$44,E14+F14)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <f aca="false">(D14+MIN(Input!$B$44,E14+F14))*(1+Input!$B$17)^(A14-Input!$B$36)</f>
+        <v>4891.09997809761</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <f aca="false">C14*0.0691</f>
+        <v>3555.37112848838</v>
+      </c>
+      <c r="M14" s="25" t="n">
+        <f aca="false">IF(B14&lt;Input!$B$6,M13*(1+Input!$B$49)+L14,M13)</f>
+        <v>42381.5649805637</v>
+      </c>
+      <c r="N14" s="25" t="n">
+        <f aca="false">IF(B14&lt;Input!$B$6,N13*(1+Input!$B$28)+L14,N13)</f>
+        <v>50162.5476217527</v>
+      </c>
+      <c r="O14" s="25" t="n">
+        <f aca="false">L14*(1+Input!$B$17)^(A14-Input!$B$36)</f>
+        <v>2748.41752105209</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
@@ -3750,7 +4219,7 @@
         <v>3608.7016954157</v>
       </c>
       <c r="E15" s="25" t="n">
-        <f aca="false">IF(B15&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B15&lt;Input!$B$6,Input!$B$26+C15*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F15" s="25" t="n">
@@ -3765,6 +4234,34 @@
         <f aca="false">H14+D15+E15+F15+G15</f>
         <v>98628.9722322721</v>
       </c>
+      <c r="I15" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E15+F15)-MIN(Input!$B$44,F15+C15*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <f aca="false">E15+F15-MIN(Input!$B$44,E15+F15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <f aca="false">(D15+MIN(Input!$B$44,E15+F15))*(1+Input!$B$17)^(A15-Input!$B$36)</f>
+        <v>5040.101012057</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <f aca="false">C15*0.0691</f>
+        <v>3608.7016954157</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <f aca="false">IF(B15&lt;Input!$B$6,M14*(1+Input!$B$49)+L15,M14)</f>
+        <v>46193.8643901017</v>
+      </c>
+      <c r="N15" s="25" t="n">
+        <f aca="false">IF(B15&lt;Input!$B$6,N14*(1+Input!$B$28)+L15,N14)</f>
+        <v>55526.9384839298</v>
+      </c>
+      <c r="O15" s="25" t="n">
+        <f aca="false">L15*(1+Input!$B$17)^(A15-Input!$B$36)</f>
+        <v>2845.43665954523</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="n">
@@ -3783,7 +4280,7 @@
         <v>3662.83222084694</v>
       </c>
       <c r="E16" s="25" t="n">
-        <f aca="false">IF(B16&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B16&lt;Input!$B$6,Input!$B$26+C16*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F16" s="25" t="n">
@@ -3798,6 +4295,34 @@
         <f aca="false">H15+D16+E16+F16+G16</f>
         <v>108538.934013994</v>
       </c>
+      <c r="I16" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E16+F16)-MIN(Input!$B$44,F16+C16*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <f aca="false">E16+F16-MIN(Input!$B$44,E16+F16)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <f aca="false">(D16+MIN(Input!$B$44,E16+F16))*(1+Input!$B$17)^(A16-Input!$B$36)</f>
+        <v>5193.88868660982</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <f aca="false">C16*0.0691</f>
+        <v>3662.83222084694</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <f aca="false">IF(B16&lt;Input!$B$6,M15*(1+Input!$B$49)+L16,M15)</f>
+        <v>50078.6083124305</v>
+      </c>
+      <c r="N16" s="25" t="n">
+        <f aca="false">IF(B16&lt;Input!$B$6,N15*(1+Input!$B$28)+L16,N15)</f>
+        <v>61133.2135517142</v>
+      </c>
+      <c r="O16" s="25" t="n">
+        <f aca="false">L16*(1+Input!$B$17)^(A16-Input!$B$36)</f>
+        <v>2945.88057362718</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="n">
@@ -3816,7 +4341,7 @@
         <v>3717.77470415964</v>
       </c>
       <c r="E17" s="25" t="n">
-        <f aca="false">IF(B17&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B17&lt;Input!$B$6,Input!$B$26+C17*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F17" s="25" t="n">
@@ -3831,6 +4356,34 @@
         <f aca="false">H16+D17+E17+F17+G17</f>
         <v>118862.61367438</v>
       </c>
+      <c r="I17" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E17+F17)-MIN(Input!$B$44,F17+C17*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <f aca="false">E17+F17-MIN(Input!$B$44,E17+F17)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <f aca="false">(D17+MIN(Input!$B$44,E17+F17))*(1+Input!$B$17)^(A17-Input!$B$36)</f>
+        <v>5352.62250825089</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <f aca="false">C17*0.0691</f>
+        <v>3717.77470415964</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <f aca="false">IF(B17&lt;Input!$B$6,M16*(1+Input!$B$49)+L17,M16)</f>
+        <v>54036.956723189</v>
+      </c>
+      <c r="N17" s="25" t="n">
+        <f aca="false">IF(B17&lt;Input!$B$6,N16*(1+Input!$B$28)+L17,N16)</f>
+        <v>66990.6507301839</v>
+      </c>
+      <c r="O17" s="25" t="n">
+        <f aca="false">L17*(1+Input!$B$17)^(A17-Input!$B$36)</f>
+        <v>3049.87015787622</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="n">
@@ -3849,7 +4402,7 @@
         <v>3773.54132472203</v>
       </c>
       <c r="E18" s="25" t="n">
-        <f aca="false">IF(B18&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B18&lt;Input!$B$6,Input!$B$26+C18*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F18" s="25" t="n">
@@ -3864,6 +4417,34 @@
         <f aca="false">H17+D18+E18+F18+G18</f>
         <v>129615.494377428</v>
       </c>
+      <c r="I18" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E18+F18)-MIN(Input!$B$44,F18+C18*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <f aca="false">E18+F18-MIN(Input!$B$44,E18+F18)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <f aca="false">(D18+MIN(Input!$B$44,E18+F18))*(1+Input!$B$17)^(A18-Input!$B$36)</f>
+        <v>5516.46742481596</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <f aca="false">C18*0.0691</f>
+        <v>3773.54132472203</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <f aca="false">IF(B18&lt;Input!$B$6,M17*(1+Input!$B$49)+L18,M17)</f>
+        <v>58070.0873498166</v>
+      </c>
+      <c r="N18" s="25" t="n">
+        <f aca="false">IF(B18&lt;Input!$B$6,N17*(1+Input!$B$28)+L18,N17)</f>
+        <v>73108.8648304623</v>
+      </c>
+      <c r="O18" s="25" t="n">
+        <f aca="false">L18*(1+Input!$B$17)^(A18-Input!$B$36)</f>
+        <v>3157.53057444925</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="n">
@@ -3882,7 +4463,7 @@
         <v>3830.14444459286</v>
       </c>
       <c r="E19" s="25" t="n">
-        <f aca="false">IF(B19&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B19&lt;Input!$B$6,Input!$B$26+C19*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F19" s="25" t="n">
@@ -3897,6 +4478,34 @@
         <f aca="false">H18+D19+E19+F19+G19</f>
         <v>140813.616243449</v>
       </c>
+      <c r="I19" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E19+F19)-MIN(Input!$B$44,F19+C19*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <f aca="false">E19+F19-MIN(Input!$B$44,E19+F19)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <f aca="false">(D19+MIN(Input!$B$44,E19+F19))*(1+Input!$B$17)^(A19-Input!$B$36)</f>
+        <v>5685.59401377626</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <f aca="false">C19*0.0691</f>
+        <v>3830.14444459286</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <f aca="false">IF(B19&lt;Input!$B$6,M18*(1+Input!$B$49)+L19,M18)</f>
+        <v>62179.1959395213</v>
+      </c>
+      <c r="N19" s="25" t="n">
+        <f aca="false">IF(B19&lt;Input!$B$6,N18*(1+Input!$B$28)+L19,N18)</f>
+        <v>79497.8195441214</v>
+      </c>
+      <c r="O19" s="25" t="n">
+        <f aca="false">L19*(1+Input!$B$17)^(A19-Input!$B$36)</f>
+        <v>3268.99140372731</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="n">
@@ -3915,7 +4524,7 @@
         <v>3887.59661126176</v>
       </c>
       <c r="E20" s="25" t="n">
-        <f aca="false">IF(B20&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B20&lt;Input!$B$6,Input!$B$26+C20*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F20" s="25" t="n">
@@ -3930,6 +4539,34 @@
         <f aca="false">H19+D20+E20+F20+G20</f>
         <v>152473.596068223</v>
       </c>
+      <c r="I20" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E20+F20)-MIN(Input!$B$44,F20+C20*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <f aca="false">E20+F20-MIN(Input!$B$44,E20+F20)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <f aca="false">(D20+MIN(Input!$B$44,E20+F20))*(1+Input!$B$17)^(A20-Input!$B$36)</f>
+        <v>5860.17867710415</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <f aca="false">C20*0.0691</f>
+        <v>3887.59661126176</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <f aca="false">IF(B20&lt;Input!$B$6,M19*(1+Input!$B$49)+L20,M19)</f>
+        <v>66365.4965312768</v>
+      </c>
+      <c r="N20" s="25" t="n">
+        <f aca="false">IF(B20&lt;Input!$B$6,N19*(1+Input!$B$28)+L20,N19)</f>
+        <v>86167.8398394274</v>
+      </c>
+      <c r="O20" s="25" t="n">
+        <f aca="false">L20*(1+Input!$B$17)^(A20-Input!$B$36)</f>
+        <v>3384.38680027888</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
@@ -3948,7 +4585,7 @@
         <v>3945.91056043068</v>
       </c>
       <c r="E21" s="25" t="n">
-        <f aca="false">IF(B21&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B21&lt;Input!$B$6,Input!$B$26+C21*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F21" s="25" t="n">
@@ -3963,6 +4600,34 @@
         <f aca="false">H20+D21+E21+F21+G21</f>
         <v>164612.647735708</v>
       </c>
+      <c r="I21" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E21+F21)-MIN(Input!$B$44,F21+C21*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <f aca="false">E21+F21-MIN(Input!$B$44,E21+F21)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="25" t="n">
+        <f aca="false">(D21+MIN(Input!$B$44,E21+F21))*(1+Input!$B$17)^(A21-Input!$B$36)</f>
+        <v>6040.40384294034</v>
+      </c>
+      <c r="L21" s="25" t="n">
+        <f aca="false">C21*0.0691</f>
+        <v>3945.91056043068</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <f aca="false">IF(B21&lt;Input!$B$6,M20*(1+Input!$B$49)+L21,M20)</f>
+        <v>70630.2217319068</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <f aca="false">IF(B21&lt;Input!$B$6,N20*(1+Input!$B$28)+L21,N20)</f>
+        <v>93129.624794238</v>
+      </c>
+      <c r="O21" s="25" t="n">
+        <f aca="false">L21*(1+Input!$B$17)^(A21-Input!$B$36)</f>
+        <v>3503.85565432872</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
@@ -3981,7 +4646,7 @@
         <v>4005.09921883714</v>
       </c>
       <c r="E22" s="25" t="n">
-        <f aca="false">IF(B22&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B22&lt;Input!$B$6,Input!$B$26+C22*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F22" s="25" t="n">
@@ -3996,6 +4661,34 @@
         <f aca="false">H21+D22+E22+F22+G22</f>
         <v>177248.603348632</v>
       </c>
+      <c r="I22" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E22+F22)-MIN(Input!$B$44,F22+C22*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <f aca="false">E22+F22-MIN(Input!$B$44,E22+F22)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <f aca="false">(D22+MIN(Input!$B$44,E22+F22))*(1+Input!$B$17)^(A22-Input!$B$36)</f>
+        <v>6226.45817430124</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <f aca="false">C22*0.0691</f>
+        <v>4005.09921883714</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <f aca="false">IF(B22&lt;Input!$B$6,M21*(1+Input!$B$49)+L22,M21)</f>
+        <v>74974.6229963187</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <f aca="false">IF(B22&lt;Input!$B$6,N21*(1+Input!$B$28)+L22,N21)</f>
+        <v>100394.260880873</v>
+      </c>
+      <c r="O22" s="25" t="n">
+        <f aca="false">L22*(1+Input!$B$17)^(A22-Input!$B$36)</f>
+        <v>3627.54175892653</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="n">
@@ -4014,7 +4707,7 @@
         <v>4065.1757071197</v>
       </c>
       <c r="E23" s="25" t="n">
-        <f aca="false">IF(B23&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B23&lt;Input!$B$6,Input!$B$26+C23*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F23" s="25" t="n">
@@ -4029,6 +4722,34 @@
         <f aca="false">H22+D23+E23+F23+G23</f>
         <v>190399.93510214</v>
       </c>
+      <c r="I23" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E23+F23)-MIN(Input!$B$44,F23+C23*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J23" s="25" t="n">
+        <f aca="false">E23+F23-MIN(Input!$B$44,E23+F23)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="25" t="n">
+        <f aca="false">(D23+MIN(Input!$B$44,E23+F23))*(1+Input!$B$17)^(A23-Input!$B$36)</f>
+        <v>6418.53678507327</v>
+      </c>
+      <c r="L23" s="25" t="n">
+        <f aca="false">C23*0.0691</f>
+        <v>4065.1757071197</v>
+      </c>
+      <c r="M23" s="25" t="n">
+        <f aca="false">IF(B23&lt;Input!$B$6,M22*(1+Input!$B$49)+L23,M22)</f>
+        <v>79399.9709119502</v>
+      </c>
+      <c r="N23" s="25" t="n">
+        <f aca="false">IF(B23&lt;Input!$B$6,N22*(1+Input!$B$28)+L23,N22)</f>
+        <v>107973.235718824</v>
+      </c>
+      <c r="O23" s="25" t="n">
+        <f aca="false">L23*(1+Input!$B$17)^(A23-Input!$B$36)</f>
+        <v>3755.59398301663</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="n">
@@ -4047,7 +4768,7 @@
         <v>4126.15334272649</v>
       </c>
       <c r="E24" s="25" t="n">
-        <f aca="false">IF(B24&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B24&lt;Input!$B$6,Input!$B$26+C24*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F24" s="25" t="n">
@@ -4062,6 +4783,34 @@
         <f aca="false">H23+D24+E24+F24+G24</f>
         <v>204085.777926566</v>
       </c>
+      <c r="I24" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E24+F24)-MIN(Input!$B$44,F24+C24*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <f aca="false">E24+F24-MIN(Input!$B$44,E24+F24)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <f aca="false">(D24+MIN(Input!$B$44,E24+F24))*(1+Input!$B$17)^(A24-Input!$B$36)</f>
+        <v>6616.84146354995</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <f aca="false">C24*0.0691</f>
+        <v>4126.15334272649</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <f aca="false">IF(B24&lt;Input!$B$6,M23*(1+Input!$B$49)+L24,M23)</f>
+        <v>83907.5554874889</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <f aca="false">IF(B24&lt;Input!$B$6,N23*(1+Input!$B$28)+L24,N23)</f>
+        <v>115878.452311709</v>
+      </c>
+      <c r="O24" s="25" t="n">
+        <f aca="false">L24*(1+Input!$B$17)^(A24-Input!$B$36)</f>
+        <v>3888.16645061712</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
@@ -4080,7 +4829,7 @@
         <v>4188.04564286739</v>
       </c>
       <c r="E25" s="25" t="n">
-        <f aca="false">IF(B25&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B25&lt;Input!$B$6,Input!$B$26+C25*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F25" s="25" t="n">
@@ -4095,6 +4844,34 @@
         <f aca="false">H24+D25+E25+F25+G25</f>
         <v>218325.952926284</v>
       </c>
+      <c r="I25" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E25+F25)-MIN(Input!$B$44,F25+C25*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J25" s="25" t="n">
+        <f aca="false">E25+F25-MIN(Input!$B$44,E25+F25)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="25" t="n">
+        <f aca="false">(D25+MIN(Input!$B$44,E25+F25))*(1+Input!$B$17)^(A25-Input!$B$36)</f>
+        <v>6821.58090377612</v>
+      </c>
+      <c r="L25" s="25" t="n">
+        <f aca="false">C25*0.0691</f>
+        <v>4188.04564286739</v>
+      </c>
+      <c r="M25" s="25" t="n">
+        <f aca="false">IF(B25&lt;Input!$B$6,M24*(1+Input!$B$49)+L25,M24)</f>
+        <v>88498.6864459335</v>
+      </c>
+      <c r="N25" s="25" t="n">
+        <f aca="false">IF(B25&lt;Input!$B$6,N24*(1+Input!$B$28)+L25,N24)</f>
+        <v>124122.243785486</v>
+      </c>
+      <c r="O25" s="25" t="n">
+        <f aca="false">L25*(1+Input!$B$17)^(A25-Input!$B$36)</f>
+        <v>4025.41872632391</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="n">
@@ -4113,7 +4890,7 @@
         <v>4250.8663275104</v>
       </c>
       <c r="E26" s="25" t="n">
-        <f aca="false">IF(B26&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B26&lt;Input!$B$6,Input!$B$26+C26*Input!$B$47,0)</f>
         <v>2000</v>
       </c>
       <c r="F26" s="25" t="n">
@@ -4128,6 +4905,34 @@
         <f aca="false">H25+D26+E26+F26+G26</f>
         <v>233140.991642577</v>
       </c>
+      <c r="I26" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E26+F26)-MIN(Input!$B$44,F26+C26*Input!$B$47)</f>
+        <v>2000</v>
+      </c>
+      <c r="J26" s="25" t="n">
+        <f aca="false">E26+F26-MIN(Input!$B$44,E26+F26)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="25" t="n">
+        <f aca="false">(D26+MIN(Input!$B$44,E26+F26))*(1+Input!$B$17)^(A26-Input!$B$36)</f>
+        <v>7032.97094497354</v>
+      </c>
+      <c r="L26" s="25" t="n">
+        <f aca="false">C26*0.0691</f>
+        <v>4250.8663275104</v>
+      </c>
+      <c r="M26" s="25" t="n">
+        <f aca="false">IF(B26&lt;Input!$B$6,M25*(1+Input!$B$49)+L26,M25)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N26" s="25" t="n">
+        <f aca="false">IF(B26&lt;Input!$B$6,N25*(1+Input!$B$28)+L26,N25)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O26" s="25" t="n">
+        <f aca="false">L26*(1+Input!$B$17)^(A26-Input!$B$36)</f>
+        <v>4167.51600736314</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="n">
@@ -4146,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="25" t="n">
-        <f aca="false">IF(B27&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B27&lt;Input!$B$6,Input!$B$26+C27*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F27" s="25" t="n">
@@ -4161,6 +4966,34 @@
         <f aca="false">H26+D27+E27+F27+G27</f>
         <v>241300.926350068</v>
       </c>
+      <c r="I27" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E27+F27)-MIN(Input!$B$44,F27+C27*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="25" t="n">
+        <f aca="false">E27+F27-MIN(Input!$B$44,E27+F27)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="25" t="n">
+        <f aca="false">(D27+MIN(Input!$B$44,E27+F27))*(1+Input!$B$17)^(A27-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="25" t="n">
+        <f aca="false">C27*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="25" t="n">
+        <f aca="false">IF(B27&lt;Input!$B$6,M26*(1+Input!$B$49)+L27,M26)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N27" s="25" t="n">
+        <f aca="false">IF(B27&lt;Input!$B$6,N26*(1+Input!$B$28)+L27,N26)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O27" s="25" t="n">
+        <f aca="false">L27*(1+Input!$B$17)^(A27-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="n">
@@ -4179,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="25" t="n">
-        <f aca="false">IF(B28&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B28&lt;Input!$B$6,Input!$B$26+C28*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="25" t="n">
@@ -4194,6 +5027,34 @@
         <f aca="false">H27+D28+E28+F28+G28</f>
         <v>249746.45877232</v>
       </c>
+      <c r="I28" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E28+F28)-MIN(Input!$B$44,F28+C28*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="25" t="n">
+        <f aca="false">E28+F28-MIN(Input!$B$44,E28+F28)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="25" t="n">
+        <f aca="false">(D28+MIN(Input!$B$44,E28+F28))*(1+Input!$B$17)^(A28-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <f aca="false">C28*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="25" t="n">
+        <f aca="false">IF(B28&lt;Input!$B$6,M27*(1+Input!$B$49)+L28,M27)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N28" s="25" t="n">
+        <f aca="false">IF(B28&lt;Input!$B$6,N27*(1+Input!$B$28)+L28,N27)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O28" s="25" t="n">
+        <f aca="false">L28*(1+Input!$B$17)^(A28-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="n">
@@ -4212,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="25" t="n">
-        <f aca="false">IF(B29&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B29&lt;Input!$B$6,Input!$B$26+C29*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F29" s="25" t="n">
@@ -4227,6 +5088,34 @@
         <f aca="false">H28+D29+E29+F29+G29</f>
         <v>258487.584829351</v>
       </c>
+      <c r="I29" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E29+F29)-MIN(Input!$B$44,F29+C29*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <f aca="false">E29+F29-MIN(Input!$B$44,E29+F29)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="25" t="n">
+        <f aca="false">(D29+MIN(Input!$B$44,E29+F29))*(1+Input!$B$17)^(A29-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="25" t="n">
+        <f aca="false">C29*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="25" t="n">
+        <f aca="false">IF(B29&lt;Input!$B$6,M28*(1+Input!$B$49)+L29,M28)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N29" s="25" t="n">
+        <f aca="false">IF(B29&lt;Input!$B$6,N28*(1+Input!$B$28)+L29,N28)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O29" s="25" t="n">
+        <f aca="false">L29*(1+Input!$B$17)^(A29-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="n">
@@ -4245,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="25" t="n">
-        <f aca="false">IF(B30&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B30&lt;Input!$B$6,Input!$B$26+C30*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F30" s="25" t="n">
@@ -4260,6 +5149,34 @@
         <f aca="false">H29+D30+E30+F30+G30</f>
         <v>267534.650298378</v>
       </c>
+      <c r="I30" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E30+F30)-MIN(Input!$B$44,F30+C30*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="25" t="n">
+        <f aca="false">E30+F30-MIN(Input!$B$44,E30+F30)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="25" t="n">
+        <f aca="false">(D30+MIN(Input!$B$44,E30+F30))*(1+Input!$B$17)^(A30-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <f aca="false">C30*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="25" t="n">
+        <f aca="false">IF(B30&lt;Input!$B$6,M29*(1+Input!$B$49)+L30,M29)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N30" s="25" t="n">
+        <f aca="false">IF(B30&lt;Input!$B$6,N29*(1+Input!$B$28)+L30,N29)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O30" s="25" t="n">
+        <f aca="false">L30*(1+Input!$B$17)^(A30-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="n">
@@ -4278,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="25" t="n">
-        <f aca="false">IF(B31&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B31&lt;Input!$B$6,Input!$B$26+C31*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F31" s="25" t="n">
@@ -4293,6 +5210,34 @@
         <f aca="false">H30+D31+E31+F31+G31</f>
         <v>276898.363058822</v>
       </c>
+      <c r="I31" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E31+F31)-MIN(Input!$B$44,F31+C31*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <f aca="false">E31+F31-MIN(Input!$B$44,E31+F31)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="25" t="n">
+        <f aca="false">(D31+MIN(Input!$B$44,E31+F31))*(1+Input!$B$17)^(A31-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <f aca="false">C31*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <f aca="false">IF(B31&lt;Input!$B$6,M30*(1+Input!$B$49)+L31,M30)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <f aca="false">IF(B31&lt;Input!$B$6,N30*(1+Input!$B$28)+L31,N30)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O31" s="25" t="n">
+        <f aca="false">L31*(1+Input!$B$17)^(A31-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="n">
@@ -4311,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="25" t="n">
-        <f aca="false">IF(B32&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B32&lt;Input!$B$6,Input!$B$26+C32*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F32" s="25" t="n">
@@ -4326,6 +5271,34 @@
         <f aca="false">H31+D32+E32+F32+G32</f>
         <v>286589.80576588</v>
       </c>
+      <c r="I32" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E32+F32)-MIN(Input!$B$44,F32+C32*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="25" t="n">
+        <f aca="false">E32+F32-MIN(Input!$B$44,E32+F32)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="25" t="n">
+        <f aca="false">(D32+MIN(Input!$B$44,E32+F32))*(1+Input!$B$17)^(A32-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <f aca="false">C32*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="25" t="n">
+        <f aca="false">IF(B32&lt;Input!$B$6,M31*(1+Input!$B$49)+L32,M31)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N32" s="25" t="n">
+        <f aca="false">IF(B32&lt;Input!$B$6,N31*(1+Input!$B$28)+L32,N31)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O32" s="25" t="n">
+        <f aca="false">L32*(1+Input!$B$17)^(A32-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="n">
@@ -4344,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="25" t="n">
-        <f aca="false">IF(B33&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B33&lt;Input!$B$6,Input!$B$26+C33*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F33" s="25" t="n">
@@ -4359,6 +5332,34 @@
         <f aca="false">H32+D33+E33+F33+G33</f>
         <v>296620.448967686</v>
       </c>
+      <c r="I33" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E33+F33)-MIN(Input!$B$44,F33+C33*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="25" t="n">
+        <f aca="false">E33+F33-MIN(Input!$B$44,E33+F33)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="25" t="n">
+        <f aca="false">(D33+MIN(Input!$B$44,E33+F33))*(1+Input!$B$17)^(A33-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <f aca="false">C33*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="25" t="n">
+        <f aca="false">IF(B33&lt;Input!$B$6,M32*(1+Input!$B$49)+L33,M32)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N33" s="25" t="n">
+        <f aca="false">IF(B33&lt;Input!$B$6,N32*(1+Input!$B$28)+L33,N32)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O33" s="25" t="n">
+        <f aca="false">L33*(1+Input!$B$17)^(A33-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="n">
@@ -4377,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="25" t="n">
-        <f aca="false">IF(B34&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B34&lt;Input!$B$6,Input!$B$26+C34*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F34" s="25" t="n">
@@ -4392,6 +5393,34 @@
         <f aca="false">H33+D34+E34+F34+G34</f>
         <v>307002.164681555</v>
       </c>
+      <c r="I34" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E34+F34)-MIN(Input!$B$44,F34+C34*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="25" t="n">
+        <f aca="false">E34+F34-MIN(Input!$B$44,E34+F34)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="25" t="n">
+        <f aca="false">(D34+MIN(Input!$B$44,E34+F34))*(1+Input!$B$17)^(A34-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <f aca="false">C34*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="25" t="n">
+        <f aca="false">IF(B34&lt;Input!$B$6,M33*(1+Input!$B$49)+L34,M33)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N34" s="25" t="n">
+        <f aca="false">IF(B34&lt;Input!$B$6,N33*(1+Input!$B$28)+L34,N33)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O34" s="25" t="n">
+        <f aca="false">L34*(1+Input!$B$17)^(A34-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="n">
@@ -4410,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="25" t="n">
-        <f aca="false">IF(B35&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B35&lt;Input!$B$6,Input!$B$26+C35*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F35" s="25" t="n">
@@ -4425,6 +5454,34 @@
         <f aca="false">H34+D35+E35+F35+G35</f>
         <v>317747.24044541</v>
       </c>
+      <c r="I35" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E35+F35)-MIN(Input!$B$44,F35+C35*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="25" t="n">
+        <f aca="false">E35+F35-MIN(Input!$B$44,E35+F35)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="25" t="n">
+        <f aca="false">(D35+MIN(Input!$B$44,E35+F35))*(1+Input!$B$17)^(A35-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <f aca="false">C35*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="25" t="n">
+        <f aca="false">IF(B35&lt;Input!$B$6,M34*(1+Input!$B$49)+L35,M34)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N35" s="25" t="n">
+        <f aca="false">IF(B35&lt;Input!$B$6,N34*(1+Input!$B$28)+L35,N34)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O35" s="25" t="n">
+        <f aca="false">L35*(1+Input!$B$17)^(A35-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="n">
@@ -4443,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="25" t="n">
-        <f aca="false">IF(B36&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B36&lt;Input!$B$6,Input!$B$26+C36*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F36" s="25" t="n">
@@ -4458,6 +5515,34 @@
         <f aca="false">H35+D36+E36+F36+G36</f>
         <v>328868.393860999</v>
       </c>
+      <c r="I36" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E36+F36)-MIN(Input!$B$44,F36+C36*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="25" t="n">
+        <f aca="false">E36+F36-MIN(Input!$B$44,E36+F36)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="25" t="n">
+        <f aca="false">(D36+MIN(Input!$B$44,E36+F36))*(1+Input!$B$17)^(A36-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <f aca="false">C36*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="25" t="n">
+        <f aca="false">IF(B36&lt;Input!$B$6,M35*(1+Input!$B$49)+L36,M35)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N36" s="25" t="n">
+        <f aca="false">IF(B36&lt;Input!$B$6,N35*(1+Input!$B$28)+L36,N35)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O36" s="25" t="n">
+        <f aca="false">L36*(1+Input!$B$17)^(A36-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="n">
@@ -4476,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="25" t="n">
-        <f aca="false">IF(B37&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B37&lt;Input!$B$6,Input!$B$26+C37*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F37" s="25" t="n">
@@ -4491,6 +5576,34 @@
         <f aca="false">H36+D37+E37+F37+G37</f>
         <v>340378.787646134</v>
       </c>
+      <c r="I37" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E37+F37)-MIN(Input!$B$44,F37+C37*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <f aca="false">E37+F37-MIN(Input!$B$44,E37+F37)</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="25" t="n">
+        <f aca="false">(D37+MIN(Input!$B$44,E37+F37))*(1+Input!$B$17)^(A37-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <f aca="false">C37*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="25" t="n">
+        <f aca="false">IF(B37&lt;Input!$B$6,M36*(1+Input!$B$49)+L37,M36)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N37" s="25" t="n">
+        <f aca="false">IF(B37&lt;Input!$B$6,N36*(1+Input!$B$28)+L37,N36)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O37" s="25" t="n">
+        <f aca="false">L37*(1+Input!$B$17)^(A37-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="n">
@@ -4509,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="25" t="n">
-        <f aca="false">IF(B38&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B38&lt;Input!$B$6,Input!$B$26+C38*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F38" s="25" t="n">
@@ -4524,6 +5637,34 @@
         <f aca="false">H37+D38+E38+F38+G38</f>
         <v>352292.045213749</v>
       </c>
+      <c r="I38" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E38+F38)-MIN(Input!$B$44,F38+C38*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="25" t="n">
+        <f aca="false">E38+F38-MIN(Input!$B$44,E38+F38)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="25" t="n">
+        <f aca="false">(D38+MIN(Input!$B$44,E38+F38))*(1+Input!$B$17)^(A38-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <f aca="false">C38*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="25" t="n">
+        <f aca="false">IF(B38&lt;Input!$B$6,M37*(1+Input!$B$49)+L38,M37)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N38" s="25" t="n">
+        <f aca="false">IF(B38&lt;Input!$B$6,N37*(1+Input!$B$28)+L38,N37)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O38" s="25" t="n">
+        <f aca="false">L38*(1+Input!$B$17)^(A38-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="n">
@@ -4542,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="25" t="n">
-        <f aca="false">IF(B39&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B39&lt;Input!$B$6,Input!$B$26+C39*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F39" s="25" t="n">
@@ -4557,6 +5698,34 @@
         <f aca="false">H38+D39+E39+F39+G39</f>
         <v>364622.26679623</v>
       </c>
+      <c r="I39" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E39+F39)-MIN(Input!$B$44,F39+C39*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="25" t="n">
+        <f aca="false">E39+F39-MIN(Input!$B$44,E39+F39)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="25" t="n">
+        <f aca="false">(D39+MIN(Input!$B$44,E39+F39))*(1+Input!$B$17)^(A39-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <f aca="false">C39*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="25" t="n">
+        <f aca="false">IF(B39&lt;Input!$B$6,M38*(1+Input!$B$49)+L39,M38)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N39" s="25" t="n">
+        <f aca="false">IF(B39&lt;Input!$B$6,N38*(1+Input!$B$28)+L39,N38)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O39" s="25" t="n">
+        <f aca="false">L39*(1+Input!$B$17)^(A39-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="n">
@@ -4575,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="25" t="n">
-        <f aca="false">IF(B40&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B40&lt;Input!$B$6,Input!$B$26+C40*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F40" s="25" t="n">
@@ -4590,6 +5759,34 @@
         <f aca="false">H39+D40+E40+F40+G40</f>
         <v>377384.046134098</v>
       </c>
+      <c r="I40" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E40+F40)-MIN(Input!$B$44,F40+C40*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <f aca="false">E40+F40-MIN(Input!$B$44,E40+F40)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="25" t="n">
+        <f aca="false">(D40+MIN(Input!$B$44,E40+F40))*(1+Input!$B$17)^(A40-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <f aca="false">C40*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="25" t="n">
+        <f aca="false">IF(B40&lt;Input!$B$6,M39*(1+Input!$B$49)+L40,M39)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N40" s="25" t="n">
+        <f aca="false">IF(B40&lt;Input!$B$6,N39*(1+Input!$B$28)+L40,N39)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O40" s="25" t="n">
+        <f aca="false">L40*(1+Input!$B$17)^(A40-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="n">
@@ -4608,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="25" t="n">
-        <f aca="false">IF(B41&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B41&lt;Input!$B$6,Input!$B$26+C41*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F41" s="25" t="n">
@@ -4623,6 +5820,34 @@
         <f aca="false">H40+D41+E41+F41+G41</f>
         <v>390592.487748791</v>
       </c>
+      <c r="I41" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E41+F41)-MIN(Input!$B$44,F41+C41*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <f aca="false">E41+F41-MIN(Input!$B$44,E41+F41)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <f aca="false">(D41+MIN(Input!$B$44,E41+F41))*(1+Input!$B$17)^(A41-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <f aca="false">C41*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="25" t="n">
+        <f aca="false">IF(B41&lt;Input!$B$6,M40*(1+Input!$B$49)+L41,M40)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N41" s="25" t="n">
+        <f aca="false">IF(B41&lt;Input!$B$6,N40*(1+Input!$B$28)+L41,N40)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O41" s="25" t="n">
+        <f aca="false">L41*(1+Input!$B$17)^(A41-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="n">
@@ -4641,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="25" t="n">
-        <f aca="false">IF(B42&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B42&lt;Input!$B$6,Input!$B$26+C42*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F42" s="25" t="n">
@@ -4656,6 +5881,34 @@
         <f aca="false">H41+D42+E42+F42+G42</f>
         <v>404263.224819999</v>
       </c>
+      <c r="I42" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E42+F42)-MIN(Input!$B$44,F42+C42*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="25" t="n">
+        <f aca="false">E42+F42-MIN(Input!$B$44,E42+F42)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="25" t="n">
+        <f aca="false">(D42+MIN(Input!$B$44,E42+F42))*(1+Input!$B$17)^(A42-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <f aca="false">C42*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="25" t="n">
+        <f aca="false">IF(B42&lt;Input!$B$6,M41*(1+Input!$B$49)+L42,M41)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N42" s="25" t="n">
+        <f aca="false">IF(B42&lt;Input!$B$6,N41*(1+Input!$B$28)+L42,N41)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O42" s="25" t="n">
+        <f aca="false">L42*(1+Input!$B$17)^(A42-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="n">
@@ -4674,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="25" t="n">
-        <f aca="false">IF(B43&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B43&lt;Input!$B$6,Input!$B$26+C43*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F43" s="25" t="n">
@@ -4689,6 +5942,34 @@
         <f aca="false">H42+D43+E43+F43+G43</f>
         <v>418412.437688699</v>
       </c>
+      <c r="I43" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E43+F43)-MIN(Input!$B$44,F43+C43*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="25" t="n">
+        <f aca="false">E43+F43-MIN(Input!$B$44,E43+F43)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="25" t="n">
+        <f aca="false">(D43+MIN(Input!$B$44,E43+F43))*(1+Input!$B$17)^(A43-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="25" t="n">
+        <f aca="false">C43*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="25" t="n">
+        <f aca="false">IF(B43&lt;Input!$B$6,M42*(1+Input!$B$49)+L43,M42)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N43" s="25" t="n">
+        <f aca="false">IF(B43&lt;Input!$B$6,N42*(1+Input!$B$28)+L43,N42)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O43" s="25" t="n">
+        <f aca="false">L43*(1+Input!$B$17)^(A43-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="n">
@@ -4707,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="25" t="n">
-        <f aca="false">IF(B44&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B44&lt;Input!$B$6,Input!$B$26+C44*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F44" s="25" t="n">
@@ -4722,6 +6003,34 @@
         <f aca="false">H43+D44+E44+F44+G44</f>
         <v>433056.873007803</v>
       </c>
+      <c r="I44" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E44+F44)-MIN(Input!$B$44,F44+C44*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <f aca="false">E44+F44-MIN(Input!$B$44,E44+F44)</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="25" t="n">
+        <f aca="false">(D44+MIN(Input!$B$44,E44+F44))*(1+Input!$B$17)^(A44-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L44" s="25" t="n">
+        <f aca="false">C44*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="25" t="n">
+        <f aca="false">IF(B44&lt;Input!$B$6,M43*(1+Input!$B$49)+L44,M43)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N44" s="25" t="n">
+        <f aca="false">IF(B44&lt;Input!$B$6,N43*(1+Input!$B$28)+L44,N43)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O44" s="25" t="n">
+        <f aca="false">L44*(1+Input!$B$17)^(A44-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="n">
@@ -4740,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="25" t="n">
-        <f aca="false">IF(B45&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B45&lt;Input!$B$6,Input!$B$26+C45*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F45" s="25" t="n">
@@ -4755,6 +6064,34 @@
         <f aca="false">H44+D45+E45+F45+G45</f>
         <v>448213.863563077</v>
       </c>
+      <c r="I45" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E45+F45)-MIN(Input!$B$44,F45+C45*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="25" t="n">
+        <f aca="false">E45+F45-MIN(Input!$B$44,E45+F45)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="25" t="n">
+        <f aca="false">(D45+MIN(Input!$B$44,E45+F45))*(1+Input!$B$17)^(A45-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <f aca="false">C45*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="25" t="n">
+        <f aca="false">IF(B45&lt;Input!$B$6,M44*(1+Input!$B$49)+L45,M44)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N45" s="25" t="n">
+        <f aca="false">IF(B45&lt;Input!$B$6,N44*(1+Input!$B$28)+L45,N44)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O45" s="25" t="n">
+        <f aca="false">L45*(1+Input!$B$17)^(A45-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="n">
@@ -4773,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="25" t="n">
-        <f aca="false">IF(B46&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B46&lt;Input!$B$6,Input!$B$26+C46*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F46" s="25" t="n">
@@ -4788,6 +6125,34 @@
         <f aca="false">H45+D46+E46+F46+G46</f>
         <v>463901.348787784</v>
       </c>
+      <c r="I46" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E46+F46)-MIN(Input!$B$44,F46+C46*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="25" t="n">
+        <f aca="false">E46+F46-MIN(Input!$B$44,E46+F46)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="25" t="n">
+        <f aca="false">(D46+MIN(Input!$B$44,E46+F46))*(1+Input!$B$17)^(A46-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <f aca="false">C46*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="25" t="n">
+        <f aca="false">IF(B46&lt;Input!$B$6,M45*(1+Input!$B$49)+L46,M45)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N46" s="25" t="n">
+        <f aca="false">IF(B46&lt;Input!$B$6,N45*(1+Input!$B$28)+L46,N45)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O46" s="25" t="n">
+        <f aca="false">L46*(1+Input!$B$17)^(A46-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="n">
@@ -4806,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="25" t="n">
-        <f aca="false">IF(B47&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B47&lt;Input!$B$6,Input!$B$26+C47*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F47" s="25" t="n">
@@ -4821,6 +6186,34 @@
         <f aca="false">H46+D47+E47+F47+G47</f>
         <v>480137.895995357</v>
       </c>
+      <c r="I47" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E47+F47)-MIN(Input!$B$44,F47+C47*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="25" t="n">
+        <f aca="false">E47+F47-MIN(Input!$B$44,E47+F47)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="25" t="n">
+        <f aca="false">(D47+MIN(Input!$B$44,E47+F47))*(1+Input!$B$17)^(A47-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <f aca="false">C47*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="25" t="n">
+        <f aca="false">IF(B47&lt;Input!$B$6,M46*(1+Input!$B$49)+L47,M46)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N47" s="25" t="n">
+        <f aca="false">IF(B47&lt;Input!$B$6,N46*(1+Input!$B$28)+L47,N46)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O47" s="25" t="n">
+        <f aca="false">L47*(1+Input!$B$17)^(A47-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="n">
@@ -4839,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="25" t="n">
-        <f aca="false">IF(B48&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B48&lt;Input!$B$6,Input!$B$26+C48*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F48" s="25" t="n">
@@ -4854,6 +6247,34 @@
         <f aca="false">H47+D48+E48+F48+G48</f>
         <v>496942.722355194</v>
       </c>
+      <c r="I48" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E48+F48)-MIN(Input!$B$44,F48+C48*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="25" t="n">
+        <f aca="false">E48+F48-MIN(Input!$B$44,E48+F48)</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="25" t="n">
+        <f aca="false">(D48+MIN(Input!$B$44,E48+F48))*(1+Input!$B$17)^(A48-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="25" t="n">
+        <f aca="false">C48*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="25" t="n">
+        <f aca="false">IF(B48&lt;Input!$B$6,M47*(1+Input!$B$49)+L48,M47)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N48" s="25" t="n">
+        <f aca="false">IF(B48&lt;Input!$B$6,N47*(1+Input!$B$28)+L48,N47)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O48" s="25" t="n">
+        <f aca="false">L48*(1+Input!$B$17)^(A48-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="n">
@@ -4872,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="25" t="n">
-        <f aca="false">IF(B49&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B49&lt;Input!$B$6,Input!$B$26+C49*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F49" s="25" t="n">
@@ -4887,6 +6308,34 @@
         <f aca="false">H48+D49+E49+F49+G49</f>
         <v>514335.717637626</v>
       </c>
+      <c r="I49" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E49+F49)-MIN(Input!$B$44,F49+C49*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="25" t="n">
+        <f aca="false">E49+F49-MIN(Input!$B$44,E49+F49)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="25" t="n">
+        <f aca="false">(D49+MIN(Input!$B$44,E49+F49))*(1+Input!$B$17)^(A49-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <f aca="false">C49*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="25" t="n">
+        <f aca="false">IF(B49&lt;Input!$B$6,M48*(1+Input!$B$49)+L49,M48)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N49" s="25" t="n">
+        <f aca="false">IF(B49&lt;Input!$B$6,N48*(1+Input!$B$28)+L49,N48)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O49" s="25" t="n">
+        <f aca="false">L49*(1+Input!$B$17)^(A49-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="n">
@@ -4905,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="25" t="n">
-        <f aca="false">IF(B50&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B50&lt;Input!$B$6,Input!$B$26+C50*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F50" s="25" t="n">
@@ -4920,6 +6369,34 @@
         <f aca="false">H49+D50+E50+F50+G50</f>
         <v>532337.467754943</v>
       </c>
+      <c r="I50" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E50+F50)-MIN(Input!$B$44,F50+C50*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="25" t="n">
+        <f aca="false">E50+F50-MIN(Input!$B$44,E50+F50)</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="25" t="n">
+        <f aca="false">(D50+MIN(Input!$B$44,E50+F50))*(1+Input!$B$17)^(A50-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="25" t="n">
+        <f aca="false">C50*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="25" t="n">
+        <f aca="false">IF(B50&lt;Input!$B$6,M49*(1+Input!$B$49)+L50,M49)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N50" s="25" t="n">
+        <f aca="false">IF(B50&lt;Input!$B$6,N49*(1+Input!$B$28)+L50,N49)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O50" s="25" t="n">
+        <f aca="false">L50*(1+Input!$B$17)^(A50-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="n">
@@ -4938,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="25" t="n">
-        <f aca="false">IF(B51&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B51&lt;Input!$B$6,Input!$B$26+C51*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F51" s="25" t="n">
@@ -4953,6 +6430,34 @@
         <f aca="false">H50+D51+E51+F51+G51</f>
         <v>550969.279126366</v>
       </c>
+      <c r="I51" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E51+F51)-MIN(Input!$B$44,F51+C51*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="25" t="n">
+        <f aca="false">E51+F51-MIN(Input!$B$44,E51+F51)</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="25" t="n">
+        <f aca="false">(D51+MIN(Input!$B$44,E51+F51))*(1+Input!$B$17)^(A51-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <f aca="false">C51*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="25" t="n">
+        <f aca="false">IF(B51&lt;Input!$B$6,M50*(1+Input!$B$49)+L51,M50)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N51" s="25" t="n">
+        <f aca="false">IF(B51&lt;Input!$B$6,N50*(1+Input!$B$28)+L51,N50)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O51" s="25" t="n">
+        <f aca="false">L51*(1+Input!$B$17)^(A51-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="n">
@@ -4971,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="25" t="n">
-        <f aca="false">IF(B52&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B52&lt;Input!$B$6,Input!$B$26+C52*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F52" s="25" t="n">
@@ -4986,6 +6491,34 @@
         <f aca="false">H51+D52+E52+F52+G52</f>
         <v>570253.203895789</v>
       </c>
+      <c r="I52" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E52+F52)-MIN(Input!$B$44,F52+C52*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="25" t="n">
+        <f aca="false">E52+F52-MIN(Input!$B$44,E52+F52)</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="25" t="n">
+        <f aca="false">(D52+MIN(Input!$B$44,E52+F52))*(1+Input!$B$17)^(A52-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <f aca="false">C52*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="25" t="n">
+        <f aca="false">IF(B52&lt;Input!$B$6,M51*(1+Input!$B$49)+L52,M51)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N52" s="25" t="n">
+        <f aca="false">IF(B52&lt;Input!$B$6,N51*(1+Input!$B$28)+L52,N51)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O52" s="25" t="n">
+        <f aca="false">L52*(1+Input!$B$17)^(A52-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="23" t="n">
@@ -5004,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="25" t="n">
-        <f aca="false">IF(B53&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B53&lt;Input!$B$6,Input!$B$26+C53*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F53" s="25" t="n">
@@ -5019,6 +6552,34 @@
         <f aca="false">H52+D53+E53+F53+G53</f>
         <v>590212.066032141</v>
       </c>
+      <c r="I53" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E53+F53)-MIN(Input!$B$44,F53+C53*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="25" t="n">
+        <f aca="false">E53+F53-MIN(Input!$B$44,E53+F53)</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="25" t="n">
+        <f aca="false">(D53+MIN(Input!$B$44,E53+F53))*(1+Input!$B$17)^(A53-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="25" t="n">
+        <f aca="false">C53*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="25" t="n">
+        <f aca="false">IF(B53&lt;Input!$B$6,M52*(1+Input!$B$49)+L53,M52)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N53" s="25" t="n">
+        <f aca="false">IF(B53&lt;Input!$B$6,N52*(1+Input!$B$28)+L53,N52)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O53" s="25" t="n">
+        <f aca="false">L53*(1+Input!$B$17)^(A53-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="n">
@@ -5037,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="25" t="n">
-        <f aca="false">IF(B54&lt;Input!$B$6, MIN(Input!$B$26, 5300), 0)</f>
+        <f aca="false">IF(B54&lt;Input!$B$6,Input!$B$26+C54*Input!$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="F54" s="25" t="n">
@@ -5052,10 +6613,38 @@
         <f aca="false">H53+D54+E54+F54+G54</f>
         <v>610869.488343266</v>
       </c>
+      <c r="I54" s="25" t="n">
+        <f aca="false">MIN(Input!$B$44,E54+F54)-MIN(Input!$B$44,F54+C54*Input!$B$47)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="25" t="n">
+        <f aca="false">E54+F54-MIN(Input!$B$44,E54+F54)</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="25" t="n">
+        <f aca="false">(D54+MIN(Input!$B$44,E54+F54))*(1+Input!$B$17)^(A54-Input!$B$36)</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="25" t="n">
+        <f aca="false">C54*0.0691</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="25" t="n">
+        <f aca="false">IF(B54&lt;Input!$B$6,M53*(1+Input!$B$49)+L54,M53)</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="N54" s="25" t="n">
+        <f aca="false">IF(B54&lt;Input!$B$6,N53*(1+Input!$B$28)+L54,N53)</f>
+        <v>132717.388645489</v>
+      </c>
+      <c r="O54" s="25" t="n">
+        <f aca="false">L54*(1+Input!$B$17)^(A54-Input!$B$36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5067,7 +6656,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(H5:H54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
@@ -5076,7 +6665,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B59" s="30" t="n">
         <f aca="false">Input!$B$38</f>
@@ -5085,57 +6674,57 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B60" s="15" t="n">
-        <f aca="false">B58*B59</f>
-        <v>26578.0730472538</v>
+        <f aca="false">((Input!$B$22*Input!$B$21+Input!$B$25)*(1+Input!$B$17)^(-Input!$B$36)+SUM(K5:K54))*Input!$B$38</f>
+        <v>14037.7117311744</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58-B60</f>
-        <v>206562.918595324</v>
+        <v>219103.279911403</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61*0.055</f>
-        <v>11360.9605227428</v>
+        <v>12050.6803951272</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">B62/13</f>
-        <v>873.920040210984</v>
+        <v>926.975415009782</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B64" s="15" t="n">
-        <f aca="false">SUM(E5:E54)*Input!$B$37</f>
+        <f aca="false">SUM(I5:I54)*Input!$B$37</f>
         <v>14520</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -5147,7 +6736,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -5159,7 +6748,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -5171,7 +6760,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="22" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -5183,7 +6772,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="22" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -5193,8 +6782,191 @@
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
     </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="15" t="n">
+        <f aca="false">MAX(0,Input!$B$44-F5-C5*Input!$B$47)</f>
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" s="15" t="n">
+        <f aca="false">SUM(J5:J54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B80" s="15" t="n">
+        <f aca="false">INDEX(M5:M54,MATCH(Input!$B$6-1,B5:B54,0))</f>
+        <v>93174.6935220567</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B81" s="15" t="n">
+        <f aca="false">Input!$B$22*(1+Input!$B$17)^(-Input!$B$36)+SUM(O5:O54)</f>
+        <v>70423.5321133614</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" s="15" t="n">
+        <f aca="false">B81*12/(Input!$B$48+Input!$B$36)</f>
+        <v>33803.2954144135</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B83" s="11" t="n">
+        <f aca="false">IF(B82&lt;=0,0,IF(B82&lt;=28000,B82*0.23,IF(B82&lt;=50000,6440+(B82-28000)*0.33,13700+(B82-50000)*0.43))/B82)</f>
+        <v>0.247167839239541</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B84" s="29" t="n">
+        <f aca="false">B80-B81*B83</f>
+        <v>75768.2612579807</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" s="15" t="n">
+        <f aca="false">INDEX(N5:N54,MATCH(Input!$B$6-1,B5:B54,0))</f>
+        <v>132717.388645489</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B86" s="15" t="n">
+        <f aca="false">B81*Input!$B$38</f>
+        <v>8028.2826609232</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B87" s="29" t="n">
+        <f aca="false">B85-B86</f>
+        <v>124689.105984565</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B88" s="29" t="n">
+        <f aca="false">B87-B84</f>
+        <v>48920.8447265847</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="22"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="15">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A57:H57"/>
@@ -5203,6 +6975,13 @@
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A91:H91"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5219,7 +6998,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
@@ -5228,7 +7007,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5236,7 +7015,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5244,21 +7023,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>0.005</v>
@@ -5273,7 +7052,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>0</v>
@@ -5288,7 +7067,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>0.025</v>
@@ -5335,7 +7114,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">(Pubblica!$E$5*(1+B6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+B6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-B8)^(Input!$B$36/2)</f>
@@ -5352,7 +7131,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B11-MAX(0,IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0))))-IF(IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0)))&gt;0,B11*0.02,0)</f>
@@ -5369,75 +7148,92 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="B13" s="26" t="n">
-        <f aca="false">(Input!$B$22+Input!$B$25)*(1+B9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+B9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+B9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+B9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
         <v>194700.656586312</v>
       </c>
       <c r="C13" s="26" t="n">
-        <f aca="false">(Input!$B$22+Input!$B$25)*(1+C9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+C9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+C9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+C9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
         <v>233140.991642577</v>
       </c>
       <c r="D13" s="26" t="n">
-        <f aca="false">(Input!$B$22+Input!$B$25)*(1+D9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27)+MIN(Input!$B$26,5300))*(1+D9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+D9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+D9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
         <v>279432.685515174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B14" s="26" t="n">
-        <f aca="false">B13*(1-Input!$B$38)</f>
-        <v>172504.781735473</v>
+        <f aca="false">B13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+B7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+B7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
+        <v>182353.79791856</v>
       </c>
       <c r="C14" s="26" t="n">
-        <f aca="false">C13*(1-Input!$B$38)</f>
-        <v>206562.918595323</v>
+        <f aca="false">C13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+C7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+C7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
+        <v>219103.279911403</v>
       </c>
       <c r="D14" s="26" t="n">
-        <f aca="false">D13*(1-Input!$B$38)</f>
-        <v>247577.359366444</v>
+        <f aca="false">D13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+D7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+D7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
+        <v>263423.987845377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B14*0.055</f>
-        <v>9487.762995451</v>
+        <v>10029.4588855208</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">C14*0.055</f>
-        <v>11360.9605227428</v>
+        <v>12050.6803951272</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">D14*0.055</f>
-        <v>13616.7547651544</v>
+        <v>14488.3193314958</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <f aca="false">IF(Input!$B$21=0,B31-B32*B33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <f aca="false">IF(Input!$B$21=0,C31-C32*C33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <f aca="false">IF(Input!$B$21=0,D31-D32*D33,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
-        <v>29693.1698656577</v>
+        <v>30234.8657557275</v>
       </c>
       <c r="C17" s="25" t="n">
         <f aca="false">C12+C15</f>
-        <v>34919.9241693609</v>
+        <v>35609.6440417453</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">D12+D15</f>
-        <v>40769.636586226</v>
+        <v>41641.2011525673</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Input!$B$39</f>
@@ -5454,63 +7250,63 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
-        <v>-6293.1698656577</v>
+        <v>-6834.86575572748</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C18-C17</f>
-        <v>-11519.9241693609</v>
+        <v>-12209.6440417453</v>
       </c>
       <c r="D19" s="33" t="n">
         <f aca="false">D18-D17</f>
-        <v>-17369.636586226</v>
+        <v>-18241.2011525673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
-        <v>-0.268938883147765</v>
+        <v>-0.292088280159294</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IFERROR(C19/C18, 0)</f>
-        <v>-0.49230445168209</v>
+        <v>-0.521779659903644</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(D19/D18, 0)</f>
-        <v>-0.742292161804531</v>
+        <v>-0.779538510793476</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="B21" s="33" t="n">
         <f aca="false">B19*(1+B7)^Input!$B$36</f>
-        <v>-10834.1412408293</v>
+        <v>-11766.7093913601</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">C19*(1+C7)^Input!$B$36</f>
-        <v>-17809.5685747117</v>
+        <v>-18875.861475948</v>
       </c>
       <c r="D21" s="33" t="n">
         <f aca="false">D19*(1+D7)^Input!$B$36</f>
-        <v>-24101.4771940065</v>
+        <v>-25310.8285477036</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -5518,7 +7314,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -5526,7 +7322,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -5534,7 +7330,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -5542,7 +7338,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -5550,11 +7346,67 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+((1+(0.015+0.75*B7)*(1-0.17))/(1+B7)-1))^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*0.0691*(1+((1+(0.015+0.75*B7)*(1-0.17))/(1+B7)-1))^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <v>82882.7461018162</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+((1+(0.015+0.75*C7)*(1-0.17))/(1+C7)-1))^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*0.0691*(1+((1+(0.015+0.75*C7)*(1-0.17))/(1+C7)-1))^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <v>93174.6935220567</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+((1+(0.015+0.75*D7)*(1-0.17))/(1+D7)-1))^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*0.0691*(1+((1+(0.015+0.75*D7)*(1-0.17))/(1+D7)-1))^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
+        <v>104970.310567601</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+B7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*0.0691*(1+B7)^(Complementare!$A$5:$A$54-Input!$B$36))</f>
+        <v>59880.6676864256</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+C7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*0.0691*(1+C7)^(Complementare!$A$5:$A$54-Input!$B$36))</f>
+        <v>70423.5321133614</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <f aca="false">Input!$B$22*(1+D7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*0.0691*(1+D7)^(Complementare!$A$5:$A$54-Input!$B$36))</f>
+        <v>82849.0443918138</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="34" t="n">
+        <f aca="false">IF((B32*12/(Input!$B$48+Input!$B$36))&lt;=0,0,IF((B32*12/(Input!$B$48+Input!$B$36))&lt;=28000,(B32*12/(Input!$B$48+Input!$B$36))*0.23,IF((B32*12/(Input!$B$48+Input!$B$36))&lt;=50000,6440+((B32*12/(Input!$B$48+Input!$B$36))-28000)*0.33,13700+((B32*12/(Input!$B$48+Input!$B$36))-50000)*0.43))/(B32*12/(Input!$B$48+Input!$B$36)))</f>
+        <v>0.232584029892912</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <f aca="false">IF((C32*12/(Input!$B$48+Input!$B$36))&lt;=0,0,IF((C32*12/(Input!$B$48+Input!$B$36))&lt;=28000,(C32*12/(Input!$B$48+Input!$B$36))*0.23,IF((C32*12/(Input!$B$48+Input!$B$36))&lt;=50000,6440+((C32*12/(Input!$B$48+Input!$B$36))-28000)*0.33,13700+((C32*12/(Input!$B$48+Input!$B$36))-50000)*0.43))/(C32*12/(Input!$B$48+Input!$B$36)))</f>
+        <v>0.247167839239541</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <f aca="false">IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=0,0,IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=28000,(D32*12/(Input!$B$48+Input!$B$36))*0.23,IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=50000,6440+((D32*12/(Input!$B$48+Input!$B$36))-28000)*0.33,13700+((D32*12/(Input!$B$48+Input!$B$36))-50000)*0.43))/(D32*12/(Input!$B$48+Input!$B$36)))</f>
+        <v>0.259590819349152</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -845,34 +845,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1018,7 +1018,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -1415,7 +1415,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -1701,7 +1701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -1770,16 +1770,16 @@
         <v>14850</v>
       </c>
       <c r="E5" s="26" t="n">
-        <f aca="false">IF(Input!$B$14&gt;0,Input!$B$14,MIN(Input!$B$10,Input!$B$43)*Input!$B$13*(IF(ABS(((1+Input!$B$16)/(1+Input!$B$12))-1)&lt;0.0000001,Input!$B$11,((1+Input!$B$16)/(1+Input!$B$12))*(((1+Input!$B$16)/(1+Input!$B$12))^Input!$B$11-1)/(((1+Input!$B$16)/(1+Input!$B$12))-1))))</f>
-        <v>243625.067612767</v>
+        <f aca="false">IF(Input!$B$14&gt;0,Input!$B$14,Input!$B$13*SUMPRODUCT((Pubblica!$A$5:$A$54+1&lt;=Input!$B$11)*((Input!$B$10*(1+Input!$B$12)^-(Pubblica!$A$5:$A$54+1)+Input!$B$43-ABS(Input!$B$10*(1+Input!$B$12)^-(Pubblica!$A$5:$A$54+1)-Input!$B$43))/2)*(1+Input!$B$16)^Pubblica!$A$5:$A$54))</f>
+        <v>242413.002599768</v>
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">E5*Input!$B$16</f>
-        <v>1218.12533806384</v>
+        <v>1212.06501299884</v>
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">IF(B5&lt;Input!$B$6, E5+D5+F5, E5)</f>
-        <v>259693.192950831</v>
+        <v>258475.067612767</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1800,15 +1800,15 @@
       </c>
       <c r="E6" s="25" t="n">
         <f aca="false">G5</f>
-        <v>259693.192950831</v>
+        <v>258475.067612767</v>
       </c>
       <c r="F6" s="25" t="n">
         <f aca="false">E6*Input!$B$16</f>
-        <v>1298.46596475416</v>
+        <v>1292.37533806384</v>
       </c>
       <c r="G6" s="25" t="n">
         <f aca="false">IF(B6&lt;Input!$B$6, E6+D6+F6, E6)</f>
-        <v>276064.408915585</v>
+        <v>274840.192950831</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1829,15 +1829,15 @@
       </c>
       <c r="E7" s="25" t="n">
         <f aca="false">G6</f>
-        <v>276064.408915585</v>
+        <v>274840.192950831</v>
       </c>
       <c r="F7" s="25" t="n">
         <f aca="false">E7*Input!$B$16</f>
-        <v>1380.32204457793</v>
+        <v>1374.20096475416</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">IF(B7&lt;Input!$B$6, E7+D7+F7, E7)</f>
-        <v>292743.572210163</v>
+        <v>291513.235165585</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1858,15 +1858,15 @@
       </c>
       <c r="E8" s="25" t="n">
         <f aca="false">G7</f>
-        <v>292743.572210163</v>
+        <v>291513.235165585</v>
       </c>
       <c r="F8" s="25" t="n">
         <f aca="false">E8*Input!$B$16</f>
-        <v>1463.71786105082</v>
+        <v>1457.56617582793</v>
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">IF(B8&lt;Input!$B$6, E8+D8+F8, E8)</f>
-        <v>309735.613939964</v>
+        <v>308499.125210163</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1887,15 +1887,15 @@
       </c>
       <c r="E9" s="25" t="n">
         <f aca="false">G8</f>
-        <v>309735.613939964</v>
+        <v>308499.125210163</v>
       </c>
       <c r="F9" s="25" t="n">
         <f aca="false">E9*Input!$B$16</f>
-        <v>1548.67806969982</v>
+        <v>1542.49562605082</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF(B9&lt;Input!$B$6, E9+D9+F9, E9)</f>
-        <v>327045.540736445</v>
+        <v>325802.869562995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1916,15 +1916,15 @@
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">G9</f>
-        <v>327045.540736445</v>
+        <v>325802.869562995</v>
       </c>
       <c r="F10" s="25" t="n">
         <f aca="false">E10*Input!$B$16</f>
-        <v>1635.22770368223</v>
+        <v>1629.01434781498</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF(B10&lt;Input!$B$6, E10+D10+F10, E10)</f>
-        <v>344678.43589781</v>
+        <v>343429.551368493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1945,15 +1945,15 @@
       </c>
       <c r="E11" s="25" t="n">
         <f aca="false">G10</f>
-        <v>344678.43589781</v>
+        <v>343429.551368493</v>
       </c>
       <c r="F11" s="25" t="n">
         <f aca="false">E11*Input!$B$16</f>
-        <v>1723.39217948905</v>
+        <v>1717.14775684247</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF(B11&lt;Input!$B$6, E11+D11+F11, E11)</f>
-        <v>362639.460546847</v>
+        <v>361384.331594884</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1974,15 +1974,15 @@
       </c>
       <c r="E12" s="25" t="n">
         <f aca="false">G11</f>
-        <v>362639.460546847</v>
+        <v>361384.331594884</v>
       </c>
       <c r="F12" s="25" t="n">
         <f aca="false">E12*Input!$B$16</f>
-        <v>1813.19730273424</v>
+        <v>1806.92165797442</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF(B12&lt;Input!$B$6, E12+D12+F12, E12)</f>
-        <v>380933.854806173</v>
+        <v>379672.45020945</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2003,15 +2003,15 @@
       </c>
       <c r="E13" s="25" t="n">
         <f aca="false">G12</f>
-        <v>380933.854806173</v>
+        <v>379672.45020945</v>
       </c>
       <c r="F13" s="25" t="n">
         <f aca="false">E13*Input!$B$16</f>
-        <v>1904.66927403087</v>
+        <v>1898.36225104725</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF(B13&lt;Input!$B$6, E13+D13+F13, E13)</f>
-        <v>399566.938991144</v>
+        <v>398299.227371437</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2032,15 +2032,15 @@
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">G13</f>
-        <v>399566.938991144</v>
+        <v>398299.227371437</v>
       </c>
       <c r="F14" s="25" t="n">
         <f aca="false">E14*Input!$B$16</f>
-        <v>1997.83469495572</v>
+        <v>1991.49613685719</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF(B14&lt;Input!$B$6, E14+D14+F14, E14)</f>
-        <v>418544.114820704</v>
+        <v>417270.064642899</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2061,15 +2061,15 @@
       </c>
       <c r="E15" s="25" t="n">
         <f aca="false">G14</f>
-        <v>418544.114820704</v>
+        <v>417270.064642899</v>
       </c>
       <c r="F15" s="25" t="n">
         <f aca="false">E15*Input!$B$16</f>
-        <v>2092.72057410352</v>
+        <v>2086.35032321449</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF(B15&lt;Input!$B$6, E15+D15+F15, E15)</f>
-        <v>437870.866646431</v>
+        <v>436590.446217737</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2090,15 +2090,15 @@
       </c>
       <c r="E16" s="25" t="n">
         <f aca="false">G15</f>
-        <v>437870.866646431</v>
+        <v>436590.446217737</v>
       </c>
       <c r="F16" s="25" t="n">
         <f aca="false">E16*Input!$B$16</f>
-        <v>2189.35433323216</v>
+        <v>2182.95223108868</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF(B16&lt;Input!$B$6, E16+D16+F16, E16)</f>
-        <v>457552.762700061</v>
+        <v>456265.940169223</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2119,15 +2119,15 @@
       </c>
       <c r="E17" s="25" t="n">
         <f aca="false">G16</f>
-        <v>457552.762700061</v>
+        <v>456265.940169223</v>
       </c>
       <c r="F17" s="25" t="n">
         <f aca="false">E17*Input!$B$16</f>
-        <v>2287.76381350031</v>
+        <v>2281.32970084612</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF(B17&lt;Input!$B$6, E17+D17+F17, E17)</f>
-        <v>477595.456359766</v>
+        <v>476302.199716273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2148,15 +2148,15 @@
       </c>
       <c r="E18" s="25" t="n">
         <f aca="false">G17</f>
-        <v>477595.456359766</v>
+        <v>476302.199716273</v>
       </c>
       <c r="F18" s="25" t="n">
         <f aca="false">E18*Input!$B$16</f>
-        <v>2387.97728179883</v>
+        <v>2381.51099858137</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF(B18&lt;Input!$B$6, E18+D18+F18, E18)</f>
-        <v>498004.687435461</v>
+        <v>496704.964508751</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2177,15 +2177,15 @@
       </c>
       <c r="E19" s="25" t="n">
         <f aca="false">G18</f>
-        <v>498004.687435461</v>
+        <v>496704.964508751</v>
       </c>
       <c r="F19" s="25" t="n">
         <f aca="false">E19*Input!$B$16</f>
-        <v>2490.02343717731</v>
+        <v>2483.52482254376</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF(B19&lt;Input!$B$6, E19+D19+F19, E19)</f>
-        <v>518786.283473444</v>
+        <v>517480.0619321</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2206,15 +2206,15 @@
       </c>
       <c r="E20" s="25" t="n">
         <f aca="false">G19</f>
-        <v>518786.283473444</v>
+        <v>517480.0619321</v>
       </c>
       <c r="F20" s="25" t="n">
         <f aca="false">E20*Input!$B$16</f>
-        <v>2593.93141736722</v>
+        <v>2587.4003096605</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF(B20&lt;Input!$B$6, E20+D20+F20, E20)</f>
-        <v>539946.161080628</v>
+        <v>538633.408431578</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2235,15 +2235,15 @@
       </c>
       <c r="E21" s="25" t="n">
         <f aca="false">G20</f>
-        <v>539946.161080628</v>
+        <v>538633.408431578</v>
       </c>
       <c r="F21" s="25" t="n">
         <f aca="false">E21*Input!$B$16</f>
-        <v>2699.73080540314</v>
+        <v>2693.16704215789</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF(B21&lt;Input!$B$6, E21+D21+F21, E21)</f>
-        <v>561490.327268696</v>
+        <v>560171.010856401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2264,15 +2264,15 @@
       </c>
       <c r="E22" s="25" t="n">
         <f aca="false">G21</f>
-        <v>561490.327268696</v>
+        <v>560171.010856401</v>
       </c>
       <c r="F22" s="25" t="n">
         <f aca="false">E22*Input!$B$16</f>
-        <v>2807.45163634348</v>
+        <v>2800.855054282</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF(B22&lt;Input!$B$6, E22+D22+F22, E22)</f>
-        <v>583424.880818444</v>
+        <v>582098.967824087</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2293,15 +2293,15 @@
       </c>
       <c r="E23" s="25" t="n">
         <f aca="false">G22</f>
-        <v>583424.880818444</v>
+        <v>582098.967824087</v>
       </c>
       <c r="F23" s="25" t="n">
         <f aca="false">E23*Input!$B$16</f>
-        <v>2917.12440409222</v>
+        <v>2910.49483912044</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF(B23&lt;Input!$B$6, E23+D23+F23, E23)</f>
-        <v>605756.013664642</v>
+        <v>604423.471105313</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2322,15 +2322,15 @@
       </c>
       <c r="E24" s="25" t="n">
         <f aca="false">G23</f>
-        <v>605756.013664642</v>
+        <v>604423.471105313</v>
       </c>
       <c r="F24" s="25" t="n">
         <f aca="false">E24*Input!$B$16</f>
-        <v>3028.78006832321</v>
+        <v>3022.11735552657</v>
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">IF(B24&lt;Input!$B$6, E24+D24+F24, E24)</f>
-        <v>628490.012301702</v>
+        <v>627150.807029577</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,15 +2351,15 @@
       </c>
       <c r="E25" s="25" t="n">
         <f aca="false">G24</f>
-        <v>628490.012301702</v>
+        <v>627150.807029577</v>
       </c>
       <c r="F25" s="25" t="n">
         <f aca="false">E25*Input!$B$16</f>
-        <v>3142.45006150851</v>
+        <v>3135.75403514789</v>
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">IF(B25&lt;Input!$B$6, E25+D25+F25, E25)</f>
-        <v>651633.259210479</v>
+        <v>650287.357911993</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2380,15 +2380,15 @@
       </c>
       <c r="E26" s="25" t="n">
         <f aca="false">G25</f>
-        <v>651633.259210479</v>
+        <v>650287.357911993</v>
       </c>
       <c r="F26" s="25" t="n">
         <f aca="false">E26*Input!$B$16</f>
-        <v>3258.1662960524</v>
+        <v>3251.43678955997</v>
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">IF(B26&lt;Input!$B$6, E26+D26+F26, E26)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2409,15 +2409,15 @@
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">G26</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F27" s="25" t="n">
         <f aca="false">E27*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G27" s="25" t="n">
         <f aca="false">IF(B27&lt;Input!$B$6, E27+D27+F27, E27)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">G27</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F28" s="25" t="n">
         <f aca="false">E28*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G28" s="25" t="n">
         <f aca="false">IF(B28&lt;Input!$B$6, E28+D28+F28, E28)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2467,15 +2467,15 @@
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">G28</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F29" s="25" t="n">
         <f aca="false">E29*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G29" s="25" t="n">
         <f aca="false">IF(B29&lt;Input!$B$6, E29+D29+F29, E29)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2496,15 +2496,15 @@
       </c>
       <c r="E30" s="25" t="n">
         <f aca="false">G29</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F30" s="25" t="n">
         <f aca="false">E30*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G30" s="25" t="n">
         <f aca="false">IF(B30&lt;Input!$B$6, E30+D30+F30, E30)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2525,15 +2525,15 @@
       </c>
       <c r="E31" s="25" t="n">
         <f aca="false">G30</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F31" s="25" t="n">
         <f aca="false">E31*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G31" s="25" t="n">
         <f aca="false">IF(B31&lt;Input!$B$6, E31+D31+F31, E31)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2554,15 +2554,15 @@
       </c>
       <c r="E32" s="25" t="n">
         <f aca="false">G31</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F32" s="25" t="n">
         <f aca="false">E32*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G32" s="25" t="n">
         <f aca="false">IF(B32&lt;Input!$B$6, E32+D32+F32, E32)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2583,15 +2583,15 @@
       </c>
       <c r="E33" s="25" t="n">
         <f aca="false">G32</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F33" s="25" t="n">
         <f aca="false">E33*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G33" s="25" t="n">
         <f aca="false">IF(B33&lt;Input!$B$6, E33+D33+F33, E33)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2612,15 +2612,15 @@
       </c>
       <c r="E34" s="25" t="n">
         <f aca="false">G33</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F34" s="25" t="n">
         <f aca="false">E34*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G34" s="25" t="n">
         <f aca="false">IF(B34&lt;Input!$B$6, E34+D34+F34, E34)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2641,15 +2641,15 @@
       </c>
       <c r="E35" s="25" t="n">
         <f aca="false">G34</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F35" s="25" t="n">
         <f aca="false">E35*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G35" s="25" t="n">
         <f aca="false">IF(B35&lt;Input!$B$6, E35+D35+F35, E35)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2670,15 +2670,15 @@
       </c>
       <c r="E36" s="25" t="n">
         <f aca="false">G35</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F36" s="25" t="n">
         <f aca="false">E36*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G36" s="25" t="n">
         <f aca="false">IF(B36&lt;Input!$B$6, E36+D36+F36, E36)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2699,15 +2699,15 @@
       </c>
       <c r="E37" s="25" t="n">
         <f aca="false">G36</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F37" s="25" t="n">
         <f aca="false">E37*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G37" s="25" t="n">
         <f aca="false">IF(B37&lt;Input!$B$6, E37+D37+F37, E37)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2728,15 +2728,15 @@
       </c>
       <c r="E38" s="25" t="n">
         <f aca="false">G37</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F38" s="25" t="n">
         <f aca="false">E38*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G38" s="25" t="n">
         <f aca="false">IF(B38&lt;Input!$B$6, E38+D38+F38, E38)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2757,15 +2757,15 @@
       </c>
       <c r="E39" s="25" t="n">
         <f aca="false">G38</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F39" s="25" t="n">
         <f aca="false">E39*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G39" s="25" t="n">
         <f aca="false">IF(B39&lt;Input!$B$6, E39+D39+F39, E39)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2786,15 +2786,15 @@
       </c>
       <c r="E40" s="25" t="n">
         <f aca="false">G39</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F40" s="25" t="n">
         <f aca="false">E40*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G40" s="25" t="n">
         <f aca="false">IF(B40&lt;Input!$B$6, E40+D40+F40, E40)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2815,15 +2815,15 @@
       </c>
       <c r="E41" s="25" t="n">
         <f aca="false">G40</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F41" s="25" t="n">
         <f aca="false">E41*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G41" s="25" t="n">
         <f aca="false">IF(B41&lt;Input!$B$6, E41+D41+F41, E41)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2844,15 +2844,15 @@
       </c>
       <c r="E42" s="25" t="n">
         <f aca="false">G41</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F42" s="25" t="n">
         <f aca="false">E42*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G42" s="25" t="n">
         <f aca="false">IF(B42&lt;Input!$B$6, E42+D42+F42, E42)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2873,15 +2873,15 @@
       </c>
       <c r="E43" s="25" t="n">
         <f aca="false">G42</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F43" s="25" t="n">
         <f aca="false">E43*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G43" s="25" t="n">
         <f aca="false">IF(B43&lt;Input!$B$6, E43+D43+F43, E43)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2902,15 +2902,15 @@
       </c>
       <c r="E44" s="25" t="n">
         <f aca="false">G43</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F44" s="25" t="n">
         <f aca="false">E44*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G44" s="25" t="n">
         <f aca="false">IF(B44&lt;Input!$B$6, E44+D44+F44, E44)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2931,15 +2931,15 @@
       </c>
       <c r="E45" s="25" t="n">
         <f aca="false">G44</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F45" s="25" t="n">
         <f aca="false">E45*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G45" s="25" t="n">
         <f aca="false">IF(B45&lt;Input!$B$6, E45+D45+F45, E45)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2960,15 +2960,15 @@
       </c>
       <c r="E46" s="25" t="n">
         <f aca="false">G45</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F46" s="25" t="n">
         <f aca="false">E46*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G46" s="25" t="n">
         <f aca="false">IF(B46&lt;Input!$B$6, E46+D46+F46, E46)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2989,15 +2989,15 @@
       </c>
       <c r="E47" s="25" t="n">
         <f aca="false">G46</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F47" s="25" t="n">
         <f aca="false">E47*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G47" s="25" t="n">
         <f aca="false">IF(B47&lt;Input!$B$6, E47+D47+F47, E47)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3018,15 +3018,15 @@
       </c>
       <c r="E48" s="25" t="n">
         <f aca="false">G47</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F48" s="25" t="n">
         <f aca="false">E48*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G48" s="25" t="n">
         <f aca="false">IF(B48&lt;Input!$B$6, E48+D48+F48, E48)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3047,15 +3047,15 @@
       </c>
       <c r="E49" s="25" t="n">
         <f aca="false">G48</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F49" s="25" t="n">
         <f aca="false">E49*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G49" s="25" t="n">
         <f aca="false">IF(B49&lt;Input!$B$6, E49+D49+F49, E49)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3076,15 +3076,15 @@
       </c>
       <c r="E50" s="25" t="n">
         <f aca="false">G49</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F50" s="25" t="n">
         <f aca="false">E50*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G50" s="25" t="n">
         <f aca="false">IF(B50&lt;Input!$B$6, E50+D50+F50, E50)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3105,15 +3105,15 @@
       </c>
       <c r="E51" s="25" t="n">
         <f aca="false">G50</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F51" s="25" t="n">
         <f aca="false">E51*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G51" s="25" t="n">
         <f aca="false">IF(B51&lt;Input!$B$6, E51+D51+F51, E51)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3134,15 +3134,15 @@
       </c>
       <c r="E52" s="25" t="n">
         <f aca="false">G51</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F52" s="25" t="n">
         <f aca="false">E52*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G52" s="25" t="n">
         <f aca="false">IF(B52&lt;Input!$B$6, E52+D52+F52, E52)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3163,15 +3163,15 @@
       </c>
       <c r="E53" s="25" t="n">
         <f aca="false">G52</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F53" s="25" t="n">
         <f aca="false">E53*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G53" s="25" t="n">
         <f aca="false">IF(B53&lt;Input!$B$6, E53+D53+F53, E53)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3192,15 +3192,15 @@
       </c>
       <c r="E54" s="25" t="n">
         <f aca="false">G53</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
       <c r="F54" s="25" t="n">
         <f aca="false">E54*Input!$B$16</f>
-        <v>3375.96117153254</v>
+        <v>3369.19801750765</v>
       </c>
       <c r="G54" s="25" t="n">
         <f aca="false">IF(B54&lt;Input!$B$6, E54+D54+F54, E54)</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(G5:G54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
-        <v>675192.234306509</v>
+        <v>673839.60350153</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58*B60</f>
-        <v>31007.1470754117</v>
+        <v>30945.0296217775</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61/13</f>
-        <v>2385.16515964705</v>
+        <v>2380.38689398289</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">IF(B61&lt;=28000, B61*0.23, IF(B61&lt;=50000, 28000*0.23 + (B61-28000)*0.33, 28000*0.23 + 22000*0.33 + (B61-50000)*0.43))</f>
-        <v>7432.35853488586</v>
+        <v>7411.85977518658</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">IF(B61&lt;=8500, 1955, IF(B61&lt;=28000, 700 + 1255*(28000-B61)/19500, IF(B61&lt;=50000, 700*(50000-B61)/22000, 0)))</f>
-        <v>604.318047600537</v>
+        <v>606.294512034352</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B65" s="15" t="n">
         <f aca="false">IF(B63-B64&gt;0,B61*0.02,0)</f>
-        <v>620.142941508234</v>
+        <v>618.900592435551</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B66" s="29" t="n">
         <f aca="false">B61-MAX(0,B63-B64)-B65</f>
-        <v>23558.9636466181</v>
+        <v>23520.5637661897</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B67" s="29" t="n">
         <f aca="false">B66/13</f>
-        <v>1812.22797281678</v>
+        <v>1809.27413586075</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B68" s="11" t="n">
         <f aca="false">IFERROR(B61/INDEX(C5:C54, MATCH(Input!$B$6-1, B5:B54, 0)), 0)</f>
-        <v>0.504036988659156</v>
+        <v>0.503027237771827</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3347,7 +3347,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
@@ -5220,7 +5220,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
@@ -5339,15 +5339,15 @@
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">(Pubblica!$E$5*(1+B6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+B5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+B6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-B8)^(Input!$B$36/2)</f>
-        <v>25820.1521293217</v>
+        <v>25766.9337894376</v>
       </c>
       <c r="C11" s="26" t="n">
         <f aca="false">(Pubblica!$E$5*(1+C6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+C5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+C5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+C6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-C8)^(Input!$B$36/2)</f>
-        <v>31007.1470754117</v>
+        <v>30945.0296217775</v>
       </c>
       <c r="D11" s="26" t="n">
         <f aca="false">(Pubblica!$E$5*(1+D6)^Input!$B$36+SUMPRODUCT((Pubblica!$A$5:$A$54&lt;Input!$B$36)*((Input!$B$10*(1+D5)^Pubblica!$A$5:$A$54+Input!$B$43-ABS(Input!$B$10*(1+D5)^Pubblica!$A$5:$A$54-Input!$B$43))/2)*Input!$B$13*(1+D6)^(Input!$B$36-1-Pubblica!$A$5:$A$54)))*VLOOKUP(Input!$B$6,Coefficienti!$A$5:$C$19,3,FALSE())*(1-D8)^(Input!$B$36/2)</f>
-        <v>36820.8382399688</v>
+        <v>36749.1904697818</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5356,15 +5356,15 @@
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B11-MAX(0,IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0))))-IF(IF(B11&lt;=28000,B11*0.23,IF(B11&lt;=50000,6440+(B11-28000)*0.33,13700+(B11-50000)*0.43))-IF(B11&lt;=8500,1955,IF(B11&lt;=28000,700+1255*(28000-B11)/19500,IF(B11&lt;=50000,700*(50000-B11)/22000,0)))&gt;0,B11*0.02,0)</f>
-        <v>20205.4068702067</v>
+        <v>20168.9181930657</v>
       </c>
       <c r="C12" s="26" t="n">
         <f aca="false">C11-MAX(0,IF(C11&lt;=28000,C11*0.23,IF(C11&lt;=50000,6440+(C11-28000)*0.33,13700+(C11-50000)*0.43))-IF(C11&lt;=8500,1955,IF(C11&lt;=28000,700+1255*(28000-C11)/19500,IF(C11&lt;=50000,700*(50000-C11)/22000,0))))-IF(IF(C11&lt;=28000,C11*0.23,IF(C11&lt;=50000,6440+(C11-28000)*0.33,13700+(C11-50000)*0.43))-IF(C11&lt;=8500,1955,IF(C11&lt;=28000,700+1255*(28000-C11)/19500,IF(C11&lt;=50000,700*(50000-C11)/22000,0)))&gt;0,C11*0.02,0)</f>
-        <v>23558.9636466181</v>
+        <v>23520.5637661897</v>
       </c>
       <c r="D12" s="26" t="n">
         <f aca="false">D11-MAX(0,IF(D11&lt;=28000,D11*0.23,IF(D11&lt;=50000,6440+(D11-28000)*0.33,13700+(D11-50000)*0.43))-IF(D11&lt;=8500,1955,IF(D11&lt;=28000,700+1255*(28000-D11)/19500,IF(D11&lt;=50000,700*(50000-D11)/22000,0))))-IF(IF(D11&lt;=28000,D11*0.23,IF(D11&lt;=50000,6440+(D11-28000)*0.33,13700+(D11-50000)*0.43))-IF(D11&lt;=8500,1955,IF(D11&lt;=28000,700+1255*(28000-D11)/19500,IF(D11&lt;=50000,700*(50000-D11)/22000,0)))&gt;0,D11*0.02,0)</f>
-        <v>27152.8818210716</v>
+        <v>27108.5904722287</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5424,15 +5424,15 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
-        <v>29693.1698656577</v>
+        <v>29656.6811885167</v>
       </c>
       <c r="C17" s="25" t="n">
         <f aca="false">C12+C15</f>
-        <v>34919.9241693609</v>
+        <v>34881.5242889325</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">D12+D15</f>
-        <v>40769.636586226</v>
+        <v>40725.3452373832</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5458,15 +5458,15 @@
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
-        <v>-6293.1698656577</v>
+        <v>-6256.6811885167</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C18-C17</f>
-        <v>-11519.9241693609</v>
+        <v>-11481.5242889325</v>
       </c>
       <c r="D19" s="33" t="n">
         <f aca="false">D18-D17</f>
-        <v>-17369.636586226</v>
+        <v>-17325.3452373832</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5475,15 +5475,15 @@
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
-        <v>-0.268938883147765</v>
+        <v>-0.267379537970799</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IFERROR(C19/C18, 0)</f>
-        <v>-0.49230445168209</v>
+        <v>-0.490663431150962</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(D19/D18, 0)</f>
-        <v>-0.742292161804531</v>
+        <v>-0.740399369118939</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5492,15 +5492,15 @@
       </c>
       <c r="B21" s="33" t="n">
         <f aca="false">B19*(1+B7)^Input!$B$36</f>
-        <v>-10834.1412408293</v>
+        <v>-10771.3233779278</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">C19*(1+C7)^Input!$B$36</f>
-        <v>-17809.5685747117</v>
+        <v>-17750.2031402091</v>
       </c>
       <c r="D21" s="33" t="n">
         <f aca="false">D19*(1+D7)^Input!$B$36</f>
-        <v>-24101.4771940065</v>
+        <v>-24040.020126167</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="180">
   <si>
     <t xml:space="preserve">Proiezione pensionistica — Parametri di input</t>
   </si>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">es. 1,5% per CCNL metalmeccanici</t>
   </si>
   <si>
-    <t xml:space="preserve">Rendimento netto comparto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">es. bilanciato ~3,5% netto</t>
+    <t xml:space="preserve">Rendimento netto reale comparto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">al netto di costi, tassa del 20% e inflazione: bilanciato ~2,5% reale (come montecarlo-pensione.py)</t>
   </si>
   <si>
     <t xml:space="preserve">Anni di partecipazione correnti</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">1. Contributo volontario costante in termini reali: tutto il foglio è in euro di oggi.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Rendimento netto del comparto (reale) al netto della tassa annua 20% (12,5% titoli di Stato).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Aliquota finale 15% → 9% sui soli TFR e contributi dedotti: rendimenti già tassati e non dedotti comunicati sono esclusi (art. 11 c. 6 D.Lgs. 252/2005). Il montante già accumulato è trattato come dedotto.</t>
+    <t xml:space="preserve">2. Rendimento netto REALE del comparto: al netto dei costi, della tassa annua del 20% (12,5% titoli di Stato) e dell'inflazione.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Aliquota finale 15% → 9% sui soli TFR e contributi dedotti: rendimenti già tassati e non dedotti comunicati sono esclusi (art. 11 c. 6 D.Lgs. 252/2005; dal 2027 art. 258 c. 4 D.Lgs. 117/2026). Il montante già accumulato è trattato come dedotto.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Tasso conversione rendita 5,5%: vitalizia a 67 anni senza reversibilità.</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">Ciò che supera il plafond va comunicato al fondo entro il 31/12 dell'anno dopo: senza comunicazione in uscita è tassato di nuovo (9-15% del non dedotto).</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFRONTO TFR: IN AZIENDA O NEL FONDO (tutto il TFR, saldo compreso; € di oggi)</t>
+    <t xml:space="preserve">CONFRONTO TFR: IN AZIENDA O NEL FONDO (€ di oggi; TFR futuro, più il saldo solo se è già nel fondo: il maturato in azienda ci resta)</t>
   </si>
   <si>
     <t xml:space="preserve">TFR in azienda al pensionamento (lordo)</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR), poi riliquidata sui 5 anni precedenti.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fondo: rendimento del comparto (Input B28) e 15%→9% sulle sole quote di TFR, non sui rendimenti già tassati (art. 11 c. 6 D.Lgs. 252/2005). Il conferimento è irrevocabile.</t>
+    <t xml:space="preserve">Fondo: rendimento del comparto (Input B28) e 15%→9% sulle sole quote di TFR, non sui rendimenti già tassati (art. 11 c. 6 D.Lgs. 252/2005; dal 2027 art. 258 c. 4 D.Lgs. 117/2026). Il conferimento è irrevocabile e riguarda il TFR futuro: con il TFR ancora in azienda il blocco confronta le sole quote future.</t>
   </si>
   <si>
     <t xml:space="preserve">Illustrazione con le ipotesi del foglio: rischio di mercato e costi del fondo restano all'iscritto. Non è consulenza.</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">  ricalcolano INPS e fondo con la propria crescita RAL, PIL reale, decadimento e rendimento.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Fondo: montante, tassa in uscita (solo TFR e dedotti) e rendita col rendimento della colonna; il TFR in azienda (riga 16) è capitale, fuori dal gap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• L'inflazione (riga 7) entra dove la legge ragiona in nominale (TFR in azienda, base del fondo in uscita) e nella riga 21.</t>
+    <t xml:space="preserve">• Fondo: montante, tassa in uscita (solo TFR e dedotti) e rendita col rendimento della colonna; il TFR in azienda (riga 16) è capitale, fuori dal gap: la riga 34 lo traduce in rendita equivalente per il confronto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• L'inflazione (riga 7) entra solo sulle basi imponibili nominali (TFR in azienda, base del fondo in uscita) e nella riga 21. Soglie fiscali (scaglioni, plafond €5.300) restano quelle di oggi in euro di oggi, come in netto-pensione.py: se la legge non le aggiorna, l'imposta reale cresce.</t>
   </si>
   <si>
     <t xml:space="preserve">CALCOLI DI SUPPORTO — TFR in azienda per scenario</t>
@@ -561,6 +561,9 @@
   </si>
   <si>
     <t xml:space="preserve">Base della tassazione separata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFR in azienda come rendita equivalente (5,5%, solo confronto, fuori dal gap)</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1372,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>40</v>
@@ -3618,11 +3621,11 @@
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*Input!$B$28</f>
-        <v>455</v>
+        <v>325</v>
       </c>
       <c r="H5" s="25" t="n">
         <f aca="false">Input!$B$22*Input!$B$21+Input!$B$25+D5+E5+F5+G5</f>
-        <v>19239.5</v>
+        <v>19109.5</v>
       </c>
       <c r="I5" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E5+F5)-MIN(Input!$B$44,F5+C5*Input!$B$47)</f>
@@ -3641,12 +3644,12 @@
         <v>3109.5</v>
       </c>
       <c r="M5" s="25" t="n">
-        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*(1+Input!$B$49)+L5,Input!$B$22)</f>
+        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*Input!$B$21*(1+Input!$B$49)+L5,Input!$B$22*Input!$B$21)</f>
         <v>11147.931372549</v>
       </c>
       <c r="N5" s="25" t="n">
-        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*(1+Input!$B$28)+L5,Input!$B$22)</f>
-        <v>11389.5</v>
+        <f aca="false">IF(B5&lt;Input!$B$6,Input!$B$22*Input!$B$21*(1+Input!$B$28)+L5,Input!$B$22*Input!$B$21)</f>
+        <v>11309.5</v>
       </c>
       <c r="O5" s="25" t="n">
         <f aca="false">L5*(1+Input!$B$17)^(A5-Input!$B$36)</f>
@@ -3679,11 +3682,11 @@
       </c>
       <c r="G6" s="25" t="n">
         <f aca="false">H5*Input!$B$28</f>
-        <v>673.3825</v>
+        <v>477.7375</v>
       </c>
       <c r="H6" s="25" t="n">
         <f aca="false">H5+D6+E6+F6+G6</f>
-        <v>25754.15</v>
+        <v>25428.505</v>
       </c>
       <c r="I6" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E6+F6)-MIN(Input!$B$44,F6+C6*Input!$B$47)</f>
@@ -3707,7 +3710,7 @@
       </c>
       <c r="N6" s="25" t="n">
         <f aca="false">IF(B6&lt;Input!$B$6,N5*(1+Input!$B$28)+L6,N5)</f>
-        <v>14944.275</v>
+        <v>14748.38</v>
       </c>
       <c r="O6" s="25" t="n">
         <f aca="false">L6*(1+Input!$B$17)^(A6-Input!$B$36)</f>
@@ -3740,11 +3743,11 @@
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">H6*Input!$B$28</f>
-        <v>901.39525</v>
+        <v>635.712625</v>
       </c>
       <c r="H7" s="25" t="n">
         <f aca="false">H6+D7+E7+F7+G7</f>
-        <v>32554.4317625</v>
+        <v>31963.1041375</v>
       </c>
       <c r="I7" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E7+F7)-MIN(Input!$B$44,F7+C7*Input!$B$47)</f>
@@ -3768,7 +3771,7 @@
       </c>
       <c r="N7" s="25" t="n">
         <f aca="false">IF(B7&lt;Input!$B$6,N6*(1+Input!$B$28)+L7,N6)</f>
-        <v>18670.8092625</v>
+        <v>18320.5741375</v>
       </c>
       <c r="O7" s="25" t="n">
         <f aca="false">L7*(1+Input!$B$17)^(A7-Input!$B$36)</f>
@@ -3801,11 +3804,11 @@
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">H7*Input!$B$28</f>
-        <v>1139.4051116875</v>
+        <v>799.0776034375</v>
       </c>
       <c r="H8" s="25" t="n">
         <f aca="false">H7+D8+E8+F8+G8</f>
-        <v>39651.206684375</v>
+        <v>38719.551551125</v>
       </c>
       <c r="I8" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E8+F8)-MIN(Input!$B$44,F8+C8*Input!$B$47)</f>
@@ -3829,7 +3832,7 @@
       </c>
       <c r="N8" s="25" t="n">
         <f aca="false">IF(B8&lt;Input!$B$6,N7*(1+Input!$B$28)+L8,N7)</f>
-        <v>22575.82449375</v>
+        <v>22030.125398</v>
       </c>
       <c r="O8" s="25" t="n">
         <f aca="false">L8*(1+Input!$B$17)^(A8-Input!$B$36)</f>
@@ -3862,11 +3865,11 @@
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">H8*Input!$B$28</f>
-        <v>1387.79223395313</v>
+        <v>967.988788778125</v>
       </c>
       <c r="H9" s="25" t="n">
         <f aca="false">H8+D9+E9+F9+G9</f>
-        <v>47055.7292756684</v>
+        <v>45704.2706972434</v>
       </c>
       <c r="I9" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E9+F9)-MIN(Input!$B$44,F9+C9*Input!$B$47)</f>
@@ -3890,7 +3893,7 @@
       </c>
       <c r="N9" s="25" t="n">
         <f aca="false">IF(B9&lt;Input!$B$6,N8*(1+Input!$B$28)+L9,N8)</f>
-        <v>26666.2883116997</v>
+        <v>25881.1884936184</v>
       </c>
       <c r="O9" s="25" t="n">
         <f aca="false">L9*(1+Input!$B$17)^(A9-Input!$B$36)</f>
@@ -3923,11 +3926,11 @@
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">H9*Input!$B$28</f>
-        <v>1646.9505246484</v>
+        <v>1142.60676743109</v>
       </c>
       <c r="H10" s="25" t="n">
         <f aca="false">H9+D10+E10+F10+G10</f>
-        <v>54779.6611130172</v>
+        <v>52923.8587773749</v>
       </c>
       <c r="I10" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E10+F10)-MIN(Input!$B$44,F10+C10*Input!$B$47)</f>
@@ -3951,7 +3954,7 @@
       </c>
       <c r="N10" s="25" t="n">
         <f aca="false">IF(B10&lt;Input!$B$6,N9*(1+Input!$B$28)+L10,N9)</f>
-        <v>30949.4230126876</v>
+        <v>29878.0328160374</v>
       </c>
       <c r="O10" s="25" t="n">
         <f aca="false">L10*(1+Input!$B$17)^(A10-Input!$B$36)</f>
@@ -3984,11 +3987,11 @@
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">H10*Input!$B$28</f>
-        <v>1917.2881389556</v>
+        <v>1323.09646943437</v>
       </c>
       <c r="H11" s="25" t="n">
         <f aca="false">H10+D11+E11+F11+G11</f>
-        <v>62835.0852843638</v>
+        <v>60385.0912792002</v>
       </c>
       <c r="I11" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E11+F11)-MIN(Input!$B$44,F11+C11*Input!$B$47)</f>
@@ -4012,7 +4015,7 @@
       </c>
       <c r="N11" s="25" t="n">
         <f aca="false">IF(B11&lt;Input!$B$6,N10*(1+Input!$B$28)+L11,N10)</f>
-        <v>35432.7146473613</v>
+        <v>34025.0454656679</v>
       </c>
       <c r="O11" s="25" t="n">
         <f aca="false">L11*(1+Input!$B$17)^(A11-Input!$B$36)</f>
@@ -4045,11 +4048,11 @@
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">H11*Input!$B$28</f>
-        <v>2199.22798495273</v>
+        <v>1509.62728198001</v>
       </c>
       <c r="H12" s="25" t="n">
         <f aca="false">H11+D12+E12+F12+G12</f>
-        <v>71234.5213421933</v>
+        <v>68094.926634057</v>
       </c>
       <c r="I12" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E12+F12)-MIN(Input!$B$44,F12+C12*Input!$B$47)</f>
@@ -4073,7 +4076,7 @@
       </c>
       <c r="N12" s="25" t="n">
         <f aca="false">IF(B12&lt;Input!$B$6,N11*(1+Input!$B$28)+L12,N11)</f>
-        <v>40123.9224166871</v>
+        <v>38326.7343589777</v>
       </c>
       <c r="O12" s="25" t="n">
         <f aca="false">L12*(1+Input!$B$17)^(A12-Input!$B$36)</f>
@@ -4106,11 +4109,11 @@
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">H12*Input!$B$28</f>
-        <v>2493.20824697676</v>
+        <v>1702.37316585143</v>
       </c>
       <c r="H13" s="25" t="n">
         <f aca="false">H12+D13+E13+F13+G13</f>
-        <v>79990.94078314</v>
+        <v>76060.5109938784</v>
       </c>
       <c r="I13" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E13+F13)-MIN(Input!$B$44,F13+C13*Input!$B$47)</f>
@@ -4134,7 +4137,7 @@
       </c>
       <c r="N13" s="25" t="n">
         <f aca="false">IF(B13&lt;Input!$B$6,N12*(1+Input!$B$28)+L13,N12)</f>
-        <v>45031.0883992892</v>
+        <v>42787.7314159703</v>
       </c>
       <c r="O13" s="25" t="n">
         <f aca="false">L13*(1+Input!$B$17)^(A13-Input!$B$36)</f>
@@ -4167,11 +4170,11 @@
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">H13*Input!$B$28</f>
-        <v>2799.6829274099</v>
+        <v>1901.51277484696</v>
       </c>
       <c r="H14" s="25" t="n">
         <f aca="false">H13+D14+E14+F14+G14</f>
-        <v>89117.7830724294</v>
+        <v>84289.1831306048</v>
       </c>
       <c r="I14" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E14+F14)-MIN(Input!$B$44,F14+C14*Input!$B$47)</f>
@@ -4195,7 +4198,7 @@
       </c>
       <c r="N14" s="25" t="n">
         <f aca="false">IF(B14&lt;Input!$B$6,N13*(1+Input!$B$28)+L14,N13)</f>
-        <v>50162.5476217527</v>
+        <v>47412.7958298579</v>
       </c>
       <c r="O14" s="25" t="n">
         <f aca="false">L14*(1+Input!$B$17)^(A14-Input!$B$36)</f>
@@ -4228,11 +4231,11 @@
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">H14*Input!$B$28</f>
-        <v>3119.12240753503</v>
+        <v>2107.22957826512</v>
       </c>
       <c r="H15" s="25" t="n">
         <f aca="false">H14+D15+E15+F15+G15</f>
-        <v>98628.9722322721</v>
+        <v>92788.4794611776</v>
       </c>
       <c r="I15" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E15+F15)-MIN(Input!$B$44,F15+C15*Input!$B$47)</f>
@@ -4256,7 +4259,7 @@
       </c>
       <c r="N15" s="25" t="n">
         <f aca="false">IF(B15&lt;Input!$B$6,N14*(1+Input!$B$28)+L15,N14)</f>
-        <v>55526.9384839298</v>
+        <v>52206.81742102</v>
       </c>
       <c r="O15" s="25" t="n">
         <f aca="false">L15*(1+Input!$B$17)^(A15-Input!$B$36)</f>
@@ -4289,11 +4292,11 @@
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">H15*Input!$B$28</f>
-        <v>3452.01402812952</v>
+        <v>2319.71198652944</v>
       </c>
       <c r="H16" s="25" t="n">
         <f aca="false">H15+D16+E16+F16+G16</f>
-        <v>108538.934013994</v>
+        <v>101566.139201299</v>
       </c>
       <c r="I16" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E16+F16)-MIN(Input!$B$44,F16+C16*Input!$B$47)</f>
@@ -4317,7 +4320,7 @@
       </c>
       <c r="N16" s="25" t="n">
         <f aca="false">IF(B16&lt;Input!$B$6,N15*(1+Input!$B$28)+L16,N15)</f>
-        <v>61133.2135517142</v>
+        <v>57174.8200773925</v>
       </c>
       <c r="O16" s="25" t="n">
         <f aca="false">L16*(1+Input!$B$17)^(A16-Input!$B$36)</f>
@@ -4350,11 +4353,11 @@
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">H16*Input!$B$28</f>
-        <v>3798.86269048979</v>
+        <v>2539.15348003248</v>
       </c>
       <c r="H17" s="25" t="n">
         <f aca="false">H16+D17+E17+F17+G17</f>
-        <v>118862.61367438</v>
+        <v>110630.109651228</v>
       </c>
       <c r="I17" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E17+F17)-MIN(Input!$B$44,F17+C17*Input!$B$47)</f>
@@ -4378,7 +4381,7 @@
       </c>
       <c r="N17" s="25" t="n">
         <f aca="false">IF(B17&lt;Input!$B$6,N16*(1+Input!$B$28)+L17,N16)</f>
-        <v>66990.6507301839</v>
+        <v>62321.9652834869</v>
       </c>
       <c r="O17" s="25" t="n">
         <f aca="false">L17*(1+Input!$B$17)^(A17-Input!$B$36)</f>
@@ -4411,11 +4414,11 @@
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">H17*Input!$B$28</f>
-        <v>4160.1914786033</v>
+        <v>2765.7527412807</v>
       </c>
       <c r="H18" s="25" t="n">
         <f aca="false">H17+D18+E18+F18+G18</f>
-        <v>129615.494377428</v>
+        <v>119988.551616953</v>
       </c>
       <c r="I18" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E18+F18)-MIN(Input!$B$44,F18+C18*Input!$B$47)</f>
@@ -4439,7 +4442,7 @@
       </c>
       <c r="N18" s="25" t="n">
         <f aca="false">IF(B18&lt;Input!$B$6,N17*(1+Input!$B$28)+L18,N17)</f>
-        <v>73108.8648304623</v>
+        <v>67653.5557402961</v>
       </c>
       <c r="O18" s="25" t="n">
         <f aca="false">L18*(1+Input!$B$17)^(A18-Input!$B$36)</f>
@@ -4472,11 +4475,11 @@
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">H18*Input!$B$28</f>
-        <v>4536.54230320997</v>
+        <v>2999.71379042383</v>
       </c>
       <c r="H19" s="25" t="n">
         <f aca="false">H18+D19+E19+F19+G19</f>
-        <v>140813.616243449</v>
+        <v>129649.844970188</v>
       </c>
       <c r="I19" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E19+F19)-MIN(Input!$B$44,F19+C19*Input!$B$47)</f>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="N19" s="25" t="n">
         <f aca="false">IF(B19&lt;Input!$B$6,N18*(1+Input!$B$28)+L19,N18)</f>
-        <v>79497.8195441214</v>
+        <v>73175.0390783964</v>
       </c>
       <c r="O19" s="25" t="n">
         <f aca="false">L19*(1+Input!$B$17)^(A19-Input!$B$36)</f>
@@ -4533,11 +4536,11 @@
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">H19*Input!$B$28</f>
-        <v>4928.47656852072</v>
+        <v>3241.24612425471</v>
       </c>
       <c r="H20" s="25" t="n">
         <f aca="false">H19+D20+E20+F20+G20</f>
-        <v>152473.596068223</v>
+        <v>139622.594350697</v>
       </c>
       <c r="I20" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E20+F20)-MIN(Input!$B$44,F20+C20*Input!$B$47)</f>
@@ -4561,7 +4564,7 @@
       </c>
       <c r="N20" s="25" t="n">
         <f aca="false">IF(B20&lt;Input!$B$6,N19*(1+Input!$B$28)+L20,N19)</f>
-        <v>86167.8398394274</v>
+        <v>78892.011666618</v>
       </c>
       <c r="O20" s="25" t="n">
         <f aca="false">L20*(1+Input!$B$17)^(A20-Input!$B$36)</f>
@@ -4594,11 +4597,11 @@
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">H20*Input!$B$28</f>
-        <v>5336.57586238781</v>
+        <v>3490.56485876742</v>
       </c>
       <c r="H21" s="25" t="n">
         <f aca="false">H20+D21+E21+F21+G21</f>
-        <v>164612.647735708</v>
+        <v>149915.635014561</v>
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E21+F21)-MIN(Input!$B$44,F21+C21*Input!$B$47)</f>
@@ -4622,7 +4625,7 @@
       </c>
       <c r="N21" s="25" t="n">
         <f aca="false">IF(B21&lt;Input!$B$6,N20*(1+Input!$B$28)+L21,N20)</f>
-        <v>93129.624794238</v>
+        <v>84810.2225187141</v>
       </c>
       <c r="O21" s="25" t="n">
         <f aca="false">L21*(1+Input!$B$17)^(A21-Input!$B$36)</f>
@@ -4655,11 +4658,11 @@
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">H21*Input!$B$28</f>
-        <v>5761.44267074979</v>
+        <v>3747.89087536403</v>
       </c>
       <c r="H22" s="25" t="n">
         <f aca="false">H21+D22+E22+F22+G22</f>
-        <v>177248.603348632</v>
+        <v>160538.038832099</v>
       </c>
       <c r="I22" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E22+F22)-MIN(Input!$B$44,F22+C22*Input!$B$47)</f>
@@ -4683,7 +4686,7 @@
       </c>
       <c r="N22" s="25" t="n">
         <f aca="false">IF(B22&lt;Input!$B$6,N21*(1+Input!$B$28)+L22,N21)</f>
-        <v>100394.260880873</v>
+        <v>90935.5773005191</v>
       </c>
       <c r="O22" s="25" t="n">
         <f aca="false">L22*(1+Input!$B$17)^(A22-Input!$B$36)</f>
@@ -4716,11 +4719,11 @@
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">H22*Input!$B$28</f>
-        <v>6203.70111720211</v>
+        <v>4013.45097080247</v>
       </c>
       <c r="H23" s="25" t="n">
         <f aca="false">H22+D23+E23+F23+G23</f>
-        <v>190399.93510214</v>
+        <v>171499.120439208</v>
       </c>
       <c r="I23" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E23+F23)-MIN(Input!$B$44,F23+C23*Input!$B$47)</f>
@@ -4744,7 +4747,7 @@
       </c>
       <c r="N23" s="25" t="n">
         <f aca="false">IF(B23&lt;Input!$B$6,N22*(1+Input!$B$28)+L23,N22)</f>
-        <v>107973.235718824</v>
+        <v>97274.1424401518</v>
       </c>
       <c r="O23" s="25" t="n">
         <f aca="false">L23*(1+Input!$B$17)^(A23-Input!$B$36)</f>
@@ -4777,11 +4780,11 @@
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">H23*Input!$B$28</f>
-        <v>6663.9977285749</v>
+        <v>4287.47801098019</v>
       </c>
       <c r="H24" s="25" t="n">
         <f aca="false">H23+D24+E24+F24+G24</f>
-        <v>204085.777926566</v>
+        <v>182808.443546039</v>
       </c>
       <c r="I24" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E24+F24)-MIN(Input!$B$44,F24+C24*Input!$B$47)</f>
@@ -4805,7 +4808,7 @@
       </c>
       <c r="N24" s="25" t="n">
         <f aca="false">IF(B24&lt;Input!$B$6,N23*(1+Input!$B$28)+L24,N23)</f>
-        <v>115878.452311709</v>
+        <v>103832.149343882</v>
       </c>
       <c r="O24" s="25" t="n">
         <f aca="false">L24*(1+Input!$B$17)^(A24-Input!$B$36)</f>
@@ -4838,11 +4841,11 @@
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">H24*Input!$B$28</f>
-        <v>7143.00222742981</v>
+        <v>4570.21108865097</v>
       </c>
       <c r="H25" s="25" t="n">
         <f aca="false">H24+D25+E25+F25+G25</f>
-        <v>218325.952926284</v>
+        <v>194475.827406979</v>
       </c>
       <c r="I25" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E25+F25)-MIN(Input!$B$44,F25+C25*Input!$B$47)</f>
@@ -4866,7 +4869,7 @@
       </c>
       <c r="N25" s="25" t="n">
         <f aca="false">IF(B25&lt;Input!$B$6,N24*(1+Input!$B$28)+L25,N24)</f>
-        <v>124122.243785486</v>
+        <v>110615.998720347</v>
       </c>
       <c r="O25" s="25" t="n">
         <f aca="false">L25*(1+Input!$B$17)^(A25-Input!$B$36)</f>
@@ -4899,11 +4902,11 @@
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">H25*Input!$B$28</f>
-        <v>7641.40835241995</v>
+        <v>4861.89568517446</v>
       </c>
       <c r="H26" s="25" t="n">
         <f aca="false">H25+D26+E26+F26+G26</f>
-        <v>233140.991642577</v>
+        <v>206511.353456026</v>
       </c>
       <c r="I26" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E26+F26)-MIN(Input!$B$44,F26+C26*Input!$B$47)</f>
@@ -4927,7 +4930,7 @@
       </c>
       <c r="N26" s="25" t="n">
         <f aca="false">IF(B26&lt;Input!$B$6,N25*(1+Input!$B$28)+L26,N25)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O26" s="25" t="n">
         <f aca="false">L26*(1+Input!$B$17)^(A26-Input!$B$36)</f>
@@ -4960,11 +4963,11 @@
       </c>
       <c r="G27" s="25" t="n">
         <f aca="false">H26*Input!$B$28</f>
-        <v>8159.93470749021</v>
+        <v>5162.78383640065</v>
       </c>
       <c r="H27" s="25" t="n">
         <f aca="false">H26+D27+E27+F27+G27</f>
-        <v>241300.926350068</v>
+        <v>211674.137292427</v>
       </c>
       <c r="I27" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E27+F27)-MIN(Input!$B$44,F27+C27*Input!$B$47)</f>
@@ -4988,7 +4991,7 @@
       </c>
       <c r="N27" s="25" t="n">
         <f aca="false">IF(B27&lt;Input!$B$6,N26*(1+Input!$B$28)+L27,N26)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O27" s="25" t="n">
         <f aca="false">L27*(1+Input!$B$17)^(A27-Input!$B$36)</f>
@@ -5021,11 +5024,11 @@
       </c>
       <c r="G28" s="25" t="n">
         <f aca="false">H27*Input!$B$28</f>
-        <v>8445.53242225237</v>
+        <v>5291.85343231067</v>
       </c>
       <c r="H28" s="25" t="n">
         <f aca="false">H27+D28+E28+F28+G28</f>
-        <v>249746.45877232</v>
+        <v>216965.990724737</v>
       </c>
       <c r="I28" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E28+F28)-MIN(Input!$B$44,F28+C28*Input!$B$47)</f>
@@ -5049,7 +5052,7 @@
       </c>
       <c r="N28" s="25" t="n">
         <f aca="false">IF(B28&lt;Input!$B$6,N27*(1+Input!$B$28)+L28,N27)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O28" s="25" t="n">
         <f aca="false">L28*(1+Input!$B$17)^(A28-Input!$B$36)</f>
@@ -5082,11 +5085,11 @@
       </c>
       <c r="G29" s="25" t="n">
         <f aca="false">H28*Input!$B$28</f>
-        <v>8741.1260570312</v>
+        <v>5424.14976811843</v>
       </c>
       <c r="H29" s="25" t="n">
         <f aca="false">H28+D29+E29+F29+G29</f>
-        <v>258487.584829351</v>
+        <v>222390.140492856</v>
       </c>
       <c r="I29" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E29+F29)-MIN(Input!$B$44,F29+C29*Input!$B$47)</f>
@@ -5110,7 +5113,7 @@
       </c>
       <c r="N29" s="25" t="n">
         <f aca="false">IF(B29&lt;Input!$B$6,N28*(1+Input!$B$28)+L29,N28)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O29" s="25" t="n">
         <f aca="false">L29*(1+Input!$B$17)^(A29-Input!$B$36)</f>
@@ -5143,11 +5146,11 @@
       </c>
       <c r="G30" s="25" t="n">
         <f aca="false">H29*Input!$B$28</f>
-        <v>9047.06546902729</v>
+        <v>5559.75351232139</v>
       </c>
       <c r="H30" s="25" t="n">
         <f aca="false">H29+D30+E30+F30+G30</f>
-        <v>267534.650298378</v>
+        <v>227949.894005177</v>
       </c>
       <c r="I30" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E30+F30)-MIN(Input!$B$44,F30+C30*Input!$B$47)</f>
@@ -5171,7 +5174,7 @@
       </c>
       <c r="N30" s="25" t="n">
         <f aca="false">IF(B30&lt;Input!$B$6,N29*(1+Input!$B$28)+L30,N29)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O30" s="25" t="n">
         <f aca="false">L30*(1+Input!$B$17)^(A30-Input!$B$36)</f>
@@ -5204,11 +5207,11 @@
       </c>
       <c r="G31" s="25" t="n">
         <f aca="false">H30*Input!$B$28</f>
-        <v>9363.71276044324</v>
+        <v>5698.74735012943</v>
       </c>
       <c r="H31" s="25" t="n">
         <f aca="false">H30+D31+E31+F31+G31</f>
-        <v>276898.363058822</v>
+        <v>233648.641355307</v>
       </c>
       <c r="I31" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E31+F31)-MIN(Input!$B$44,F31+C31*Input!$B$47)</f>
@@ -5232,7 +5235,7 @@
       </c>
       <c r="N31" s="25" t="n">
         <f aca="false">IF(B31&lt;Input!$B$6,N30*(1+Input!$B$28)+L31,N30)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O31" s="25" t="n">
         <f aca="false">L31*(1+Input!$B$17)^(A31-Input!$B$36)</f>
@@ -5265,11 +5268,11 @@
       </c>
       <c r="G32" s="25" t="n">
         <f aca="false">H31*Input!$B$28</f>
-        <v>9691.44270705876</v>
+        <v>5841.21603388266</v>
       </c>
       <c r="H32" s="25" t="n">
         <f aca="false">H31+D32+E32+F32+G32</f>
-        <v>286589.80576588</v>
+        <v>239489.857389189</v>
       </c>
       <c r="I32" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E32+F32)-MIN(Input!$B$44,F32+C32*Input!$B$47)</f>
@@ -5293,7 +5296,7 @@
       </c>
       <c r="N32" s="25" t="n">
         <f aca="false">IF(B32&lt;Input!$B$6,N31*(1+Input!$B$28)+L32,N31)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O32" s="25" t="n">
         <f aca="false">L32*(1+Input!$B$17)^(A32-Input!$B$36)</f>
@@ -5326,11 +5329,11 @@
       </c>
       <c r="G33" s="25" t="n">
         <f aca="false">H32*Input!$B$28</f>
-        <v>10030.6432018058</v>
+        <v>5987.24643472973</v>
       </c>
       <c r="H33" s="25" t="n">
         <f aca="false">H32+D33+E33+F33+G33</f>
-        <v>296620.448967686</v>
+        <v>245477.103823919</v>
       </c>
       <c r="I33" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E33+F33)-MIN(Input!$B$44,F33+C33*Input!$B$47)</f>
@@ -5354,7 +5357,7 @@
       </c>
       <c r="N33" s="25" t="n">
         <f aca="false">IF(B33&lt;Input!$B$6,N32*(1+Input!$B$28)+L33,N32)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O33" s="25" t="n">
         <f aca="false">L33*(1+Input!$B$17)^(A33-Input!$B$36)</f>
@@ -5387,11 +5390,11 @@
       </c>
       <c r="G34" s="25" t="n">
         <f aca="false">H33*Input!$B$28</f>
-        <v>10381.715713869</v>
+        <v>6136.92759559797</v>
       </c>
       <c r="H34" s="25" t="n">
         <f aca="false">H33+D34+E34+F34+G34</f>
-        <v>307002.164681555</v>
+        <v>251614.031419517</v>
       </c>
       <c r="I34" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E34+F34)-MIN(Input!$B$44,F34+C34*Input!$B$47)</f>
@@ -5415,7 +5418,7 @@
       </c>
       <c r="N34" s="25" t="n">
         <f aca="false">IF(B34&lt;Input!$B$6,N33*(1+Input!$B$28)+L34,N33)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O34" s="25" t="n">
         <f aca="false">L34*(1+Input!$B$17)^(A34-Input!$B$36)</f>
@@ -5448,11 +5451,11 @@
       </c>
       <c r="G35" s="25" t="n">
         <f aca="false">H34*Input!$B$28</f>
-        <v>10745.0757638544</v>
+        <v>6290.35078548792</v>
       </c>
       <c r="H35" s="25" t="n">
         <f aca="false">H34+D35+E35+F35+G35</f>
-        <v>317747.24044541</v>
+        <v>257904.382205005</v>
       </c>
       <c r="I35" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E35+F35)-MIN(Input!$B$44,F35+C35*Input!$B$47)</f>
@@ -5476,7 +5479,7 @@
       </c>
       <c r="N35" s="25" t="n">
         <f aca="false">IF(B35&lt;Input!$B$6,N34*(1+Input!$B$28)+L35,N34)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O35" s="25" t="n">
         <f aca="false">L35*(1+Input!$B$17)^(A35-Input!$B$36)</f>
@@ -5509,11 +5512,11 @@
       </c>
       <c r="G36" s="25" t="n">
         <f aca="false">H35*Input!$B$28</f>
-        <v>11121.1534155893</v>
+        <v>6447.60955512512</v>
       </c>
       <c r="H36" s="25" t="n">
         <f aca="false">H35+D36+E36+F36+G36</f>
-        <v>328868.393860999</v>
+        <v>264351.99176013</v>
       </c>
       <c r="I36" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E36+F36)-MIN(Input!$B$44,F36+C36*Input!$B$47)</f>
@@ -5537,7 +5540,7 @@
       </c>
       <c r="N36" s="25" t="n">
         <f aca="false">IF(B36&lt;Input!$B$6,N35*(1+Input!$B$28)+L36,N35)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O36" s="25" t="n">
         <f aca="false">L36*(1+Input!$B$17)^(A36-Input!$B$36)</f>
@@ -5570,11 +5573,11 @@
       </c>
       <c r="G37" s="25" t="n">
         <f aca="false">H36*Input!$B$28</f>
-        <v>11510.393785135</v>
+        <v>6608.79979400325</v>
       </c>
       <c r="H37" s="25" t="n">
         <f aca="false">H36+D37+E37+F37+G37</f>
-        <v>340378.787646134</v>
+        <v>270960.791554133</v>
       </c>
       <c r="I37" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E37+F37)-MIN(Input!$B$44,F37+C37*Input!$B$47)</f>
@@ -5598,7 +5601,7 @@
       </c>
       <c r="N37" s="25" t="n">
         <f aca="false">IF(B37&lt;Input!$B$6,N36*(1+Input!$B$28)+L37,N36)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O37" s="25" t="n">
         <f aca="false">L37*(1+Input!$B$17)^(A37-Input!$B$36)</f>
@@ -5631,11 +5634,11 @@
       </c>
       <c r="G38" s="25" t="n">
         <f aca="false">H37*Input!$B$28</f>
-        <v>11913.2575676147</v>
+        <v>6774.01978885333</v>
       </c>
       <c r="H38" s="25" t="n">
         <f aca="false">H37+D38+E38+F38+G38</f>
-        <v>352292.045213749</v>
+        <v>277734.811342987</v>
       </c>
       <c r="I38" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E38+F38)-MIN(Input!$B$44,F38+C38*Input!$B$47)</f>
@@ -5659,7 +5662,7 @@
       </c>
       <c r="N38" s="25" t="n">
         <f aca="false">IF(B38&lt;Input!$B$6,N37*(1+Input!$B$28)+L38,N37)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O38" s="25" t="n">
         <f aca="false">L38*(1+Input!$B$17)^(A38-Input!$B$36)</f>
@@ -5692,11 +5695,11 @@
       </c>
       <c r="G39" s="25" t="n">
         <f aca="false">H38*Input!$B$28</f>
-        <v>12330.2215824812</v>
+        <v>6943.37028357467</v>
       </c>
       <c r="H39" s="25" t="n">
         <f aca="false">H38+D39+E39+F39+G39</f>
-        <v>364622.26679623</v>
+        <v>284678.181626561</v>
       </c>
       <c r="I39" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E39+F39)-MIN(Input!$B$44,F39+C39*Input!$B$47)</f>
@@ -5720,7 +5723,7 @@
       </c>
       <c r="N39" s="25" t="n">
         <f aca="false">IF(B39&lt;Input!$B$6,N38*(1+Input!$B$28)+L39,N38)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O39" s="25" t="n">
         <f aca="false">L39*(1+Input!$B$17)^(A39-Input!$B$36)</f>
@@ -5753,11 +5756,11 @@
       </c>
       <c r="G40" s="25" t="n">
         <f aca="false">H39*Input!$B$28</f>
-        <v>12761.779337868</v>
+        <v>7116.95454066403</v>
       </c>
       <c r="H40" s="25" t="n">
         <f aca="false">H39+D40+E40+F40+G40</f>
-        <v>377384.046134098</v>
+        <v>291795.136167225</v>
       </c>
       <c r="I40" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E40+F40)-MIN(Input!$B$44,F40+C40*Input!$B$47)</f>
@@ -5781,7 +5784,7 @@
       </c>
       <c r="N40" s="25" t="n">
         <f aca="false">IF(B40&lt;Input!$B$6,N39*(1+Input!$B$28)+L40,N39)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O40" s="25" t="n">
         <f aca="false">L40*(1+Input!$B$17)^(A40-Input!$B$36)</f>
@@ -5814,11 +5817,11 @@
       </c>
       <c r="G41" s="25" t="n">
         <f aca="false">H40*Input!$B$28</f>
-        <v>13208.4416146934</v>
+        <v>7294.87840418063</v>
       </c>
       <c r="H41" s="25" t="n">
         <f aca="false">H40+D41+E41+F41+G41</f>
-        <v>390592.487748791</v>
+        <v>299090.014571406</v>
       </c>
       <c r="I41" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E41+F41)-MIN(Input!$B$44,F41+C41*Input!$B$47)</f>
@@ -5842,7 +5845,7 @@
       </c>
       <c r="N41" s="25" t="n">
         <f aca="false">IF(B41&lt;Input!$B$6,N40*(1+Input!$B$28)+L41,N40)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O41" s="25" t="n">
         <f aca="false">L41*(1+Input!$B$17)^(A41-Input!$B$36)</f>
@@ -5875,11 +5878,11 @@
       </c>
       <c r="G42" s="25" t="n">
         <f aca="false">H41*Input!$B$28</f>
-        <v>13670.7370712077</v>
+        <v>7477.25036428515</v>
       </c>
       <c r="H42" s="25" t="n">
         <f aca="false">H41+D42+E42+F42+G42</f>
-        <v>404263.224819999</v>
+        <v>306567.264935691</v>
       </c>
       <c r="I42" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E42+F42)-MIN(Input!$B$44,F42+C42*Input!$B$47)</f>
@@ -5903,7 +5906,7 @@
       </c>
       <c r="N42" s="25" t="n">
         <f aca="false">IF(B42&lt;Input!$B$6,N41*(1+Input!$B$28)+L42,N41)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O42" s="25" t="n">
         <f aca="false">L42*(1+Input!$B$17)^(A42-Input!$B$36)</f>
@@ -5936,11 +5939,11 @@
       </c>
       <c r="G43" s="25" t="n">
         <f aca="false">H42*Input!$B$28</f>
-        <v>14149.2128687</v>
+        <v>7664.18162339228</v>
       </c>
       <c r="H43" s="25" t="n">
         <f aca="false">H42+D43+E43+F43+G43</f>
-        <v>418412.437688699</v>
+        <v>314231.446559083</v>
       </c>
       <c r="I43" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E43+F43)-MIN(Input!$B$44,F43+C43*Input!$B$47)</f>
@@ -5964,7 +5967,7 @@
       </c>
       <c r="N43" s="25" t="n">
         <f aca="false">IF(B43&lt;Input!$B$6,N42*(1+Input!$B$28)+L43,N42)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O43" s="25" t="n">
         <f aca="false">L43*(1+Input!$B$17)^(A43-Input!$B$36)</f>
@@ -5997,11 +6000,11 @@
       </c>
       <c r="G44" s="25" t="n">
         <f aca="false">H43*Input!$B$28</f>
-        <v>14644.4353191045</v>
+        <v>7855.78616397708</v>
       </c>
       <c r="H44" s="25" t="n">
         <f aca="false">H43+D44+E44+F44+G44</f>
-        <v>433056.873007803</v>
+        <v>322087.23272306</v>
       </c>
       <c r="I44" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E44+F44)-MIN(Input!$B$44,F44+C44*Input!$B$47)</f>
@@ -6025,7 +6028,7 @@
       </c>
       <c r="N44" s="25" t="n">
         <f aca="false">IF(B44&lt;Input!$B$6,N43*(1+Input!$B$28)+L44,N43)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O44" s="25" t="n">
         <f aca="false">L44*(1+Input!$B$17)^(A44-Input!$B$36)</f>
@@ -6058,11 +6061,11 @@
       </c>
       <c r="G45" s="25" t="n">
         <f aca="false">H44*Input!$B$28</f>
-        <v>15156.9905552731</v>
+        <v>8052.18081807651</v>
       </c>
       <c r="H45" s="25" t="n">
         <f aca="false">H44+D45+E45+F45+G45</f>
-        <v>448213.863563077</v>
+        <v>330139.413541137</v>
       </c>
       <c r="I45" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E45+F45)-MIN(Input!$B$44,F45+C45*Input!$B$47)</f>
@@ -6086,7 +6089,7 @@
       </c>
       <c r="N45" s="25" t="n">
         <f aca="false">IF(B45&lt;Input!$B$6,N44*(1+Input!$B$28)+L45,N44)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O45" s="25" t="n">
         <f aca="false">L45*(1+Input!$B$17)^(A45-Input!$B$36)</f>
@@ -6119,11 +6122,11 @@
       </c>
       <c r="G46" s="25" t="n">
         <f aca="false">H45*Input!$B$28</f>
-        <v>15687.4852247077</v>
+        <v>8253.48533852842</v>
       </c>
       <c r="H46" s="25" t="n">
         <f aca="false">H45+D46+E46+F46+G46</f>
-        <v>463901.348787784</v>
+        <v>338392.898879665</v>
       </c>
       <c r="I46" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E46+F46)-MIN(Input!$B$44,F46+C46*Input!$B$47)</f>
@@ -6147,7 +6150,7 @@
       </c>
       <c r="N46" s="25" t="n">
         <f aca="false">IF(B46&lt;Input!$B$6,N45*(1+Input!$B$28)+L46,N45)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O46" s="25" t="n">
         <f aca="false">L46*(1+Input!$B$17)^(A46-Input!$B$36)</f>
@@ -6180,11 +6183,11 @@
       </c>
       <c r="G47" s="25" t="n">
         <f aca="false">H46*Input!$B$28</f>
-        <v>16236.5472075724</v>
+        <v>8459.82247199163</v>
       </c>
       <c r="H47" s="25" t="n">
         <f aca="false">H46+D47+E47+F47+G47</f>
-        <v>480137.895995357</v>
+        <v>346852.721351657</v>
       </c>
       <c r="I47" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E47+F47)-MIN(Input!$B$44,F47+C47*Input!$B$47)</f>
@@ -6208,7 +6211,7 @@
       </c>
       <c r="N47" s="25" t="n">
         <f aca="false">IF(B47&lt;Input!$B$6,N46*(1+Input!$B$28)+L47,N46)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O47" s="25" t="n">
         <f aca="false">L47*(1+Input!$B$17)^(A47-Input!$B$36)</f>
@@ -6241,11 +6244,11 @@
       </c>
       <c r="G48" s="25" t="n">
         <f aca="false">H47*Input!$B$28</f>
-        <v>16804.8263598375</v>
+        <v>8671.31803379143</v>
       </c>
       <c r="H48" s="25" t="n">
         <f aca="false">H47+D48+E48+F48+G48</f>
-        <v>496942.722355194</v>
+        <v>355524.039385448</v>
       </c>
       <c r="I48" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E48+F48)-MIN(Input!$B$44,F48+C48*Input!$B$47)</f>
@@ -6269,7 +6272,7 @@
       </c>
       <c r="N48" s="25" t="n">
         <f aca="false">IF(B48&lt;Input!$B$6,N47*(1+Input!$B$28)+L48,N47)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O48" s="25" t="n">
         <f aca="false">L48*(1+Input!$B$17)^(A48-Input!$B$36)</f>
@@ -6302,11 +6305,11 @@
       </c>
       <c r="G49" s="25" t="n">
         <f aca="false">H48*Input!$B$28</f>
-        <v>17392.9952824318</v>
+        <v>8888.10098463621</v>
       </c>
       <c r="H49" s="25" t="n">
         <f aca="false">H48+D49+E49+F49+G49</f>
-        <v>514335.717637626</v>
+        <v>364412.140370085</v>
       </c>
       <c r="I49" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E49+F49)-MIN(Input!$B$44,F49+C49*Input!$B$47)</f>
@@ -6330,7 +6333,7 @@
       </c>
       <c r="N49" s="25" t="n">
         <f aca="false">IF(B49&lt;Input!$B$6,N48*(1+Input!$B$28)+L49,N48)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O49" s="25" t="n">
         <f aca="false">L49*(1+Input!$B$17)^(A49-Input!$B$36)</f>
@@ -6363,11 +6366,11 @@
       </c>
       <c r="G50" s="25" t="n">
         <f aca="false">H49*Input!$B$28</f>
-        <v>18001.7501173169</v>
+        <v>9110.30350925212</v>
       </c>
       <c r="H50" s="25" t="n">
         <f aca="false">H49+D50+E50+F50+G50</f>
-        <v>532337.467754943</v>
+        <v>373522.443879337</v>
       </c>
       <c r="I50" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E50+F50)-MIN(Input!$B$44,F50+C50*Input!$B$47)</f>
@@ -6391,7 +6394,7 @@
       </c>
       <c r="N50" s="25" t="n">
         <f aca="false">IF(B50&lt;Input!$B$6,N49*(1+Input!$B$28)+L50,N49)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O50" s="25" t="n">
         <f aca="false">L50*(1+Input!$B$17)^(A50-Input!$B$36)</f>
@@ -6424,11 +6427,11 @@
       </c>
       <c r="G51" s="25" t="n">
         <f aca="false">H50*Input!$B$28</f>
-        <v>18631.811371423</v>
+        <v>9338.06109698342</v>
       </c>
       <c r="H51" s="25" t="n">
         <f aca="false">H50+D51+E51+F51+G51</f>
-        <v>550969.279126366</v>
+        <v>382860.50497632</v>
       </c>
       <c r="I51" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E51+F51)-MIN(Input!$B$44,F51+C51*Input!$B$47)</f>
@@ -6452,7 +6455,7 @@
       </c>
       <c r="N51" s="25" t="n">
         <f aca="false">IF(B51&lt;Input!$B$6,N50*(1+Input!$B$28)+L51,N50)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O51" s="25" t="n">
         <f aca="false">L51*(1+Input!$B$17)^(A51-Input!$B$36)</f>
@@ -6485,11 +6488,11 @@
       </c>
       <c r="G52" s="25" t="n">
         <f aca="false">H51*Input!$B$28</f>
-        <v>19283.9247694228</v>
+        <v>9571.51262440801</v>
       </c>
       <c r="H52" s="25" t="n">
         <f aca="false">H51+D52+E52+F52+G52</f>
-        <v>570253.203895789</v>
+        <v>392432.017600728</v>
       </c>
       <c r="I52" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E52+F52)-MIN(Input!$B$44,F52+C52*Input!$B$47)</f>
@@ -6513,7 +6516,7 @@
       </c>
       <c r="N52" s="25" t="n">
         <f aca="false">IF(B52&lt;Input!$B$6,N51*(1+Input!$B$28)+L52,N51)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O52" s="25" t="n">
         <f aca="false">L52*(1+Input!$B$17)^(A52-Input!$B$36)</f>
@@ -6546,11 +6549,11 @@
       </c>
       <c r="G53" s="25" t="n">
         <f aca="false">H52*Input!$B$28</f>
-        <v>19958.8621363526</v>
+        <v>9810.80044001821</v>
       </c>
       <c r="H53" s="25" t="n">
         <f aca="false">H52+D53+E53+F53+G53</f>
-        <v>590212.066032141</v>
+        <v>402242.818040746</v>
       </c>
       <c r="I53" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E53+F53)-MIN(Input!$B$44,F53+C53*Input!$B$47)</f>
@@ -6574,7 +6577,7 @@
       </c>
       <c r="N53" s="25" t="n">
         <f aca="false">IF(B53&lt;Input!$B$6,N52*(1+Input!$B$28)+L53,N52)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O53" s="25" t="n">
         <f aca="false">L53*(1+Input!$B$17)^(A53-Input!$B$36)</f>
@@ -6607,11 +6610,11 @@
       </c>
       <c r="G54" s="25" t="n">
         <f aca="false">H53*Input!$B$28</f>
-        <v>20657.4223111249</v>
+        <v>10056.0704510187</v>
       </c>
       <c r="H54" s="25" t="n">
         <f aca="false">H53+D54+E54+F54+G54</f>
-        <v>610869.488343266</v>
+        <v>412298.888491765</v>
       </c>
       <c r="I54" s="25" t="n">
         <f aca="false">MIN(Input!$B$44,E54+F54)-MIN(Input!$B$44,F54+C54*Input!$B$47)</f>
@@ -6635,7 +6638,7 @@
       </c>
       <c r="N54" s="25" t="n">
         <f aca="false">IF(B54&lt;Input!$B$6,N53*(1+Input!$B$28)+L54,N53)</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
       <c r="O54" s="25" t="n">
         <f aca="false">L54*(1+Input!$B$17)^(A54-Input!$B$36)</f>
@@ -6660,7 +6663,7 @@
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">INDEX(H5:H54, MATCH(Input!$B$6-1, B5:B54, 0))</f>
-        <v>233140.991642577</v>
+        <v>206511.353456026</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6687,7 +6690,7 @@
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">B58-B60</f>
-        <v>219103.279911403</v>
+        <v>192473.641724852</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6696,7 +6699,7 @@
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B61*0.055</f>
-        <v>12050.6803951272</v>
+        <v>10586.0502948668</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6705,7 +6708,7 @@
       </c>
       <c r="B63" s="15" t="n">
         <f aca="false">B62/13</f>
-        <v>926.975415009782</v>
+        <v>814.311561143603</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6862,7 +6865,7 @@
         <v>138</v>
       </c>
       <c r="B81" s="15" t="n">
-        <f aca="false">Input!$B$22*(1+Input!$B$17)^(-Input!$B$36)+SUM(O5:O54)</f>
+        <f aca="false">Input!$B$22*Input!$B$21*(1+Input!$B$17)^(-Input!$B$36)+SUM(O5:O54)</f>
         <v>70423.5321133614</v>
       </c>
     </row>
@@ -6871,7 +6874,7 @@
         <v>139</v>
       </c>
       <c r="B82" s="15" t="n">
-        <f aca="false">B81*12/(Input!$B$48+Input!$B$36)</f>
+        <f aca="false">B81*12/(Input!$B$48*Input!$B$21+Input!$B$36)</f>
         <v>33803.2954144135</v>
       </c>
     </row>
@@ -6899,7 +6902,7 @@
       </c>
       <c r="B85" s="15" t="n">
         <f aca="false">INDEX(N5:N54,MATCH(Input!$B$6-1,B5:B54,0))</f>
-        <v>132717.388645489</v>
+        <v>117632.265015866</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6917,7 +6920,7 @@
       </c>
       <c r="B87" s="29" t="n">
         <f aca="false">B85-B86</f>
-        <v>124689.105984565</v>
+        <v>109603.982354942</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6926,7 +6929,7 @@
       </c>
       <c r="B88" s="29" t="n">
         <f aca="false">B87-B84</f>
-        <v>48920.8447265847</v>
+        <v>33835.7210969616</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6998,7 +7001,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
@@ -7101,15 +7104,15 @@
       </c>
       <c r="B9" s="32" t="n">
         <f aca="false">Input!$B$28-0.01</f>
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">Input!$B$28</f>
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D9" s="32" t="n">
         <f aca="false">Input!$B$28+0.01</f>
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7152,15 +7155,15 @@
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+B9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+B9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
-        <v>194700.656586312</v>
+        <v>172497.30771332</v>
       </c>
       <c r="C13" s="26" t="n">
         <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+C9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+C9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
-        <v>233140.991642577</v>
+        <v>206511.353456026</v>
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">(Input!$B$22*Input!$B$21+Input!$B$25)*(1+D9)^Input!$B$36+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(0.0691*Input!$B$21+Input!$B$27+Input!$B$47)+Input!$B$26)*(1+D9)^(Input!$B$36-1-Complementare!$A$5:$A$54))</f>
-        <v>279432.685515174</v>
+        <v>247509.315024691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7169,15 +7172,15 @@
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">B13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+B7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+B5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+B7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
-        <v>182353.79791856</v>
+        <v>160150.449045567</v>
       </c>
       <c r="C14" s="26" t="n">
         <f aca="false">C13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+C7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+C5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+C7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
-        <v>219103.279911403</v>
+        <v>192473.641724851</v>
       </c>
       <c r="D14" s="26" t="n">
         <f aca="false">D13-((Input!$B$22*Input!$B$21+Input!$B$25)*(1+D7)^(-Input!$B$36)+SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$36)*(Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*0.0691*Input!$B$21+((Input!$B$44+(Input!$B$26+Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))-ABS(Input!$B$44-(Input!$B$26+Input!$B$10*(1+D5)^Complementare!$A$5:$A$54*(Input!$B$47+Input!$B$27))))/2))*(1+D7)^(Complementare!$A$5:$A$54-Input!$B$36)))*Input!$B$38</f>
-        <v>263423.987845377</v>
+        <v>231500.617354895</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7186,15 +7189,15 @@
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B14*0.055</f>
-        <v>10029.4588855208</v>
+        <v>8808.2746975062</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">C14*0.055</f>
-        <v>12050.6803951272</v>
+        <v>10586.0502948668</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">D14*0.055</f>
-        <v>14488.3193314958</v>
+        <v>12732.5339545192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7220,15 +7223,15 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B12+B15</f>
-        <v>30198.3770785865</v>
+        <v>28977.1928905719</v>
       </c>
       <c r="C17" s="25" t="n">
         <f aca="false">C12+C15</f>
-        <v>35571.2441613169</v>
+        <v>34106.6140610565</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">D12+D15</f>
-        <v>41596.9098037245</v>
+        <v>39841.124426748</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7254,15 +7257,15 @@
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B18-B17</f>
-        <v>-6798.37707858647</v>
+        <v>-5577.1928905719</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C18-C17</f>
-        <v>-12171.2441613169</v>
+        <v>-10706.6140610565</v>
       </c>
       <c r="D19" s="33" t="n">
         <f aca="false">D18-D17</f>
-        <v>-18196.9098037245</v>
+        <v>-16441.124426748</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7271,15 +7274,15 @@
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(B19/B18, 0)</f>
-        <v>-0.290528934982328</v>
+        <v>-0.238341576520167</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IFERROR(C19/C18, 0)</f>
-        <v>-0.520138639372516</v>
+        <v>-0.457547609446861</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(D19/D18, 0)</f>
-        <v>-0.777645718107885</v>
+        <v>-0.702612154989229</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7288,15 +7291,15 @@
       </c>
       <c r="B21" s="33" t="n">
         <f aca="false">B19*(1+B7)^Input!$B$36</f>
-        <v>-11703.8915284586</v>
+        <v>-9601.53575919563</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">C19*(1+C7)^Input!$B$36</f>
-        <v>-18816.4960414455</v>
+        <v>-16552.2076812366</v>
       </c>
       <c r="D21" s="33" t="n">
         <f aca="false">D19*(1+D7)^Input!$B$36</f>
-        <v>-25249.3714798641</v>
+        <v>-22813.1074273204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7406,6 +7409,23 @@
       <c r="D33" s="34" t="n">
         <f aca="false">IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=0,0,IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=28000,(D32*12/(Input!$B$48+Input!$B$36))*0.23,IF((D32*12/(Input!$B$48+Input!$B$36))&lt;=50000,6440+((D32*12/(Input!$B$48+Input!$B$36))-28000)*0.33,13700+((D32*12/(Input!$B$48+Input!$B$36))-50000)*0.43))/(D32*12/(Input!$B$48+Input!$B$36)))</f>
         <v>0.259590819349152</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="26" t="n">
+        <f aca="false">B16*0.055</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <f aca="false">C16*0.055</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <f aca="false">D16*0.055</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -7043,6 +7043,7 @@
         <v>155</v>
       </c>
       <c r="B5" s="31" t="n">
+        <f aca="false">Input!$B$12-0.01</f>
         <v>0.005</v>
       </c>
       <c r="C5" s="32" t="n">
@@ -7050,6 +7051,7 @@
         <v>0.015</v>
       </c>
       <c r="D5" s="31" t="n">
+        <f aca="false">Input!$B$12+0.01</f>
         <v>0.025</v>
       </c>
     </row>
@@ -7058,6 +7060,7 @@
         <v>156</v>
       </c>
       <c r="B6" s="31" t="n">
+        <f aca="false">MAX(0,Input!$B$16-0.005)</f>
         <v>0</v>
       </c>
       <c r="C6" s="32" t="n">
@@ -7065,6 +7068,7 @@
         <v>0.005</v>
       </c>
       <c r="D6" s="31" t="n">
+        <f aca="false">Input!$B$16+0.005</f>
         <v>0.01</v>
       </c>
     </row>
@@ -7073,6 +7077,7 @@
         <v>157</v>
       </c>
       <c r="B7" s="31" t="n">
+        <f aca="false">Input!$B$17+0.005</f>
         <v>0.025</v>
       </c>
       <c r="C7" s="32" t="n">
@@ -7080,6 +7085,7 @@
         <v>0.02</v>
       </c>
       <c r="D7" s="31" t="n">
+        <f aca="false">MAX(0,Input!$B$17-0.005)</f>
         <v>0.015</v>
       </c>
     </row>
@@ -7088,6 +7094,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="31" t="n">
+        <f aca="false">Input!$B$18+0.004</f>
         <v>0.022</v>
       </c>
       <c r="C8" s="32" t="n">
@@ -7095,6 +7102,7 @@
         <v>0.018</v>
       </c>
       <c r="D8" s="31" t="n">
+        <f aca="false">MAX(0,Input!$B$18-0.003)</f>
         <v>0.015</v>
       </c>
     </row>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -431,7 +431,7 @@
     <t xml:space="preserve">Lo spazio residuo è un tetto fiscale, non un importo consigliato: dipende da liquidità e alternative. Non è consulenza.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciò che supera il plafond va comunicato al fondo entro il 31/12 dell'anno dopo: senza comunicazione in uscita è tassato di nuovo (9-15% del non dedotto).</t>
+    <t xml:space="preserve">Ciò che supera il plafond va comunicato al fondo entro il 31/12 dell'anno dopo: senza comunicazione in uscita è tassato di nuovo (9-15% del non dedotto, 23% con anticipazioni non sanitarie o riscatti per altre cause).</t>
   </si>
   <si>
     <t xml:space="preserve">CONFRONTO TFR: IN AZIENDA O NEL FONDO (€ di oggi; TFR futuro, più il saldo solo se è già nel fondo: il maturato in azienda ci resta)</t>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -323,7 +323,7 @@
     <t xml:space="preserve">IRPEF lorda su pensione (scaglioni 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR)</t>
+    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR, dal 2027 art. 13 c. 3 D.Lgs. 117/2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Addizionali regionali + comunali (~2%, se c'è IRPEF)</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">Vantaggio netto del fondo sul TFR (fondo − azienda)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR), poi riliquidata sui 5 anni precedenti.</t>
+    <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR; dal 2027 nel D.Lgs. 117/2026, articolo da verificare), poi riliquidata sui 5 anni precedenti.</t>
   </si>
   <si>
     <t xml:space="preserve">Fondo: rendimento del comparto (Input B28) e 15%→9% sulle sole quote di TFR, non sui rendimenti già tassati (art. 11 c. 6 D.Lgs. 252/2005; dal 2027 art. 258 c. 4 D.Lgs. 117/2026). Il conferimento è irrevocabile e riguarda il TFR futuro: con il TFR ancora in azienda il blocco confronta le sole quote future.</t>

--- a/skills/it-pianificazione/assets/proiezione-pensione.xlsx
+++ b/skills/it-pianificazione/assets/proiezione-pensione.xlsx
@@ -464,7 +464,7 @@
     <t xml:space="preserve">Vantaggio netto del fondo sul TFR (fondo − azienda)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR; dal 2027 nel D.Lgs. 117/2026, articolo da verificare), poi riliquidata sui 5 anni precedenti.</t>
+    <t xml:space="preserve">Azienda: rivalutazione 1,5% + 75% dell'inflazione con imposta del 17%; tassazione separata all'aliquota media del reddito di riferimento (art. 2120 c.c., art. 19 TUIR; dal 2027 art. 21 D.Lgs. 117/2026), poi riliquidata sui 5 anni precedenti.</t>
   </si>
   <si>
     <t xml:space="preserve">Fondo: rendimento del comparto (Input B28) e 15%→9% sulle sole quote di TFR, non sui rendimenti già tassati (art. 11 c. 6 D.Lgs. 252/2005; dal 2027 art. 258 c. 4 D.Lgs. 117/2026). Il conferimento è irrevocabile e riguarda il TFR futuro: con il TFR ancora in azienda il blocco confronta le sole quote future.</t>
